--- a/data/proteomics/ratio_of_organelle_volume_to_total_protein_volume.xlsx
+++ b/data/proteomics/ratio_of_organelle_volume_to_total_protein_volume.xlsx
@@ -1270,25 +1270,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4514011107868159</v>
+        <v>0.4514011107868155</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001138145322776526</v>
+        <v>0.001138145322776525</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00075640249831066</v>
+        <v>0.0007564024983106602</v>
       </c>
       <c r="E2" t="n">
         <v>0.009598240105774959</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2647587701603151</v>
+        <v>0.2647587701603148</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5835637813424227</v>
+        <v>0.5835637813424226</v>
       </c>
       <c r="H2" t="n">
-        <v>0.280762087383224</v>
+        <v>0.2807620873832241</v>
       </c>
       <c r="I2" t="n">
         <v>0.08811556074491009</v>
@@ -1300,25 +1300,25 @@
         <v>0.1238652254207412</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03168293346528692</v>
+        <v>0.03168293346528697</v>
       </c>
       <c r="M2" t="n">
         <v>0.004368911114365766</v>
       </c>
       <c r="N2" t="n">
-        <v>0.02187998626371159</v>
+        <v>0.02187998626371158</v>
       </c>
       <c r="O2" t="n">
-        <v>0.003299161701704413</v>
+        <v>0.003299161701704414</v>
       </c>
       <c r="P2" t="n">
         <v>0.004943010874955365</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007299149278678302</v>
+        <v>0.0072991492786783</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0064406365463601</v>
+        <v>0.006440636546360097</v>
       </c>
       <c r="S2" t="n">
         <v>0.004349487013014682</v>
@@ -1333,7 +1333,7 @@
         <v>0.001673429335754054</v>
       </c>
       <c r="W2" t="n">
-        <v>0.05663180859787956</v>
+        <v>0.05663180859787954</v>
       </c>
       <c r="X2" t="n">
         <v>0.0002561871569803065</v>
@@ -1345,16 +1345,16 @@
         <v>0.003091116167185114</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.02044826382745894</v>
+        <v>0.02044826382745893</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0008307916238502618</v>
+        <v>0.0008307916238502617</v>
       </c>
       <c r="AC2" t="n">
         <v>0.03615553610610975</v>
       </c>
       <c r="AD2" t="n">
-        <v>5.655671841690027e-05</v>
+        <v>5.655671841690028e-05</v>
       </c>
       <c r="AE2" t="n">
         <v>1.370749101543504e-05</v>
@@ -1363,10 +1363,10 @@
         <v>0.05163401771683859</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.03398950311822549</v>
+        <v>0.03398950311822548</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.001819325671496335</v>
+        <v>0.001819325671496336</v>
       </c>
       <c r="AI2" t="n">
         <v>0.001088840188651876</v>
@@ -1381,13 +1381,13 @@
         <v>0.000969098409233749</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.0004082609748373422</v>
+        <v>0.0004082609748373423</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.0003148811135487377</v>
+        <v>0.0003148811135487376</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.0006209891212877012</v>
+        <v>0.0006209891212877011</v>
       </c>
       <c r="AP2" t="n">
         <v>0.0005618771491061518</v>
@@ -1396,7 +1396,7 @@
         <v>0.001237985231383709</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.006803721620284389</v>
+        <v>0.006803721620284387</v>
       </c>
       <c r="AS2" t="n">
         <v>0.0001529218598010382</v>
@@ -1414,7 +1414,7 @@
         <v>0.002690212388466481</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.000260692687935699</v>
+        <v>0.0002606926879356991</v>
       </c>
       <c r="AY2" t="n">
         <v>0.02564207079487959</v>
@@ -1426,13 +1426,13 @@
         <v>0.00011278566634715</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.05068208213166546</v>
+        <v>0.05068208213166548</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.008037157056752333</v>
+        <v>0.008037157056752332</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.0216249628274928</v>
+        <v>0.02162496282749279</v>
       </c>
       <c r="BE2" t="n">
         <v>0.0004993351953941975</v>
@@ -1453,7 +1453,7 @@
         <v>0.0001898789649306993</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.02259081292718942</v>
+        <v>0.02259081292718941</v>
       </c>
       <c r="BL2" t="n">
         <v>5.814966281408395e-05</v>
@@ -1465,16 +1465,16 @@
         <v>0.001514882179045458</v>
       </c>
       <c r="BO2" t="n">
-        <v>8.122049296627732e-05</v>
+        <v>8.122049296627733e-05</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.0002506051290756246</v>
+        <v>0.0002506051290756247</v>
       </c>
       <c r="BQ2" t="n">
         <v>0.0004009095635308535</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.0004159423476499579</v>
+        <v>0.000415942347649958</v>
       </c>
       <c r="BS2" t="n">
         <v>0.02563426646094737</v>
@@ -1483,7 +1483,7 @@
         <v>0.005115191182953885</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.003659725236897285</v>
+        <v>0.003659725236897286</v>
       </c>
       <c r="BV2" t="n">
         <v>0.003339001830252153</v>
@@ -1492,10 +1492,10 @@
         <v>9.935573353947257e-06</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.002471027620689082</v>
+        <v>0.002471027620689084</v>
       </c>
       <c r="BY2" t="n">
-        <v>6.626471018563797e-05</v>
+        <v>6.626471018563796e-05</v>
       </c>
       <c r="BZ2" t="n">
         <v>0.00809651840137781</v>
@@ -1525,7 +1525,7 @@
         <v>0.0004302386434430936</v>
       </c>
       <c r="CI2" t="n">
-        <v>6.059673848522341e-05</v>
+        <v>6.059673848522342e-05</v>
       </c>
       <c r="CJ2" t="n">
         <v>0.007534733357598618</v>
@@ -1534,13 +1534,13 @@
         <v>7.956493022428301e-06</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.0004665695480942267</v>
+        <v>0.0004665695480942268</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.858461671242169e-05</v>
+        <v>2.858461671242168e-05</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.0002094064012606916</v>
+        <v>0.0002094064012606915</v>
       </c>
       <c r="CO2" t="n">
         <v>0.001531535818213803</v>
@@ -1555,10 +1555,10 @@
         <v>0.0004745486677151287</v>
       </c>
       <c r="CS2" t="n">
-        <v>6.663681591795403e-05</v>
+        <v>6.663681591795404e-05</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.0001564733439512219</v>
+        <v>0.0001564733439512218</v>
       </c>
       <c r="CU2" t="n">
         <v>7.532030353908455e-05</v>
@@ -1570,7 +1570,7 @@
         <v>0.0004454556700479366</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.004115811913481493</v>
+        <v>0.004115811913481494</v>
       </c>
       <c r="CY2" t="n">
         <v>0.0001169367282664049</v>
@@ -1579,7 +1579,7 @@
         <v>0.0002484235842227201</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.0002839159308649933</v>
+        <v>0.0002839159308649934</v>
       </c>
       <c r="DB2" t="n">
         <v>0.0004597132695445061</v>
@@ -1600,13 +1600,13 @@
         <v>0.006184904806043987</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.0004726616705908945</v>
+        <v>0.0004726616705908946</v>
       </c>
       <c r="DI2" t="n">
         <v>9.891434610827142e-05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>4.688250196906364e-05</v>
+        <v>4.688250196906363e-05</v>
       </c>
       <c r="DK2" t="n">
         <v>0.0009800760325524318</v>
@@ -1624,7 +1624,7 @@
         <v>0.0007246314682725262</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.07177026400670203</v>
+        <v>0.07177026400670201</v>
       </c>
       <c r="DQ2" t="n">
         <v>1.060362453724319e-05</v>
@@ -1645,7 +1645,7 @@
         <v>8.069318543692785e-05</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.0002891579234470404</v>
+        <v>0.0002891579234470403</v>
       </c>
       <c r="DX2" t="n">
         <v>0.0007470332889742125</v>
@@ -1678,7 +1678,7 @@
         <v>5.726454534572673e-05</v>
       </c>
       <c r="EH2" t="n">
-        <v>3.447405095807095e-05</v>
+        <v>3.447405095807094e-05</v>
       </c>
       <c r="EI2" t="n">
         <v>2.396033981212264e-05</v>
@@ -1778,37 +1778,37 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.4536859217675874</v>
+        <v>0.4536859217675871</v>
       </c>
       <c r="C3" t="n">
         <v>0.001190017355736136</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0007680449174261291</v>
+        <v>0.0007680449174261289</v>
       </c>
       <c r="E3" t="n">
         <v>0.009765240334658519</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2672907387193528</v>
+        <v>0.2672907387193527</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5851790127364522</v>
+        <v>0.585179012736452</v>
       </c>
       <c r="H3" t="n">
         <v>0.2726503286665412</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09036794060833292</v>
+        <v>0.09036794060833289</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02245936352087539</v>
+        <v>0.02245936352087538</v>
       </c>
       <c r="K3" t="n">
         <v>0.1205266605731308</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03157312306134623</v>
+        <v>0.0315731230613462</v>
       </c>
       <c r="M3" t="n">
         <v>0.004179979268314905</v>
@@ -1820,10 +1820,10 @@
         <v>0.003524899145616539</v>
       </c>
       <c r="P3" t="n">
-        <v>0.005156969452704175</v>
+        <v>0.005156969452704177</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.006422106503573297</v>
+        <v>0.006422106503573298</v>
       </c>
       <c r="R3" t="n">
         <v>0.006227037417604293</v>
@@ -1844,7 +1844,7 @@
         <v>0.05083355610080138</v>
       </c>
       <c r="X3" t="n">
-        <v>0.000290698303550565</v>
+        <v>0.0002906983035505651</v>
       </c>
       <c r="Y3" t="n">
         <v>0.003458154648143777</v>
@@ -1853,13 +1853,13 @@
         <v>0.003130223312450443</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01935157965516326</v>
+        <v>0.01935157965516325</v>
       </c>
       <c r="AB3" t="n">
         <v>0.0008482564582939524</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.03833206522084407</v>
+        <v>0.03833206522084406</v>
       </c>
       <c r="AD3" t="n">
         <v>5.418479544510544e-05</v>
@@ -1874,16 +1874,16 @@
         <v>0.03319886772038113</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.001747255584688526</v>
+        <v>0.001747255584688527</v>
       </c>
       <c r="AI3" t="n">
         <v>0.001153402767956103</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.002682065259628817</v>
+        <v>0.002682065259628815</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.01509147944556135</v>
+        <v>0.01509147944556134</v>
       </c>
       <c r="AL3" t="n">
         <v>0.0009970353294941196</v>
@@ -1895,16 +1895,16 @@
         <v>0.0002664835091614188</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.0005537462201997648</v>
+        <v>0.0005537462201997649</v>
       </c>
       <c r="AP3" t="n">
         <v>0.0004672320248287168</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.001198341356746271</v>
+        <v>0.00119834135674627</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.006463141014695298</v>
+        <v>0.006463141014695297</v>
       </c>
       <c r="AS3" t="n">
         <v>0.0001437077421570678</v>
@@ -1934,31 +1934,31 @@
         <v>0.0001196051086679883</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.05064121076697332</v>
+        <v>0.05064121076697334</v>
       </c>
       <c r="BC3" t="n">
         <v>0.007728441673491691</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.02115811677003062</v>
+        <v>0.02115811677003063</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.0004833924087487743</v>
+        <v>0.0004833924087487742</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.0008330070072213021</v>
+        <v>0.0008330070072213022</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.000803026569002872</v>
+        <v>0.0008030265690028719</v>
       </c>
       <c r="BH3" t="n">
         <v>0.01287181406900986</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.0006197372534777155</v>
+        <v>0.0006197372534777153</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.264342697978811e-05</v>
+        <v>1.264342697978812e-05</v>
       </c>
       <c r="BK3" t="n">
         <v>0.02454992913682944</v>
@@ -1967,7 +1967,7 @@
         <v>5.624979226651411e-05</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.0412716072410006</v>
+        <v>0.04127160724100061</v>
       </c>
       <c r="BN3" t="n">
         <v>0.001462551414528014</v>
@@ -1997,7 +1997,7 @@
         <v>0.003388614769110951</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.500637622412699e-06</v>
+        <v>9.500637622412701e-06</v>
       </c>
       <c r="BX3" t="n">
         <v>0.002394312049834817</v>
@@ -2039,16 +2039,16 @@
         <v>0.007720746186446582</v>
       </c>
       <c r="CK3" t="n">
-        <v>8.727305418555209e-06</v>
+        <v>8.727305418555207e-06</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.0004486990294781685</v>
+        <v>0.0004486990294781687</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.658435963637779e-05</v>
+        <v>2.658435963637778e-05</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.0002064370694548269</v>
+        <v>0.0002064370694548268</v>
       </c>
       <c r="CO3" t="n">
         <v>0.001442538034624295</v>
@@ -2057,7 +2057,7 @@
         <v>0.001104545556367649</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.001135010553992822</v>
+        <v>0.001135010553992823</v>
       </c>
       <c r="CR3" t="n">
         <v>0.0004250304910871536</v>
@@ -2078,7 +2078,7 @@
         <v>0.0004812388623252395</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.003900378018905863</v>
+        <v>0.003900378018905862</v>
       </c>
       <c r="CY3" t="n">
         <v>0.000124126258843698</v>
@@ -2093,7 +2093,7 @@
         <v>0.0004780552672017843</v>
       </c>
       <c r="DC3" t="n">
-        <v>9.88962309093617e-05</v>
+        <v>9.88962309093616e-05</v>
       </c>
       <c r="DD3" t="n">
         <v>0.001378170334893687</v>
@@ -2105,10 +2105,10 @@
         <v>0.0004425536508744434</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.006211260460040989</v>
+        <v>0.00621126046004099</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.0004541151718643716</v>
+        <v>0.0004541151718643715</v>
       </c>
       <c r="DI3" t="n">
         <v>7.344831446231966e-05</v>
@@ -2120,7 +2120,7 @@
         <v>0.0009699797078465398</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.0002934917652170636</v>
+        <v>0.0002934917652170637</v>
       </c>
       <c r="DM3" t="n">
         <v>0.0001251137037567987</v>
@@ -2132,10 +2132,10 @@
         <v>0.0006712545820733941</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.06891074474912709</v>
+        <v>0.06891074474912708</v>
       </c>
       <c r="DQ3" t="n">
-        <v>1.06445408191453e-05</v>
+        <v>1.064454081914529e-05</v>
       </c>
       <c r="DR3" t="n">
         <v>9.566710355794177e-05</v>
@@ -2144,7 +2144,7 @@
         <v>0.003265706118986035</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.001457081899758115</v>
+        <v>0.001457081899758114</v>
       </c>
       <c r="DU3" t="n">
         <v>0.003462906833552784</v>
@@ -2159,7 +2159,7 @@
         <v>0.0007711207898277211</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.0002248942708778207</v>
+        <v>0.0002248942708778208</v>
       </c>
       <c r="DZ3" t="n">
         <v>0.000200115438332615</v>
@@ -2186,7 +2186,7 @@
         <v>5.695606790626441e-05</v>
       </c>
       <c r="EH3" t="n">
-        <v>3.534571896786013e-05</v>
+        <v>3.534571896786012e-05</v>
       </c>
       <c r="EI3" t="n">
         <v>2.550314938926626e-05</v>
@@ -2286,7 +2286,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.4546769531128737</v>
+        <v>0.4546769531128738</v>
       </c>
       <c r="C4" t="n">
         <v>0.001036090688825052</v>
@@ -2298,10 +2298,10 @@
         <v>0.009531187683197603</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2704048328691838</v>
+        <v>0.2704048328691835</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5778917462687787</v>
+        <v>0.5778917462687793</v>
       </c>
       <c r="H4" t="n">
         <v>0.255821182078385</v>
@@ -2316,25 +2316,25 @@
         <v>0.1009001715220335</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03003470011600453</v>
+        <v>0.03003470011600452</v>
       </c>
       <c r="M4" t="n">
         <v>0.0041699906214876</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02616070204960104</v>
+        <v>0.02616070204960105</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003599261445777715</v>
+        <v>0.003599261445777716</v>
       </c>
       <c r="P4" t="n">
-        <v>0.004701502298385578</v>
+        <v>0.004701502298385577</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.006494758845649595</v>
+        <v>0.006494758845649594</v>
       </c>
       <c r="R4" t="n">
-        <v>0.00579236105791163</v>
+        <v>0.005792361057911629</v>
       </c>
       <c r="S4" t="n">
         <v>0.004266624905191249</v>
@@ -2349,25 +2349,25 @@
         <v>0.001611825193917325</v>
       </c>
       <c r="W4" t="n">
-        <v>0.04436376656898494</v>
+        <v>0.04436376656898493</v>
       </c>
       <c r="X4" t="n">
         <v>0.000334954037722334</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.00346652532020754</v>
+        <v>0.003466525320207539</v>
       </c>
       <c r="Z4" t="n">
         <v>0.00291322575477225</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.02024379977189248</v>
+        <v>0.02024379977189249</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0009228730472713821</v>
+        <v>0.0009228730472713828</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.03930560113956549</v>
+        <v>0.0393056011395655</v>
       </c>
       <c r="AD4" t="n">
         <v>5.802075169389524e-05</v>
@@ -2376,7 +2376,7 @@
         <v>1.578473002420768e-05</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.06482912571748299</v>
+        <v>0.06482912571748298</v>
       </c>
       <c r="AG4" t="n">
         <v>0.03962589797069917</v>
@@ -2385,19 +2385,19 @@
         <v>0.001709215079799333</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.00105532042093492</v>
+        <v>0.001055320420934921</v>
       </c>
       <c r="AJ4" t="n">
         <v>0.002642914915330515</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.01603931407200481</v>
+        <v>0.01603931407200479</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.001019689985894211</v>
+        <v>0.001019689985894212</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0004689816751697236</v>
+        <v>0.0004689816751697237</v>
       </c>
       <c r="AN4" t="n">
         <v>0.0002779340070911843</v>
@@ -2412,13 +2412,13 @@
         <v>0.001227862258222554</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.005829649317944525</v>
+        <v>0.005829649317944522</v>
       </c>
       <c r="AS4" t="n">
         <v>0.0001438831992132121</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.365631256124364e-05</v>
+        <v>8.365631256124362e-05</v>
       </c>
       <c r="AU4" t="n">
         <v>0.000398995456393626</v>
@@ -2433,7 +2433,7 @@
         <v>0.0002517308230112055</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.02374874757143994</v>
+        <v>0.02374874757143995</v>
       </c>
       <c r="AZ4" t="n">
         <v>0.0006107485110117163</v>
@@ -2442,19 +2442,19 @@
         <v>0.000114261125826021</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.04983176326419914</v>
+        <v>0.04983176326419915</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.007896109753469776</v>
+        <v>0.007896109753469778</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.02116731265853499</v>
+        <v>0.02116731265853498</v>
       </c>
       <c r="BE4" t="n">
         <v>0.0005785731792104751</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.0008181678991504555</v>
+        <v>0.0008181678991504551</v>
       </c>
       <c r="BG4" t="n">
         <v>0.0009868729972667602</v>
@@ -2481,7 +2481,7 @@
         <v>0.001450579693027305</v>
       </c>
       <c r="BO4" t="n">
-        <v>7.662702977880792e-05</v>
+        <v>7.662702977880793e-05</v>
       </c>
       <c r="BP4" t="n">
         <v>0.0002423757442130722</v>
@@ -2499,10 +2499,10 @@
         <v>0.005056887233924069</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.003544995891757779</v>
+        <v>0.003544995891757778</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.003452831585003979</v>
+        <v>0.003452831585003978</v>
       </c>
       <c r="BW4" t="n">
         <v>1.037294469037091e-05</v>
@@ -2514,13 +2514,13 @@
         <v>6.33521601827009e-05</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.008178217921525312</v>
+        <v>0.008178217921525311</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.0001245319921969532</v>
+        <v>0.0001245319921969533</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.0002517170632457235</v>
+        <v>0.0002517170632457233</v>
       </c>
       <c r="CC4" t="n">
         <v>0.000145661773098678</v>
@@ -2541,7 +2541,7 @@
         <v>0.0004205276441955875</v>
       </c>
       <c r="CI4" t="n">
-        <v>6.446543949698327e-05</v>
+        <v>6.446543949698325e-05</v>
       </c>
       <c r="CJ4" t="n">
         <v>0.008602033057261954</v>
@@ -2571,19 +2571,19 @@
         <v>0.0004018979955411816</v>
       </c>
       <c r="CS4" t="n">
-        <v>6.657676969777369e-05</v>
+        <v>6.657676969777368e-05</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.0001513424192276227</v>
+        <v>0.0001513424192276226</v>
       </c>
       <c r="CU4" t="n">
-        <v>8.859966220996153e-05</v>
+        <v>8.859966220996152e-05</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0003892256446475493</v>
+        <v>0.0003892256446475494</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.000429806564708727</v>
+        <v>0.0004298065647087271</v>
       </c>
       <c r="CX4" t="n">
         <v>0.003793568264295546</v>
@@ -2592,16 +2592,16 @@
         <v>0.0001179787916173633</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0002448763264696968</v>
+        <v>0.0002448763264696966</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.00025241209015792</v>
+        <v>0.0002524120901579198</v>
       </c>
       <c r="DB4" t="n">
         <v>0.0005324967557723864</v>
       </c>
       <c r="DC4" t="n">
-        <v>7.592779161251312e-05</v>
+        <v>7.592779161251314e-05</v>
       </c>
       <c r="DD4" t="n">
         <v>0.001386644903557045</v>
@@ -2613,22 +2613,22 @@
         <v>0.0003658479336120572</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.006181245156015991</v>
+        <v>0.00618124515601599</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.0005544673486470456</v>
+        <v>0.0005544673486470455</v>
       </c>
       <c r="DI4" t="n">
-        <v>7.597458918222002e-05</v>
+        <v>7.597458918222001e-05</v>
       </c>
       <c r="DJ4" t="n">
         <v>4.25350803238105e-05</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.0009519100974202362</v>
+        <v>0.0009519100974202372</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0002972217646922551</v>
+        <v>0.0002972217646922552</v>
       </c>
       <c r="DM4" t="n">
         <v>0.0001183785616395543</v>
@@ -2637,10 +2637,10 @@
         <v>2.392159993273484e-05</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.0007119959987661356</v>
+        <v>0.0007119959987661358</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.07038673500289598</v>
+        <v>0.07038673500289599</v>
       </c>
       <c r="DQ4" t="n">
         <v>1.114338984082168e-05</v>
@@ -2655,10 +2655,10 @@
         <v>0.001443633501436199</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.00305973484592015</v>
+        <v>0.003059734845920151</v>
       </c>
       <c r="DV4" t="n">
-        <v>6.408431369588346e-05</v>
+        <v>6.408431369588347e-05</v>
       </c>
       <c r="DW4" t="n">
         <v>0.0002374235572865494</v>
@@ -2685,7 +2685,7 @@
         <v>1.128021600501435e-05</v>
       </c>
       <c r="EE4" t="n">
-        <v>8.989315256237304e-05</v>
+        <v>8.989315256237303e-05</v>
       </c>
       <c r="EF4" t="n">
         <v>4.209032238781583e-06</v>
@@ -2794,22 +2794,22 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.4263936587167928</v>
+        <v>0.426393658716793</v>
       </c>
       <c r="C5" t="n">
         <v>0.001086987898536733</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0008835042779916193</v>
+        <v>0.0008835042779916192</v>
       </c>
       <c r="E5" t="n">
         <v>0.01145152515317253</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2510756159658741</v>
+        <v>0.251075615965874</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5663175038609508</v>
+        <v>0.566317503860951</v>
       </c>
       <c r="H5" t="n">
         <v>0.2676788059523421</v>
@@ -2830,22 +2830,22 @@
         <v>0.005103602078365277</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02022264825618191</v>
+        <v>0.0202226482561819</v>
       </c>
       <c r="O5" t="n">
-        <v>0.00335992985978082</v>
+        <v>0.003359929859780819</v>
       </c>
       <c r="P5" t="n">
         <v>0.00589582029116055</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.007365026049752811</v>
+        <v>0.007365026049752812</v>
       </c>
       <c r="R5" t="n">
         <v>0.00654916253638194</v>
       </c>
       <c r="S5" t="n">
-        <v>0.005024181085500312</v>
+        <v>0.005024181085500316</v>
       </c>
       <c r="T5" t="n">
         <v>0.01395492599191237</v>
@@ -2860,10 +2860,10 @@
         <v>0.04569397711134843</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0003464340458299951</v>
+        <v>0.000346434045829995</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.003709320322272921</v>
+        <v>0.003709320322272919</v>
       </c>
       <c r="Z5" t="n">
         <v>0.003775004523656916</v>
@@ -2875,10 +2875,10 @@
         <v>0.0009489254109138447</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.03725046939883496</v>
+        <v>0.03725046939883495</v>
       </c>
       <c r="AD5" t="n">
-        <v>5.570777481768508e-05</v>
+        <v>5.57077748176851e-05</v>
       </c>
       <c r="AE5" t="n">
         <v>1.50342817885009e-05</v>
@@ -2887,10 +2887,10 @@
         <v>0.05533502255064026</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.03951862230956376</v>
+        <v>0.03951862230956375</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.001794264421421019</v>
+        <v>0.001794264421421018</v>
       </c>
       <c r="AI5" t="n">
         <v>0.001142437232772119</v>
@@ -2911,7 +2911,7 @@
         <v>0.0002913856093048322</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0006268675586784515</v>
+        <v>0.0006268675586784514</v>
       </c>
       <c r="AP5" t="n">
         <v>0.0005309033432393475</v>
@@ -2923,13 +2923,13 @@
         <v>0.006777427524272307</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.0001529538731269048</v>
+        <v>0.0001529538731269049</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.305051973989205e-05</v>
+        <v>8.305051973989203e-05</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.0004347594291988384</v>
+        <v>0.0004347594291988383</v>
       </c>
       <c r="AV5" t="n">
         <v>0.00346035931239486</v>
@@ -2944,37 +2944,37 @@
         <v>0.02786407035277116</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0007123157257704512</v>
+        <v>0.0007123157257704508</v>
       </c>
       <c r="BA5" t="n">
         <v>0.0001130125046276351</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.04316816359047597</v>
+        <v>0.04316816359047596</v>
       </c>
       <c r="BC5" t="n">
         <v>0.009081159626295385</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.02833203554007147</v>
+        <v>0.02833203554007145</v>
       </c>
       <c r="BE5" t="n">
         <v>0.0005431514543861904</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.0009011511308431917</v>
+        <v>0.0009011511308431916</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.0008672758183233374</v>
+        <v>0.0008672758183233376</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.01886638236493762</v>
+        <v>0.01886638236493761</v>
       </c>
       <c r="BI5" t="n">
         <v>0.000532002414147426</v>
       </c>
       <c r="BJ5" t="n">
-        <v>5.66409514733609e-06</v>
+        <v>5.664095147336091e-06</v>
       </c>
       <c r="BK5" t="n">
         <v>0.01865760314305323</v>
@@ -2989,7 +2989,7 @@
         <v>0.001551270622380146</v>
       </c>
       <c r="BO5" t="n">
-        <v>8.051745426837371e-05</v>
+        <v>8.051745426837372e-05</v>
       </c>
       <c r="BP5" t="n">
         <v>0.0002739858649026024</v>
@@ -3010,16 +3010,16 @@
         <v>0.003766606529781044</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.003386697658783602</v>
+        <v>0.003386697658783601</v>
       </c>
       <c r="BW5" t="n">
         <v>1.076583434027208e-05</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.002528397896113922</v>
+        <v>0.002528397896113923</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.651104004021183e-05</v>
+        <v>8.651104004021184e-05</v>
       </c>
       <c r="BZ5" t="n">
         <v>0.009512952866026598</v>
@@ -3037,16 +3037,16 @@
         <v>0.0001673573638653699</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.0057326525470674</v>
+        <v>0.005732652547067399</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.0009759551209329709</v>
+        <v>0.000975955120932971</v>
       </c>
       <c r="CG5" t="n">
         <v>0.003856918905163178</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.0004550513373468718</v>
+        <v>0.0004550513373468719</v>
       </c>
       <c r="CI5" t="n">
         <v>8.271887595369813e-05</v>
@@ -3058,7 +3058,7 @@
         <v>1.013994484564103e-05</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.0005073825807525251</v>
+        <v>0.0005073825807525252</v>
       </c>
       <c r="CM5" t="n">
         <v>2.858312715415653e-05</v>
@@ -3070,7 +3070,7 @@
         <v>0.001279569521459332</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.0008902051093832292</v>
+        <v>0.0008902051093832293</v>
       </c>
       <c r="CQ5" t="n">
         <v>0.001117470662754544</v>
@@ -3088,7 +3088,7 @@
         <v>0.0001015853022629581</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.0003864954127770404</v>
+        <v>0.0003864954127770403</v>
       </c>
       <c r="CW5" t="n">
         <v>0.0004041246547790937</v>
@@ -3124,10 +3124,10 @@
         <v>0.006131116771282704</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.0005141827829695761</v>
+        <v>0.000514182782969576</v>
       </c>
       <c r="DI5" t="n">
-        <v>8.205786339171998e-05</v>
+        <v>8.205786339171997e-05</v>
       </c>
       <c r="DJ5" t="n">
         <v>5.70685716540379e-05</v>
@@ -3145,10 +3145,10 @@
         <v>3.365077072887017e-05</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.0009604147927331547</v>
+        <v>0.0009604147927331545</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.07920413304493257</v>
+        <v>0.07920413304493254</v>
       </c>
       <c r="DQ5" t="n">
         <v>1.002737830444164e-05</v>
@@ -3169,10 +3169,10 @@
         <v>8.785095693233644e-05</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.0003461417547028038</v>
+        <v>0.0003461417547028039</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.0007990926380037985</v>
+        <v>0.0007990926380037986</v>
       </c>
       <c r="DY5" t="n">
         <v>0.000233705076129715</v>
@@ -3181,13 +3181,13 @@
         <v>0.0001993502567594431</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.0004205601129810139</v>
+        <v>0.000420560112981014</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.0002580396522472382</v>
+        <v>0.0002580396522472383</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.005365205032086626</v>
+        <v>0.005365205032086627</v>
       </c>
       <c r="ED5" t="n">
         <v>1.133325090666739e-05</v>
@@ -3199,13 +3199,13 @@
         <v>4.804658657057016e-06</v>
       </c>
       <c r="EG5" t="n">
-        <v>9.835533551432516e-05</v>
+        <v>9.835533551432515e-05</v>
       </c>
       <c r="EH5" t="n">
-        <v>4.08143447097147e-05</v>
+        <v>4.081434470971468e-05</v>
       </c>
       <c r="EI5" t="n">
-        <v>2.837847993465129e-05</v>
+        <v>2.837847993465128e-05</v>
       </c>
       <c r="EJ5" t="n">
         <v>4.280733588173251e-05</v>
@@ -3302,28 +3302,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.4227352516911568</v>
+        <v>0.4227352516911569</v>
       </c>
       <c r="C6" t="n">
         <v>0.001066704132296637</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0008726615853132888</v>
+        <v>0.0008726615853132887</v>
       </c>
       <c r="E6" t="n">
         <v>0.01111363487178603</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2515811101390258</v>
+        <v>0.2515811101390256</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5663702387268805</v>
+        <v>0.5663702387268813</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2614041969077068</v>
+        <v>0.2614041969077067</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0825767104522898</v>
+        <v>0.08257671045228986</v>
       </c>
       <c r="J6" t="n">
         <v>0.02815547285160128</v>
@@ -3332,25 +3332,25 @@
         <v>0.103011272284949</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03438301543595158</v>
+        <v>0.03438301543595159</v>
       </c>
       <c r="M6" t="n">
         <v>0.005601051590717518</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02206054957389998</v>
+        <v>0.02206054957389996</v>
       </c>
       <c r="O6" t="n">
-        <v>0.003474109133720714</v>
+        <v>0.003474109133720713</v>
       </c>
       <c r="P6" t="n">
         <v>0.005688818709110314</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.008061015446207555</v>
+        <v>0.008061015446207557</v>
       </c>
       <c r="R6" t="n">
-        <v>0.006791665756680056</v>
+        <v>0.006791665756680058</v>
       </c>
       <c r="S6" t="n">
         <v>0.004924852278047216</v>
@@ -3371,7 +3371,7 @@
         <v>0.0003022099131444274</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.003793012992107939</v>
+        <v>0.003793012992107941</v>
       </c>
       <c r="Z6" t="n">
         <v>0.003594781959460518</v>
@@ -3380,7 +3380,7 @@
         <v>0.02207652046551524</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0009343019799458824</v>
+        <v>0.0009343019799458826</v>
       </c>
       <c r="AC6" t="n">
         <v>0.04069959670922148</v>
@@ -3407,10 +3407,10 @@
         <v>0.002808019728542689</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.01661091608057941</v>
+        <v>0.0166109160805794</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.0009570577564899209</v>
+        <v>0.0009570577564899213</v>
       </c>
       <c r="AM6" t="n">
         <v>0.0003981695691104413</v>
@@ -3422,7 +3422,7 @@
         <v>0.0006060281983793638</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.0005263893586533079</v>
+        <v>0.0005263893586533082</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.001415472210854034</v>
@@ -3449,7 +3449,7 @@
         <v>0.0002550161853322615</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.02627862706672283</v>
+        <v>0.02627862706672282</v>
       </c>
       <c r="AZ6" t="n">
         <v>0.0007139173525756071</v>
@@ -3461,7 +3461,7 @@
         <v>0.04688263262378842</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.009107309064640239</v>
+        <v>0.009107309064640237</v>
       </c>
       <c r="BD6" t="n">
         <v>0.02799779567923098</v>
@@ -3470,7 +3470,7 @@
         <v>0.000548128291267283</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.0009330877553775716</v>
+        <v>0.0009330877553775715</v>
       </c>
       <c r="BG6" t="n">
         <v>0.0011245813849962</v>
@@ -3479,7 +3479,7 @@
         <v>0.01713220518042309</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.0005092520778577367</v>
+        <v>0.0005092520778577369</v>
       </c>
       <c r="BJ6" t="n">
         <v>0.0002313847828477033</v>
@@ -3488,13 +3488,13 @@
         <v>0.0219041196173692</v>
       </c>
       <c r="BL6" t="n">
-        <v>7.576919944009851e-05</v>
+        <v>7.576919944009848e-05</v>
       </c>
       <c r="BM6" t="n">
         <v>0.02603943026841241</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.00161356607264513</v>
+        <v>0.001613566072645129</v>
       </c>
       <c r="BO6" t="n">
         <v>8.177430860095533e-05</v>
@@ -3518,7 +3518,7 @@
         <v>0.003769445650886081</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.003337774494566181</v>
+        <v>0.00333777449456618</v>
       </c>
       <c r="BW6" t="n">
         <v>1.054412450191566e-05</v>
@@ -3536,7 +3536,7 @@
         <v>0.0001229187363685428</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.0002996847235903552</v>
+        <v>0.0002996847235903553</v>
       </c>
       <c r="CC6" t="n">
         <v>0.0001299054710828738</v>
@@ -3548,10 +3548,10 @@
         <v>0.005544851793944127</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.0009932124789159391</v>
+        <v>0.0009932124789159393</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.004416257370812519</v>
+        <v>0.004416257370812521</v>
       </c>
       <c r="CH6" t="n">
         <v>0.0004516806323105955</v>
@@ -3578,7 +3578,7 @@
         <v>0.001284429072469377</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.0009703338827003325</v>
+        <v>0.0009703338827003326</v>
       </c>
       <c r="CQ6" t="n">
         <v>0.001164733289791738</v>
@@ -3587,7 +3587,7 @@
         <v>0.000509320767969408</v>
       </c>
       <c r="CS6" t="n">
-        <v>8.262680603546192e-05</v>
+        <v>8.26268060354619e-05</v>
       </c>
       <c r="CT6" t="n">
         <v>0.0001831861232492419</v>
@@ -3602,7 +3602,7 @@
         <v>0.0004555790365386943</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.003694441908169486</v>
+        <v>0.003694441908169485</v>
       </c>
       <c r="CY6" t="n">
         <v>0.0001212824903189612</v>
@@ -3611,10 +3611,10 @@
         <v>0.0002833889747667166</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.0002912877747387426</v>
+        <v>0.0002912877747387425</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.0005351462774161597</v>
+        <v>0.0005351462774161596</v>
       </c>
       <c r="DC6" t="n">
         <v>0.0001242588648592677</v>
@@ -3623,13 +3623,13 @@
         <v>0.001480312618808335</v>
       </c>
       <c r="DE6" t="n">
-        <v>9.4578980177534e-06</v>
+        <v>9.457898017753402e-06</v>
       </c>
       <c r="DF6" t="n">
         <v>0.000483594658682301</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.00621338702724572</v>
+        <v>0.006213387027245723</v>
       </c>
       <c r="DH6" t="n">
         <v>0.0005163818081614936</v>
@@ -3638,13 +3638,13 @@
         <v>7.67157452725074e-05</v>
       </c>
       <c r="DJ6" t="n">
-        <v>5.166602281082181e-05</v>
+        <v>5.16660228108218e-05</v>
       </c>
       <c r="DK6" t="n">
         <v>0.001064257804534139</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.0003189893933449248</v>
+        <v>0.0003189893933449249</v>
       </c>
       <c r="DM6" t="n">
         <v>0.0001161518803692998</v>
@@ -3656,7 +3656,7 @@
         <v>0.0009615572421100846</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.07581372615487006</v>
+        <v>0.07581372615487005</v>
       </c>
       <c r="DQ6" t="n">
         <v>1.034858085341082e-05</v>
@@ -3671,7 +3671,7 @@
         <v>0.001772297936858553</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.003615452291658845</v>
+        <v>0.003615452291658844</v>
       </c>
       <c r="DV6" t="n">
         <v>8.571568568734518e-05</v>
@@ -3683,7 +3683,7 @@
         <v>0.0008145095895362592</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.0002220324034119362</v>
+        <v>0.0002220324034119361</v>
       </c>
       <c r="DZ6" t="n">
         <v>0.0001935972120078755</v>
@@ -3704,7 +3704,7 @@
         <v>8.012324544205515e-05</v>
       </c>
       <c r="EF6" t="n">
-        <v>4.91584776143842e-06</v>
+        <v>4.915847761438418e-06</v>
       </c>
       <c r="EG6" t="n">
         <v>9.491487454593311e-05</v>
@@ -3713,7 +3713,7 @@
         <v>4.020648351617218e-05</v>
       </c>
       <c r="EI6" t="n">
-        <v>2.896654366541916e-05</v>
+        <v>2.896654366541917e-05</v>
       </c>
       <c r="EJ6" t="n">
         <v>4.513677188067991e-05</v>
@@ -3810,22 +3810,22 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4512088687422484</v>
+        <v>0.4512088687422479</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0007296455465054329</v>
+        <v>0.000729645546505433</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0006821625563865078</v>
+        <v>0.0006821625563865076</v>
       </c>
       <c r="E7" t="n">
         <v>0.01116522728610826</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2574374059033812</v>
+        <v>0.2574374059033813</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5881230487205839</v>
+        <v>0.5881230487205842</v>
       </c>
       <c r="H7" t="n">
         <v>0.3024792976751285</v>
@@ -3840,31 +3840,31 @@
         <v>0.141051231127172</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02573062721388294</v>
+        <v>0.02573062721388295</v>
       </c>
       <c r="M7" t="n">
         <v>0.00321457763481158</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0209946720768532</v>
+        <v>0.02099467207685321</v>
       </c>
       <c r="O7" t="n">
-        <v>0.005505219917798486</v>
+        <v>0.005505219917798488</v>
       </c>
       <c r="P7" t="n">
         <v>0.003699955521931143</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.005330180751681559</v>
+        <v>0.005330180751681558</v>
       </c>
       <c r="R7" t="n">
-        <v>0.004714260085010937</v>
+        <v>0.004714260085010939</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003910361819797149</v>
+        <v>0.003910361819797151</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01388764138730868</v>
+        <v>0.01388764138730869</v>
       </c>
       <c r="U7" t="n">
         <v>2.009440303992471e-05</v>
@@ -3876,28 +3876,28 @@
         <v>0.07958488400974721</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0003261793016035721</v>
+        <v>0.0003261793016035722</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.004013082790983339</v>
+        <v>0.00401308279098334</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.002244172093713539</v>
+        <v>0.00224417209371354</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.02289387107701319</v>
+        <v>0.02289387107701318</v>
       </c>
       <c r="AB7" t="n">
         <v>0.0006848128999392874</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.02594043055284688</v>
+        <v>0.02594043055284689</v>
       </c>
       <c r="AD7" t="n">
         <v>4.884138244872699e-05</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.110510761988633e-05</v>
+        <v>1.110510761988632e-05</v>
       </c>
       <c r="AF7" t="n">
         <v>0.05922247508711111</v>
@@ -3921,22 +3921,22 @@
         <v>0.0006969837275471068</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.0003128133575532775</v>
+        <v>0.0003128133575532776</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.0002579357859064338</v>
+        <v>0.0002579357859064336</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.000740839081271194</v>
+        <v>0.0007408390812711942</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.0005471863218728762</v>
+        <v>0.0005471863218728763</v>
       </c>
       <c r="AQ7" t="n">
         <v>0.001373412286213659</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.00538689377352201</v>
+        <v>0.005386893773522008</v>
       </c>
       <c r="AS7" t="n">
         <v>0.0001172817929353189</v>
@@ -3954,7 +3954,7 @@
         <v>0.002955062960795952</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0002416101699192542</v>
+        <v>0.0002416101699192543</v>
       </c>
       <c r="AY7" t="n">
         <v>0.02679733946509781</v>
@@ -3966,10 +3966,10 @@
         <v>8.707566585529874e-05</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.04173120507133175</v>
+        <v>0.04173120507133177</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.009600289791425442</v>
+        <v>0.009600289791425451</v>
       </c>
       <c r="BD7" t="n">
         <v>0.02179742698384157</v>
@@ -3993,10 +3993,10 @@
         <v>0.0001375810939115557</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.01915456682004774</v>
+        <v>0.01915456682004773</v>
       </c>
       <c r="BL7" t="n">
-        <v>6.627433425225079e-05</v>
+        <v>6.627433425225078e-05</v>
       </c>
       <c r="BM7" t="n">
         <v>0.03198886341481717</v>
@@ -4008,7 +4008,7 @@
         <v>5.688595161116749e-05</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.0002278380859693067</v>
+        <v>0.0002278380859693068</v>
       </c>
       <c r="BQ7" t="n">
         <v>0.0004470505037050659</v>
@@ -4020,13 +4020,13 @@
         <v>0.02432615682297292</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.00430615389297866</v>
+        <v>0.004306153892978661</v>
       </c>
       <c r="BU7" t="n">
         <v>0.003628611241928438</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.004199792804089682</v>
+        <v>0.004199792804089681</v>
       </c>
       <c r="BW7" t="n">
         <v>1.087431983260142e-05</v>
@@ -4068,7 +4068,7 @@
         <v>7.577190797293083e-05</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.006189827850683229</v>
+        <v>0.006189827850683231</v>
       </c>
       <c r="CK7" t="n">
         <v>7.173158778315475e-06</v>
@@ -4095,7 +4095,7 @@
         <v>0.0005646133279953498</v>
       </c>
       <c r="CS7" t="n">
-        <v>5.676328476822276e-05</v>
+        <v>5.676328476822275e-05</v>
       </c>
       <c r="CT7" t="n">
         <v>0.0001685847910219153</v>
@@ -4107,10 +4107,10 @@
         <v>0.0003422272076665877</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.0003077211116929093</v>
+        <v>0.0003077211116929092</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.003766102357410378</v>
+        <v>0.003766102357410377</v>
       </c>
       <c r="CY7" t="n">
         <v>0.0001280700647111048</v>
@@ -4119,7 +4119,7 @@
         <v>0.0001803329831529484</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.0002296314162457404</v>
+        <v>0.0002296314162457405</v>
       </c>
       <c r="DB7" t="n">
         <v>0.0004491181097675201</v>
@@ -4137,7 +4137,7 @@
         <v>0.0003368678465904926</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.005640154976530077</v>
+        <v>0.005640154976530079</v>
       </c>
       <c r="DH7" t="n">
         <v>0.0003976638085500405</v>
@@ -4146,13 +4146,13 @@
         <v>0.000100416437033503</v>
       </c>
       <c r="DJ7" t="n">
-        <v>6.711676852233648e-05</v>
+        <v>6.711676852233647e-05</v>
       </c>
       <c r="DK7" t="n">
         <v>0.0008727259950441484</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.0002522724203201565</v>
+        <v>0.0002522724203201564</v>
       </c>
       <c r="DM7" t="n">
         <v>0.0001339068415715043</v>
@@ -4170,7 +4170,7 @@
         <v>6.750365975570304e-06</v>
       </c>
       <c r="DR7" t="n">
-        <v>5.037822988110055e-05</v>
+        <v>5.037822988110054e-05</v>
       </c>
       <c r="DS7" t="n">
         <v>0.002796812640718052</v>
@@ -4185,16 +4185,16 @@
         <v>6.801563727176921e-05</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.0002421559554248662</v>
+        <v>0.0002421559554248663</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.00045249441386706</v>
+        <v>0.0004524944138670601</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.0002223111673012861</v>
+        <v>0.0002223111673012862</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.000141623024696146</v>
+        <v>0.0001416230246961461</v>
       </c>
       <c r="EA7" t="n">
         <v>0.0003091519681715799</v>
@@ -4215,10 +4215,10 @@
         <v>2.891273521419899e-06</v>
       </c>
       <c r="EG7" t="n">
-        <v>7.233880403028732e-05</v>
+        <v>7.233880403028733e-05</v>
       </c>
       <c r="EH7" t="n">
-        <v>2.570755751536343e-05</v>
+        <v>2.570755751536342e-05</v>
       </c>
       <c r="EI7" t="n">
         <v>2.112448643991745e-05</v>
@@ -4318,7 +4318,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.4185874707716747</v>
+        <v>0.4185874707716742</v>
       </c>
       <c r="C8" t="n">
         <v>0.0009182979219400753</v>
@@ -4330,13 +4330,13 @@
         <v>0.01257891601691838</v>
       </c>
       <c r="F8" t="n">
-        <v>0.242073961629441</v>
+        <v>0.2420739616294409</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5603785905562928</v>
+        <v>0.5603785905562932</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2665094618397647</v>
+        <v>0.2665094618397649</v>
       </c>
       <c r="I8" t="n">
         <v>0.07736590648399899</v>
@@ -4348,7 +4348,7 @@
         <v>0.1094202738713886</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03495570200526717</v>
+        <v>0.0349557020052672</v>
       </c>
       <c r="M8" t="n">
         <v>0.005832361432074206</v>
@@ -4366,10 +4366,10 @@
         <v>0.00856179080204846</v>
       </c>
       <c r="R8" t="n">
-        <v>0.006855887057705692</v>
+        <v>0.006855887057705695</v>
       </c>
       <c r="S8" t="n">
-        <v>0.005095442367488778</v>
+        <v>0.005095442367488779</v>
       </c>
       <c r="T8" t="n">
         <v>0.01456310661122788</v>
@@ -4378,19 +4378,19 @@
         <v>3.196061731174844e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001826443480112324</v>
+        <v>0.001826443480112325</v>
       </c>
       <c r="W8" t="n">
-        <v>0.05804575346060428</v>
+        <v>0.05804575346060426</v>
       </c>
       <c r="X8" t="n">
         <v>0.0003969114223776121</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003705618171910458</v>
+        <v>0.003705618171910457</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.003733877196616807</v>
+        <v>0.003733877196616809</v>
       </c>
       <c r="AA8" t="n">
         <v>0.02445430028984909</v>
@@ -4399,7 +4399,7 @@
         <v>0.0008665426211706415</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.03310241668819733</v>
+        <v>0.03310241668819731</v>
       </c>
       <c r="AD8" t="n">
         <v>4.859171621027023e-05</v>
@@ -4408,7 +4408,7 @@
         <v>1.282288369708415e-05</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.05481467135186881</v>
+        <v>0.0548146713518688</v>
       </c>
       <c r="AG8" t="n">
         <v>0.03515864598957492</v>
@@ -4420,22 +4420,22 @@
         <v>0.0014194851335409</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.002877338380008576</v>
+        <v>0.002877338380008577</v>
       </c>
       <c r="AK8" t="n">
         <v>0.01951746144543203</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0009178527375708043</v>
+        <v>0.0009178527375708037</v>
       </c>
       <c r="AM8" t="n">
         <v>0.0003989387867221434</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.0003177212584909772</v>
+        <v>0.0003177212584909771</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.0006177232733068819</v>
+        <v>0.0006177232733068818</v>
       </c>
       <c r="AP8" t="n">
         <v>0.0005141124502169301</v>
@@ -4453,7 +4453,7 @@
         <v>8.495240889889956e-05</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.0004198088393302269</v>
+        <v>0.000419808839330227</v>
       </c>
       <c r="AV8" t="n">
         <v>0.003792155694872007</v>
@@ -4465,7 +4465,7 @@
         <v>0.0002691290903528688</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.03092193403290284</v>
+        <v>0.03092193403290283</v>
       </c>
       <c r="AZ8" t="n">
         <v>0.0008044312323735831</v>
@@ -4474,13 +4474,13 @@
         <v>9.961741918484205e-05</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.04155325052245556</v>
+        <v>0.04155325052245558</v>
       </c>
       <c r="BC8" t="n">
         <v>0.009546392941887702</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.03114882908089266</v>
+        <v>0.03114882908089268</v>
       </c>
       <c r="BE8" t="n">
         <v>0.0004879574728392893</v>
@@ -4507,10 +4507,10 @@
         <v>7.587271765914685e-05</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.02704966738291014</v>
+        <v>0.02704966738291015</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.00178666884603313</v>
+        <v>0.001786668846033129</v>
       </c>
       <c r="BO8" t="n">
         <v>6.398629006414612e-05</v>
@@ -4525,10 +4525,10 @@
         <v>0.0002064377192702194</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.02868939677219061</v>
+        <v>0.0286893967721906</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.005601280858091069</v>
+        <v>0.005601280858091071</v>
       </c>
       <c r="BU8" t="n">
         <v>0.003942398452163197</v>
@@ -4540,7 +4540,7 @@
         <v>9.97568254422909e-06</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.00258900389422287</v>
+        <v>0.002589003894222869</v>
       </c>
       <c r="BY8" t="n">
         <v>9.935463151683942e-05</v>
@@ -4552,10 +4552,10 @@
         <v>0.0001172876929700365</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0003382253801087038</v>
+        <v>0.0003382253801087039</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.000115919420787347</v>
+        <v>0.0001159194207873469</v>
       </c>
       <c r="CD8" t="n">
         <v>0.0001872214042859456</v>
@@ -4567,7 +4567,7 @@
         <v>0.001208180454770268</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.004630124880982714</v>
+        <v>0.004630124880982715</v>
       </c>
       <c r="CH8" t="n">
         <v>0.0004901590318621084</v>
@@ -4582,10 +4582,10 @@
         <v>8.918499860381597e-06</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.0004547532637707501</v>
+        <v>0.0004547532637707502</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.568389699582836e-05</v>
+        <v>2.568389699582835e-05</v>
       </c>
       <c r="CN8" t="n">
         <v>0.000212143546922692</v>
@@ -4603,7 +4603,7 @@
         <v>0.0005772208703116492</v>
       </c>
       <c r="CS8" t="n">
-        <v>8.392174428003296e-05</v>
+        <v>8.392174428003303e-05</v>
       </c>
       <c r="CT8" t="n">
         <v>0.0002059257995501268</v>
@@ -4615,7 +4615,7 @@
         <v>0.0003865187223967765</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.0004735773807275567</v>
+        <v>0.0004735773807275566</v>
       </c>
       <c r="CX8" t="n">
         <v>0.003969444865231082</v>
@@ -4624,10 +4624,10 @@
         <v>0.0001313501623837471</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.0002621734757694376</v>
+        <v>0.0002621734757694375</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.0003016891521015849</v>
+        <v>0.000301689152101585</v>
       </c>
       <c r="DB8" t="n">
         <v>0.0005236531152600403</v>
@@ -4636,7 +4636,7 @@
         <v>0.0001135563554548111</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.00144182468900738</v>
+        <v>0.001441824689007381</v>
       </c>
       <c r="DE8" t="n">
         <v>8.887681861744466e-06</v>
@@ -4645,7 +4645,7 @@
         <v>0.0004865141747124761</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.006154011982984111</v>
+        <v>0.00615401198298411</v>
       </c>
       <c r="DH8" t="n">
         <v>0.0004619320225859645</v>
@@ -4654,7 +4654,7 @@
         <v>8.837917000834815e-05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>5.505224729798112e-05</v>
+        <v>5.505224729798111e-05</v>
       </c>
       <c r="DK8" t="n">
         <v>0.001104272551395457</v>
@@ -4675,7 +4675,7 @@
         <v>0.08960722933550004</v>
       </c>
       <c r="DQ8" t="n">
-        <v>7.635395976985975e-06</v>
+        <v>7.635395976985982e-06</v>
       </c>
       <c r="DR8" t="n">
         <v>8.461491645797574e-05</v>
@@ -4705,7 +4705,7 @@
         <v>0.000198008284222198</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.0004179396392974169</v>
+        <v>0.000417939639297417</v>
       </c>
       <c r="EB8" t="n">
         <v>0.0002683390819392805</v>
@@ -4726,7 +4726,7 @@
         <v>8.159689207490149e-05</v>
       </c>
       <c r="EH8" t="n">
-        <v>3.930680540322752e-05</v>
+        <v>3.930680540322751e-05</v>
       </c>
       <c r="EI8" t="n">
         <v>2.859634109038066e-05</v>
@@ -4826,7 +4826,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4206230090933054</v>
+        <v>0.4206230090933055</v>
       </c>
       <c r="C9" t="n">
         <v>0.0008861545834932984</v>
@@ -4838,7 +4838,7 @@
         <v>0.01247913185216071</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2471561411295326</v>
+        <v>0.2471561411295324</v>
       </c>
       <c r="G9" t="n">
         <v>0.5584154370198481</v>
@@ -4847,7 +4847,7 @@
         <v>0.2701226509151341</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07900965566410828</v>
+        <v>0.07900965566410829</v>
       </c>
       <c r="J9" t="n">
         <v>0.03086140033662638</v>
@@ -4856,13 +4856,13 @@
         <v>0.1099627838772212</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03457142741800375</v>
+        <v>0.03457142741800372</v>
       </c>
       <c r="M9" t="n">
         <v>0.005481639076710339</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02218574555128188</v>
+        <v>0.02218574555128189</v>
       </c>
       <c r="O9" t="n">
         <v>0.005074721046069027</v>
@@ -4871,25 +4871,25 @@
         <v>0.005538328073384968</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.008178306797290615</v>
+        <v>0.008178306797290607</v>
       </c>
       <c r="R9" t="n">
-        <v>0.006605363965043273</v>
+        <v>0.006605363965043277</v>
       </c>
       <c r="S9" t="n">
-        <v>0.005230095749707733</v>
+        <v>0.005230095749707736</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01465627153899894</v>
+        <v>0.01465627153899893</v>
       </c>
       <c r="U9" t="n">
         <v>3.208849545458228e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001902801944076172</v>
+        <v>0.001902801944076173</v>
       </c>
       <c r="W9" t="n">
-        <v>0.05663733234435009</v>
+        <v>0.05663733234435006</v>
       </c>
       <c r="X9" t="n">
         <v>0.0003867427853699841</v>
@@ -4898,7 +4898,7 @@
         <v>0.003764931573672967</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.003550377360484212</v>
+        <v>0.003550377360484213</v>
       </c>
       <c r="AA9" t="n">
         <v>0.02430260618052312</v>
@@ -4907,7 +4907,7 @@
         <v>0.0008675842159623827</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.03285569065337129</v>
+        <v>0.03285569065337133</v>
       </c>
       <c r="AD9" t="n">
         <v>5.171796060828524e-05</v>
@@ -4964,7 +4964,7 @@
         <v>0.0004064401179867325</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.003700794729834849</v>
+        <v>0.00370079472983485</v>
       </c>
       <c r="AW9" t="n">
         <v>0.003839133010820785</v>
@@ -4973,13 +4973,13 @@
         <v>0.0002821960810717486</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.03069738614254761</v>
+        <v>0.03069738614254763</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.0008079864315854585</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.464275449122237e-05</v>
+        <v>9.464275449122245e-05</v>
       </c>
       <c r="BB9" t="n">
         <v>0.03927097684150835</v>
@@ -4988,10 +4988,10 @@
         <v>0.009638331446216694</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.03080030862609277</v>
+        <v>0.03080030862609279</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.0005464423400826753</v>
+        <v>0.0005464423400826754</v>
       </c>
       <c r="BF9" t="n">
         <v>0.0008283976088964431</v>
@@ -5012,13 +5012,13 @@
         <v>0.01807001660112404</v>
       </c>
       <c r="BL9" t="n">
-        <v>7.746115098640577e-05</v>
+        <v>7.746115098640579e-05</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.02744036884264832</v>
+        <v>0.02744036884264833</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.001771729597464904</v>
+        <v>0.001771729597464905</v>
       </c>
       <c r="BO9" t="n">
         <v>6.284282435804147e-05</v>
@@ -5027,22 +5027,22 @@
         <v>0.0002706966659756605</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.0005046484597673816</v>
+        <v>0.0005046484597673817</v>
       </c>
       <c r="BR9" t="n">
         <v>0.0001822298882981393</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.02901067621456172</v>
+        <v>0.02901067621456173</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.005379728394836999</v>
+        <v>0.005379728394837002</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.003743452435176626</v>
+        <v>0.003743452435176627</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.003755422488185732</v>
+        <v>0.003755422488185731</v>
       </c>
       <c r="BW9" t="n">
         <v>9.521104269836174e-06</v>
@@ -5069,13 +5069,13 @@
         <v>0.0001772445490583476</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.007239378611006459</v>
+        <v>0.007239378611006458</v>
       </c>
       <c r="CF9" t="n">
         <v>0.001276952497685258</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.00430107127050358</v>
+        <v>0.004301071270503579</v>
       </c>
       <c r="CH9" t="n">
         <v>0.0005058538204923151</v>
@@ -5117,13 +5117,13 @@
         <v>0.0001941249192287875</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.0001223872540965596</v>
+        <v>0.0001223872540965595</v>
       </c>
       <c r="CV9" t="n">
         <v>0.0003829302297349509</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.000431738207025463</v>
+        <v>0.0004317382070254632</v>
       </c>
       <c r="CX9" t="n">
         <v>0.004261356402639937</v>
@@ -5135,7 +5135,7 @@
         <v>0.0002605784200409152</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.0003087262306103853</v>
+        <v>0.0003087262306103854</v>
       </c>
       <c r="DB9" t="n">
         <v>0.0005197055237990333</v>
@@ -5153,7 +5153,7 @@
         <v>0.0004720250126189642</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.006020903563259797</v>
+        <v>0.006020903563259796</v>
       </c>
       <c r="DH9" t="n">
         <v>0.0005201630302955506</v>
@@ -5195,7 +5195,7 @@
         <v>0.001456093857529799</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.003447447219291094</v>
+        <v>0.003447447219291095</v>
       </c>
       <c r="DV9" t="n">
         <v>9.4808575618102e-05</v>
@@ -5210,7 +5210,7 @@
         <v>0.0002644892628782009</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.0001980238905267614</v>
+        <v>0.0001980238905267615</v>
       </c>
       <c r="EA9" t="n">
         <v>0.0004150350141639595</v>
@@ -5222,10 +5222,10 @@
         <v>0.005958819351875369</v>
       </c>
       <c r="ED9" t="n">
-        <v>9.643944624101786e-06</v>
+        <v>9.643944624101778e-06</v>
       </c>
       <c r="EE9" t="n">
-        <v>7.360234912432838e-05</v>
+        <v>7.36023491243284e-05</v>
       </c>
       <c r="EF9" t="n">
         <v>3.842423521804625e-06</v>
@@ -5240,7 +5240,7 @@
         <v>2.587103487495073e-05</v>
       </c>
       <c r="EJ9" t="n">
-        <v>3.346903254062491e-05</v>
+        <v>3.346903254062493e-05</v>
       </c>
       <c r="EK9" t="n">
         <v>1.223260742146816</v>
@@ -5334,10 +5334,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4224183149283154</v>
+        <v>0.4224183149283155</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0009731771207667348</v>
+        <v>0.0009731771207667356</v>
       </c>
       <c r="D10" t="n">
         <v>0.0008181621756732727</v>
@@ -5346,10 +5346,10 @@
         <v>0.0125445729801706</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2424259790045787</v>
+        <v>0.242425979004579</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5583310924903381</v>
+        <v>0.558331092490337</v>
       </c>
       <c r="H10" t="n">
         <v>0.2668216473034422</v>
@@ -5364,10 +5364,10 @@
         <v>0.1108189839690889</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03610005043046514</v>
+        <v>0.03610005043046509</v>
       </c>
       <c r="M10" t="n">
-        <v>0.006098691506406943</v>
+        <v>0.006098691506406944</v>
       </c>
       <c r="N10" t="n">
         <v>0.02146263184778546</v>
@@ -5379,13 +5379,13 @@
         <v>0.005843396852143966</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.007265777880520762</v>
+        <v>0.007265777880520761</v>
       </c>
       <c r="R10" t="n">
-        <v>0.007313670063244736</v>
+        <v>0.00731367006324473</v>
       </c>
       <c r="S10" t="n">
-        <v>0.00515278328017468</v>
+        <v>0.005152783280174681</v>
       </c>
       <c r="T10" t="n">
         <v>0.01477913247216642</v>
@@ -5397,7 +5397,7 @@
         <v>0.001883565828390125</v>
       </c>
       <c r="W10" t="n">
-        <v>0.05245883400314946</v>
+        <v>0.05245883400314948</v>
       </c>
       <c r="X10" t="n">
         <v>0.0003696715529890334</v>
@@ -5406,7 +5406,7 @@
         <v>0.003936618385454477</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.003927550294526612</v>
+        <v>0.003927550294526613</v>
       </c>
       <c r="AA10" t="n">
         <v>0.02331116474217443</v>
@@ -5415,7 +5415,7 @@
         <v>0.000880553244149592</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.03528452238758959</v>
+        <v>0.0352845223875896</v>
       </c>
       <c r="AD10" t="n">
         <v>4.527773046452795e-05</v>
@@ -5451,7 +5451,7 @@
         <v>0.0003062675937544332</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.0006193077142924304</v>
+        <v>0.00061930771429243</v>
       </c>
       <c r="AP10" t="n">
         <v>0.0005079866712448635</v>
@@ -5469,13 +5469,13 @@
         <v>8.850361794302431e-05</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.0003418303309742503</v>
+        <v>0.0003418303309742502</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.004250953948004395</v>
+        <v>0.004250953948004394</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.003636454412703789</v>
+        <v>0.003636454412703787</v>
       </c>
       <c r="AX10" t="n">
         <v>0.0002690710198120019</v>
@@ -5496,16 +5496,16 @@
         <v>0.009626261157134294</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.03246017506296604</v>
+        <v>0.03246017506296602</v>
       </c>
       <c r="BE10" t="n">
         <v>0.0005062653919237684</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.0008451935192772085</v>
+        <v>0.0008451935192772079</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.001105847097102291</v>
+        <v>0.00110584709710229</v>
       </c>
       <c r="BH10" t="n">
         <v>0.02053384157675798</v>
@@ -5517,10 +5517,10 @@
         <v>1.390907258648706e-05</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.01775081311500679</v>
+        <v>0.0177508131150068</v>
       </c>
       <c r="BL10" t="n">
-        <v>7.525438999177854e-05</v>
+        <v>7.525438999177853e-05</v>
       </c>
       <c r="BM10" t="n">
         <v>0.02811287951840209</v>
@@ -5529,7 +5529,7 @@
         <v>0.001749536479925363</v>
       </c>
       <c r="BO10" t="n">
-        <v>6.85941196277827e-05</v>
+        <v>6.859411962778271e-05</v>
       </c>
       <c r="BP10" t="n">
         <v>0.0003012526461364932</v>
@@ -5547,10 +5547,10 @@
         <v>0.005754444108481574</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.004031524492878666</v>
+        <v>0.004031524492878664</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.003494756723867278</v>
+        <v>0.003494756723867277</v>
       </c>
       <c r="BW10" t="n">
         <v>9.565092530312235e-06</v>
@@ -5571,7 +5571,7 @@
         <v>0.0003194197344847168</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.0001197999713527573</v>
+        <v>0.0001197999713527574</v>
       </c>
       <c r="CD10" t="n">
         <v>0.000187088570063471</v>
@@ -5580,13 +5580,13 @@
         <v>0.007148207512631613</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.001184034169540991</v>
+        <v>0.001184034169540992</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.00476733358663861</v>
+        <v>0.004767333586638608</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.0004804863598406773</v>
+        <v>0.0004804863598406772</v>
       </c>
       <c r="CI10" t="n">
         <v>0.0001344048853553475</v>
@@ -5601,7 +5601,7 @@
         <v>0.0004718884182203335</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.583608757101104e-05</v>
+        <v>2.583608757101105e-05</v>
       </c>
       <c r="CN10" t="n">
         <v>0.0002296812786545581</v>
@@ -5622,7 +5622,7 @@
         <v>8.505491759945778e-05</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.0002025330533468305</v>
+        <v>0.0002025330533468306</v>
       </c>
       <c r="CU10" t="n">
         <v>0.0001117937682366517</v>
@@ -5631,7 +5631,7 @@
         <v>0.0003754577264816678</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.0005011393458739696</v>
+        <v>0.0005011393458739697</v>
       </c>
       <c r="CX10" t="n">
         <v>0.004118925798625317</v>
@@ -5652,7 +5652,7 @@
         <v>0.0001171456798137446</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.00148652084207987</v>
+        <v>0.001486520842079869</v>
       </c>
       <c r="DE10" t="n">
         <v>8.999166901350645e-06</v>
@@ -5664,7 +5664,7 @@
         <v>0.006207471292888288</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.0004798137727617031</v>
+        <v>0.000479813772761703</v>
       </c>
       <c r="DI10" t="n">
         <v>8.508608771697038e-05</v>
@@ -5673,7 +5673,7 @@
         <v>5.874514354711446e-05</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.001132270706881733</v>
+        <v>0.001132270706881734</v>
       </c>
       <c r="DL10" t="n">
         <v>0.0002979893456883849</v>
@@ -5682,10 +5682,10 @@
         <v>0.0002095913366250654</v>
       </c>
       <c r="DN10" t="n">
-        <v>3.271250636896176e-05</v>
+        <v>3.271250636896177e-05</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.001136243286093227</v>
+        <v>0.001136243286093226</v>
       </c>
       <c r="DP10" t="n">
         <v>0.08525067786572045</v>
@@ -5697,19 +5697,19 @@
         <v>9.6896916094861e-05</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.003380988911157814</v>
+        <v>0.003380988911157813</v>
       </c>
       <c r="DT10" t="n">
         <v>0.001691869639363836</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.003890576237390471</v>
+        <v>0.003890576237390472</v>
       </c>
       <c r="DV10" t="n">
         <v>8.564667677345881e-05</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.0003878465813253055</v>
+        <v>0.0003878465813253056</v>
       </c>
       <c r="DX10" t="n">
         <v>0.0007773268213553178</v>
@@ -5727,7 +5727,7 @@
         <v>0.000261828937378869</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.005681897934782786</v>
+        <v>0.005681897934782785</v>
       </c>
       <c r="ED10" t="n">
         <v>7.725339143622216e-06</v>
@@ -5748,7 +5748,7 @@
         <v>2.794455247663429e-05</v>
       </c>
       <c r="EJ10" t="n">
-        <v>3.627131720215832e-05</v>
+        <v>3.627131720215831e-05</v>
       </c>
       <c r="EK10" t="n">
         <v>1.239796368527286</v>
@@ -5842,28 +5842,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3927613042226928</v>
+        <v>0.3927613042226931</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0009001040096423594</v>
+        <v>0.0009001040096423587</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0008305757230112741</v>
+        <v>0.0008305757230112748</v>
       </c>
       <c r="E11" t="n">
         <v>0.01313612873128284</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2168672546525011</v>
+        <v>0.2168672546525009</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5621063130926707</v>
+        <v>0.5621063130926708</v>
       </c>
       <c r="H11" t="n">
         <v>0.2271299957274628</v>
       </c>
       <c r="I11" t="n">
-        <v>0.06304588114846742</v>
+        <v>0.0630458811484674</v>
       </c>
       <c r="J11" t="n">
         <v>0.03050113451124808</v>
@@ -5872,19 +5872,19 @@
         <v>0.08428064805080884</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03615107707992394</v>
+        <v>0.03615107707992395</v>
       </c>
       <c r="M11" t="n">
         <v>0.006119210245762084</v>
       </c>
       <c r="N11" t="n">
-        <v>0.02070635970999601</v>
+        <v>0.020706359709996</v>
       </c>
       <c r="O11" t="n">
-        <v>0.004174605431637815</v>
+        <v>0.004174605431637816</v>
       </c>
       <c r="P11" t="n">
-        <v>0.006219206048390012</v>
+        <v>0.00621920604839001</v>
       </c>
       <c r="Q11" t="n">
         <v>0.008609782022464625</v>
@@ -5896,13 +5896,13 @@
         <v>0.005285492137918932</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01571429964967858</v>
+        <v>0.01571429964967857</v>
       </c>
       <c r="U11" t="n">
         <v>3.191156495598179e-05</v>
       </c>
       <c r="V11" t="n">
-        <v>0.001915841828425006</v>
+        <v>0.001915841828425005</v>
       </c>
       <c r="W11" t="n">
         <v>0.04213679849349709</v>
@@ -5914,28 +5914,28 @@
         <v>0.00401253850174765</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.004022306898270746</v>
+        <v>0.004022306898270747</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.02799554354653958</v>
+        <v>0.0279955435465396</v>
       </c>
       <c r="AB11" t="n">
         <v>0.0008599745103255551</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.03443275662752716</v>
+        <v>0.03443275662752714</v>
       </c>
       <c r="AD11" t="n">
         <v>4.457734340344005e-05</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.325747948049828e-05</v>
+        <v>1.325747948049829e-05</v>
       </c>
       <c r="AF11" t="n">
         <v>0.05760200694387686</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.02849765431307863</v>
+        <v>0.02849765431307862</v>
       </c>
       <c r="AH11" t="n">
         <v>0.002064999519383479</v>
@@ -5944,7 +5944,7 @@
         <v>0.001330297068098717</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.002877478242600886</v>
+        <v>0.002877478242600884</v>
       </c>
       <c r="AK11" t="n">
         <v>0.0197396477769612</v>
@@ -5959,13 +5959,13 @@
         <v>0.00032384043371095</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.0007277565025931618</v>
+        <v>0.0007277565025931612</v>
       </c>
       <c r="AP11" t="n">
         <v>0.0006170387923389534</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.001570538545976575</v>
+        <v>0.001570538545976574</v>
       </c>
       <c r="AR11" t="n">
         <v>0.007605122230494715</v>
@@ -5977,16 +5977,16 @@
         <v>8.208110753530205e-05</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.0003995464359297443</v>
+        <v>0.0003995464359297444</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.003859721402552268</v>
+        <v>0.003859721402552269</v>
       </c>
       <c r="AW11" t="n">
         <v>0.003987252068719941</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.000299455223086401</v>
+        <v>0.0002994552230864008</v>
       </c>
       <c r="AY11" t="n">
         <v>0.03680807347342493</v>
@@ -5995,10 +5995,10 @@
         <v>0.0008122347629909497</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.755652427636998e-05</v>
+        <v>9.75565242763699e-05</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.03641294508856617</v>
+        <v>0.03641294508856616</v>
       </c>
       <c r="BC11" t="n">
         <v>0.008740826116006363</v>
@@ -6019,13 +6019,13 @@
         <v>0.01989926728436671</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.0005153012396921023</v>
+        <v>0.0005153012396921024</v>
       </c>
       <c r="BJ11" t="n">
         <v>0.0001509650074374186</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.01369892831667569</v>
+        <v>0.01369892831667568</v>
       </c>
       <c r="BL11" t="n">
         <v>8.280298130543375e-05</v>
@@ -6043,7 +6043,7 @@
         <v>0.0002834036871648271</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.0004762631390579144</v>
+        <v>0.0004762631390579143</v>
       </c>
       <c r="BR11" t="n">
         <v>0.0001912408626727468</v>
@@ -6055,7 +6055,7 @@
         <v>0.006102111442644785</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.004013259743547977</v>
+        <v>0.004013259743547978</v>
       </c>
       <c r="BV11" t="n">
         <v>0.003548447570473684</v>
@@ -6064,7 +6064,7 @@
         <v>1.129186916551695e-05</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.002555541814966951</v>
+        <v>0.00255554181496695</v>
       </c>
       <c r="BY11" t="n">
         <v>0.0001071546841740086</v>
@@ -6079,10 +6079,10 @@
         <v>0.0003208402555335389</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.0001155254250924168</v>
+        <v>0.0001155254250924167</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.0002536014918296583</v>
+        <v>0.0002536014918296584</v>
       </c>
       <c r="CE11" t="n">
         <v>0.007963372675573427</v>
@@ -6100,19 +6100,19 @@
         <v>0.0001211388013362684</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.008195279573858389</v>
+        <v>0.008195279573858382</v>
       </c>
       <c r="CK11" t="n">
         <v>9.34041368332001e-06</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.0004597715940457977</v>
+        <v>0.0004597715940457976</v>
       </c>
       <c r="CM11" t="n">
         <v>2.971656928120091e-05</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.0002501096042022539</v>
+        <v>0.0002501096042022537</v>
       </c>
       <c r="CO11" t="n">
         <v>0.001252013336108305</v>
@@ -6130,7 +6130,7 @@
         <v>0.0001044221102583587</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.0002238461755984771</v>
+        <v>0.000223846175598477</v>
       </c>
       <c r="CU11" t="n">
         <v>0.0001153784751674855</v>
@@ -6139,7 +6139,7 @@
         <v>0.0003798559105146192</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.0004799794891722265</v>
+        <v>0.0004799794891722266</v>
       </c>
       <c r="CX11" t="n">
         <v>0.003965858793580521</v>
@@ -6154,13 +6154,13 @@
         <v>0.0002863402837606557</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.0004895380513683733</v>
+        <v>0.0004895380513683734</v>
       </c>
       <c r="DC11" t="n">
         <v>9.620238397662191e-05</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.00143783665558865</v>
+        <v>0.001437836655588649</v>
       </c>
       <c r="DE11" t="n">
         <v>9.59667047045813e-06</v>
@@ -6196,7 +6196,7 @@
         <v>0.001171078146748624</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.1070592906061596</v>
+        <v>0.1070592906061595</v>
       </c>
       <c r="DQ11" t="n">
         <v>7.684925633990661e-06</v>
@@ -6211,7 +6211,7 @@
         <v>0.001563637756484061</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.003798184652619326</v>
+        <v>0.003798184652619325</v>
       </c>
       <c r="DV11" t="n">
         <v>9.245782750407802e-05</v>
@@ -6235,7 +6235,7 @@
         <v>0.0002733419312668523</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.006487760531014645</v>
+        <v>0.006487760531014647</v>
       </c>
       <c r="ED11" t="n">
         <v>1.026978227562515e-05</v>
@@ -6253,7 +6253,7 @@
         <v>4.019069890351101e-05</v>
       </c>
       <c r="EI11" t="n">
-        <v>2.787982865855127e-05</v>
+        <v>2.787982865855126e-05</v>
       </c>
       <c r="EJ11" t="n">
         <v>3.534730802663559e-05</v>
@@ -6350,28 +6350,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.3997486739716912</v>
+        <v>0.3997486739716909</v>
       </c>
       <c r="C12" t="n">
         <v>0.0009033436859297453</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0008795061911787017</v>
+        <v>0.000879506191178701</v>
       </c>
       <c r="E12" t="n">
         <v>0.01338985403059623</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2244592979384058</v>
+        <v>0.224459297938406</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5587847287484471</v>
+        <v>0.5587847287484478</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2366756784218132</v>
+        <v>0.2366756784218133</v>
       </c>
       <c r="I12" t="n">
-        <v>0.06437983001709734</v>
+        <v>0.06437983001709732</v>
       </c>
       <c r="J12" t="n">
         <v>0.02944351516413556</v>
@@ -6380,7 +6380,7 @@
         <v>0.08995119039757772</v>
       </c>
       <c r="L12" t="n">
-        <v>0.03448166045904138</v>
+        <v>0.03448166045904137</v>
       </c>
       <c r="M12" t="n">
         <v>0.005467910157767718</v>
@@ -6389,22 +6389,22 @@
         <v>0.02010098911995819</v>
       </c>
       <c r="O12" t="n">
-        <v>0.003947184133550462</v>
+        <v>0.003947184133550461</v>
       </c>
       <c r="P12" t="n">
-        <v>0.006140956599595907</v>
+        <v>0.006140956599595909</v>
       </c>
       <c r="Q12" t="n">
         <v>0.007863725633610657</v>
       </c>
       <c r="R12" t="n">
-        <v>0.006988193368375383</v>
+        <v>0.006988193368375384</v>
       </c>
       <c r="S12" t="n">
         <v>0.005220563071132268</v>
       </c>
       <c r="T12" t="n">
-        <v>0.01618095493951033</v>
+        <v>0.01618095493951034</v>
       </c>
       <c r="U12" t="n">
         <v>3.415047346663751e-05</v>
@@ -6413,19 +6413,19 @@
         <v>0.001898374748548179</v>
       </c>
       <c r="W12" t="n">
-        <v>0.04745493410170752</v>
+        <v>0.04745493410170753</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0004058413406473972</v>
+        <v>0.0004058413406473971</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.004015078534447647</v>
+        <v>0.004015078534447646</v>
       </c>
       <c r="Z12" t="n">
         <v>0.003835943853716995</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.02751956947394898</v>
+        <v>0.02751956947394897</v>
       </c>
       <c r="AB12" t="n">
         <v>0.0009017637555758249</v>
@@ -6437,10 +6437,10 @@
         <v>5.129036994829747e-05</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.332304912318154e-05</v>
+        <v>1.332304912318153e-05</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.05977984331822755</v>
+        <v>0.05977984331822753</v>
       </c>
       <c r="AG12" t="n">
         <v>0.03035020629215674</v>
@@ -6464,13 +6464,13 @@
         <v>0.0003935483532908249</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.0003083494450859051</v>
+        <v>0.000308349445085905</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.0006290918541944786</v>
+        <v>0.0006290918541944785</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.0005090088078499097</v>
+        <v>0.0005090088078499096</v>
       </c>
       <c r="AQ12" t="n">
         <v>0.001537502041263434</v>
@@ -6485,10 +6485,10 @@
         <v>8.176846637502431e-05</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.0003953813216756067</v>
+        <v>0.0003953813216756066</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.003968232090307461</v>
+        <v>0.003968232090307462</v>
       </c>
       <c r="AW12" t="n">
         <v>0.003664251799648766</v>
@@ -6497,28 +6497,28 @@
         <v>0.0003047866443877397</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.03611871606269333</v>
+        <v>0.0361187160626933</v>
       </c>
       <c r="AZ12" t="n">
         <v>0.0008117901024291548</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.967358397406388e-05</v>
+        <v>9.967358397406383e-05</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.03813886188839966</v>
+        <v>0.03813886188839967</v>
       </c>
       <c r="BC12" t="n">
         <v>0.008957913426307779</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.03347918221537487</v>
+        <v>0.03347918221537485</v>
       </c>
       <c r="BE12" t="n">
         <v>0.0005347441704871735</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.0008449117668520585</v>
+        <v>0.0008449117668520592</v>
       </c>
       <c r="BG12" t="n">
         <v>0.001174644739498</v>
@@ -6527,13 +6527,13 @@
         <v>0.01968156157277993</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.000510181000058703</v>
+        <v>0.0005101810000587029</v>
       </c>
       <c r="BJ12" t="n">
         <v>0.0001446075906485954</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.01455330497681617</v>
+        <v>0.01455330497681615</v>
       </c>
       <c r="BL12" t="n">
         <v>8.362561340918776e-05</v>
@@ -6545,13 +6545,13 @@
         <v>0.001706782475754271</v>
       </c>
       <c r="BO12" t="n">
-        <v>5.882040609289754e-05</v>
+        <v>5.882040609289753e-05</v>
       </c>
       <c r="BP12" t="n">
         <v>0.0002883122975055694</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.0004862548341672527</v>
+        <v>0.0004862548341672526</v>
       </c>
       <c r="BR12" t="n">
         <v>0.0001715573896471926</v>
@@ -6560,7 +6560,7 @@
         <v>0.02610345237148766</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.005673609264695538</v>
+        <v>0.005673609264695536</v>
       </c>
       <c r="BU12" t="n">
         <v>0.003997431894849598</v>
@@ -6620,7 +6620,7 @@
         <v>2.943958849561442e-05</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.0002564919588333966</v>
+        <v>0.0002564919588333965</v>
       </c>
       <c r="CO12" t="n">
         <v>0.001238610473057252</v>
@@ -6686,7 +6686,7 @@
         <v>8.823100194475419e-05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>6.358365978610061e-05</v>
+        <v>6.35836597861006e-05</v>
       </c>
       <c r="DK12" t="n">
         <v>0.001249280585944312</v>
@@ -6701,7 +6701,7 @@
         <v>3.783204201062425e-05</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.001102456084272922</v>
+        <v>0.001102456084272921</v>
       </c>
       <c r="DP12" t="n">
         <v>0.1062430045909735</v>
@@ -6710,13 +6710,13 @@
         <v>7.526692992133471e-06</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.144068699965362e-05</v>
+        <v>8.144068699965356e-05</v>
       </c>
       <c r="DS12" t="n">
         <v>0.003220020524857663</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.001684303557023464</v>
+        <v>0.001684303557023463</v>
       </c>
       <c r="DU12" t="n">
         <v>0.003513568585081964</v>
@@ -6731,19 +6731,19 @@
         <v>0.0006968148020709399</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.0002545918432439873</v>
+        <v>0.0002545918432439872</v>
       </c>
       <c r="DZ12" t="n">
         <v>0.0001922150708347241</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.0004551043571077095</v>
+        <v>0.0004551043571077096</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.0002667653291226905</v>
+        <v>0.0002667653291226906</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.00696434831213428</v>
+        <v>0.006964348312134277</v>
       </c>
       <c r="ED12" t="n">
         <v>1.012929721638498e-05</v>
@@ -6858,7 +6858,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.4029575683656931</v>
+        <v>0.4029575683656929</v>
       </c>
       <c r="C13" t="n">
         <v>0.0009911258553004885</v>
@@ -6870,16 +6870,16 @@
         <v>0.0129995658995503</v>
       </c>
       <c r="F13" t="n">
-        <v>0.223828644536024</v>
+        <v>0.2238286445360239</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5466021605261879</v>
+        <v>0.5466021605261885</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2295755366449047</v>
+        <v>0.2295755366449045</v>
       </c>
       <c r="I13" t="n">
-        <v>0.05498120950354823</v>
+        <v>0.05498120950354822</v>
       </c>
       <c r="J13" t="n">
         <v>0.03227010782656917</v>
@@ -6888,7 +6888,7 @@
         <v>0.07682420209201914</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03661659824761725</v>
+        <v>0.03661659824761723</v>
       </c>
       <c r="M13" t="n">
         <v>0.006257835575850979</v>
@@ -6897,16 +6897,16 @@
         <v>0.0217504750601525</v>
       </c>
       <c r="O13" t="n">
-        <v>0.004359834280795159</v>
+        <v>0.00435983428079516</v>
       </c>
       <c r="P13" t="n">
-        <v>0.006429049964392364</v>
+        <v>0.006429049964392365</v>
       </c>
       <c r="Q13" t="n">
         <v>0.008751836352522835</v>
       </c>
       <c r="R13" t="n">
-        <v>0.007199549184384033</v>
+        <v>0.007199549184384025</v>
       </c>
       <c r="S13" t="n">
         <v>0.005439338367947628</v>
@@ -6927,19 +6927,19 @@
         <v>0.0003764771683347946</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.004009560400312626</v>
+        <v>0.004009560400312625</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.004016066603758059</v>
+        <v>0.004016066603758058</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.02772928275970316</v>
+        <v>0.02772928275970313</v>
       </c>
       <c r="AB13" t="n">
         <v>0.0008921494294329666</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.03547677419884859</v>
+        <v>0.03547677419884858</v>
       </c>
       <c r="AD13" t="n">
         <v>4.804965714772897e-05</v>
@@ -6951,7 +6951,7 @@
         <v>0.05554456905223483</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.03562610501758674</v>
+        <v>0.03562610501758676</v>
       </c>
       <c r="AH13" t="n">
         <v>0.00201781924455335</v>
@@ -6966,34 +6966,34 @@
         <v>0.01942134328175589</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.0009521130620154356</v>
+        <v>0.0009521130620154349</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.0004155055647836903</v>
+        <v>0.0004155055647836905</v>
       </c>
       <c r="AN13" t="n">
         <v>0.0003173638682255038</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.0006205032545987697</v>
+        <v>0.0006205032545987698</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.0005454588007786162</v>
+        <v>0.0005454588007786163</v>
       </c>
       <c r="AQ13" t="n">
         <v>0.001590203900170766</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.007496525398550173</v>
+        <v>0.007496525398550181</v>
       </c>
       <c r="AS13" t="n">
         <v>0.000158995723185645</v>
       </c>
       <c r="AT13" t="n">
-        <v>8.976213411041994e-05</v>
+        <v>8.976213411042001e-05</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.0004219891390979902</v>
+        <v>0.0004219891390979903</v>
       </c>
       <c r="AV13" t="n">
         <v>0.003971715983529561</v>
@@ -7002,22 +7002,22 @@
         <v>0.004119756903385117</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.0002919804776659674</v>
+        <v>0.0002919804776659676</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.03357265576084898</v>
+        <v>0.03357265576084897</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.0008646884872261088</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.0001041830490403049</v>
+        <v>0.000104183049040305</v>
       </c>
       <c r="BB13" t="n">
         <v>0.03938491367778248</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.008791296142347235</v>
+        <v>0.008791296142347227</v>
       </c>
       <c r="BD13" t="n">
         <v>0.03554540556336339</v>
@@ -7032,7 +7032,7 @@
         <v>0.001127055979273568</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.02156003172107031</v>
+        <v>0.02156003172107032</v>
       </c>
       <c r="BI13" t="n">
         <v>0.000522527477268284</v>
@@ -7041,10 +7041,10 @@
         <v>0.0002012482023852344</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.01634725120525401</v>
+        <v>0.01634725120525402</v>
       </c>
       <c r="BL13" t="n">
-        <v>8.584282646736607e-05</v>
+        <v>8.584282646736615e-05</v>
       </c>
       <c r="BM13" t="n">
         <v>0.02833907640184907</v>
@@ -7056,7 +7056,7 @@
         <v>6.63973715650966e-05</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.0002943586909629766</v>
+        <v>0.0002943586909629767</v>
       </c>
       <c r="BQ13" t="n">
         <v>0.0004847617474476743</v>
@@ -7068,7 +7068,7 @@
         <v>0.0293308497852251</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.00559185346242362</v>
+        <v>0.005591853462423618</v>
       </c>
       <c r="BU13" t="n">
         <v>0.00399845249137139</v>
@@ -7080,7 +7080,7 @@
         <v>1.026281367244737e-05</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.002540010990654137</v>
+        <v>0.002540010990654136</v>
       </c>
       <c r="BY13" t="n">
         <v>0.0001043245587279266</v>
@@ -7095,7 +7095,7 @@
         <v>0.0003203667917502421</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.0001286327593754401</v>
+        <v>0.0001286327593754402</v>
       </c>
       <c r="CD13" t="n">
         <v>0.0002217984292593931</v>
@@ -7110,7 +7110,7 @@
         <v>0.004935002338835611</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.0005213264688691278</v>
+        <v>0.0005213264688691279</v>
       </c>
       <c r="CI13" t="n">
         <v>7.177216637475714e-05</v>
@@ -7140,7 +7140,7 @@
         <v>0.001069743228782819</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.0006562119931608932</v>
+        <v>0.000656211993160893</v>
       </c>
       <c r="CS13" t="n">
         <v>0.0001014279990037085</v>
@@ -7155,7 +7155,7 @@
         <v>0.0004036414633258255</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.0004528579753936808</v>
+        <v>0.0004528579753936809</v>
       </c>
       <c r="CX13" t="n">
         <v>0.003835936569741179</v>
@@ -7185,16 +7185,16 @@
         <v>0.0004788199554279932</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.005899227841421145</v>
+        <v>0.005899227841421142</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.0004910635443756276</v>
+        <v>0.0004910635443756277</v>
       </c>
       <c r="DI13" t="n">
         <v>9.800187308532359e-05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>5.044017312783787e-05</v>
+        <v>5.044017312783786e-05</v>
       </c>
       <c r="DK13" t="n">
         <v>0.001183688102568919</v>
@@ -7209,7 +7209,7 @@
         <v>3.965970970984978e-05</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.001218568931624896</v>
+        <v>0.001218568931624897</v>
       </c>
       <c r="DP13" t="n">
         <v>0.09801641926546897</v>
@@ -7218,10 +7218,10 @@
         <v>7.802759505435844e-06</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.0001010017483153961</v>
+        <v>0.0001010017483153962</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.003505517034114726</v>
+        <v>0.003505517034114728</v>
       </c>
       <c r="DT13" t="n">
         <v>0.001673859394140202</v>
@@ -7239,7 +7239,7 @@
         <v>0.0007388361720716767</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.0002595730256028297</v>
+        <v>0.0002595730256028298</v>
       </c>
       <c r="DZ13" t="n">
         <v>0.00020223125588746</v>
@@ -7378,7 +7378,7 @@
         <v>0.01195299673536621</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2105056703590827</v>
+        <v>0.2105056703590826</v>
       </c>
       <c r="G14" t="n">
         <v>0.5846018177044652</v>
@@ -7396,7 +7396,7 @@
         <v>0.0922941339980769</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0297605043280114</v>
+        <v>0.02976050432801141</v>
       </c>
       <c r="M14" t="n">
         <v>0.004351712635042238</v>
@@ -7414,7 +7414,7 @@
         <v>0.004722456529650835</v>
       </c>
       <c r="R14" t="n">
-        <v>0.006178693260952189</v>
+        <v>0.006178693260952193</v>
       </c>
       <c r="S14" t="n">
         <v>0.004280649971192278</v>
@@ -7426,7 +7426,7 @@
         <v>2.745801347682813e-05</v>
       </c>
       <c r="V14" t="n">
-        <v>0.00155096338813997</v>
+        <v>0.001550963388139971</v>
       </c>
       <c r="W14" t="n">
         <v>0.04649610747190033</v>
@@ -7441,13 +7441,13 @@
         <v>0.003030284907741911</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.03345846546275212</v>
+        <v>0.03345846546275213</v>
       </c>
       <c r="AB14" t="n">
         <v>0.0007759001059731127</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.02724957836995043</v>
+        <v>0.02724957836995044</v>
       </c>
       <c r="AD14" t="n">
         <v>4.231279918826416e-05</v>
@@ -7456,10 +7456,10 @@
         <v>1.033670711016709e-05</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.06295297975981885</v>
+        <v>0.06295297975981889</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.0281593081310111</v>
+        <v>0.02815930813101109</v>
       </c>
       <c r="AH14" t="n">
         <v>0.001947482294071053</v>
@@ -7471,7 +7471,7 @@
         <v>0.002565134843833156</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.01556563952171849</v>
+        <v>0.0155656395217185</v>
       </c>
       <c r="AL14" t="n">
         <v>0.0007526310919049107</v>
@@ -7489,7 +7489,7 @@
         <v>0.0003755585825982744</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.001447848844312975</v>
+        <v>0.001447848844312974</v>
       </c>
       <c r="AR14" t="n">
         <v>0.007090229515782497</v>
@@ -7507,34 +7507,34 @@
         <v>0.003614099665546478</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.003430888200001615</v>
+        <v>0.003430888200001616</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.0002971737447005021</v>
+        <v>0.0002971737447005022</v>
       </c>
       <c r="AY14" t="n">
         <v>0.04607048755427436</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.0006995317754527709</v>
+        <v>0.0006995317754527706</v>
       </c>
       <c r="BA14" t="n">
         <v>7.519871835081359e-05</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.0470618432799363</v>
+        <v>0.04706184327993634</v>
       </c>
       <c r="BC14" t="n">
         <v>0.007463279767988679</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.02919181432732507</v>
+        <v>0.02919181432732508</v>
       </c>
       <c r="BE14" t="n">
         <v>0.0004445582881644009</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.0006965227743040091</v>
+        <v>0.0006965227743040096</v>
       </c>
       <c r="BG14" t="n">
         <v>0.0009210921101643337</v>
@@ -7549,13 +7549,13 @@
         <v>6.916426329507535e-06</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.009325062347561235</v>
+        <v>0.009325062347561227</v>
       </c>
       <c r="BL14" t="n">
         <v>9.332807583133168e-05</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.02655723213902981</v>
+        <v>0.02655723213902982</v>
       </c>
       <c r="BN14" t="n">
         <v>0.001543112532667671</v>
@@ -7579,7 +7579,7 @@
         <v>0.00631908719916499</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.003059636365690173</v>
+        <v>0.003059636365690174</v>
       </c>
       <c r="BV14" t="n">
         <v>0.003436872104061444</v>
@@ -7615,7 +7615,7 @@
         <v>0.001513227631051634</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.003083050461299972</v>
+        <v>0.003083050461299973</v>
       </c>
       <c r="CH14" t="n">
         <v>0.0003855379705972497</v>
@@ -7690,7 +7690,7 @@
         <v>8.061391412552294e-06</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.0003938557404281361</v>
+        <v>0.0003938557404281357</v>
       </c>
       <c r="DG14" t="n">
         <v>0.004876090302189321</v>
@@ -7720,7 +7720,7 @@
         <v>0.0009275555313592261</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.1355465752808667</v>
+        <v>0.1355465752808668</v>
       </c>
       <c r="DQ14" t="n">
         <v>5.807179363487638e-06</v>
@@ -7735,7 +7735,7 @@
         <v>0.001344501663793321</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.002882667771097321</v>
+        <v>0.00288266777109732</v>
       </c>
       <c r="DV14" t="n">
         <v>8.611169094694585e-05</v>
@@ -7744,10 +7744,10 @@
         <v>0.0003850057104404745</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.0005644636656785762</v>
+        <v>0.0005644636656785766</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.0002291910798939039</v>
+        <v>0.0002291910798939038</v>
       </c>
       <c r="DZ14" t="n">
         <v>0.0001878243184327571</v>
@@ -7880,19 +7880,19 @@
         <v>0.0006769301927890275</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0007515450148729984</v>
+        <v>0.0007515450148729987</v>
       </c>
       <c r="E15" t="n">
         <v>0.01251693699455387</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2110347464309044</v>
+        <v>0.2110347464309047</v>
       </c>
       <c r="G15" t="n">
         <v>0.5819908750752426</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2295379752627645</v>
+        <v>0.2295379752627643</v>
       </c>
       <c r="I15" t="n">
         <v>0.06368476116144381</v>
@@ -7904,7 +7904,7 @@
         <v>0.09208671485886526</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03019627805468142</v>
+        <v>0.03019627805468139</v>
       </c>
       <c r="M15" t="n">
         <v>0.004026277802644333</v>
@@ -7916,19 +7916,19 @@
         <v>0.003928870594591798</v>
       </c>
       <c r="P15" t="n">
-        <v>0.004854955675197013</v>
+        <v>0.004854955675197017</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.006061649686325234</v>
+        <v>0.006061649686325238</v>
       </c>
       <c r="R15" t="n">
         <v>0.006222076046113688</v>
       </c>
       <c r="S15" t="n">
-        <v>0.004352289928152074</v>
+        <v>0.004352289928152078</v>
       </c>
       <c r="T15" t="n">
-        <v>0.01585275927729118</v>
+        <v>0.01585275927729119</v>
       </c>
       <c r="U15" t="n">
         <v>2.747479263017608e-05</v>
@@ -7943,7 +7943,7 @@
         <v>0.0003725669646492275</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.003622164216168038</v>
+        <v>0.00362216421616804</v>
       </c>
       <c r="Z15" t="n">
         <v>0.00293400925960779</v>
@@ -7955,7 +7955,7 @@
         <v>0.0007351061333116742</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.02762012487575338</v>
+        <v>0.0276201248757534</v>
       </c>
       <c r="AD15" t="n">
         <v>4.38334204413744e-05</v>
@@ -7967,7 +7967,7 @@
         <v>0.05967161516228275</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.02927278122445531</v>
+        <v>0.0292727812244553</v>
       </c>
       <c r="AH15" t="n">
         <v>0.00187000677569149</v>
@@ -7982,7 +7982,7 @@
         <v>0.01615932771095959</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.0007957244676842723</v>
+        <v>0.0007957244676842718</v>
       </c>
       <c r="AM15" t="n">
         <v>0.0003373008507095158</v>
@@ -7997,7 +7997,7 @@
         <v>0.0003987896570499901</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.001435717612104419</v>
+        <v>0.00143571761210442</v>
       </c>
       <c r="AR15" t="n">
         <v>0.007433254409609012</v>
@@ -8018,13 +8018,13 @@
         <v>0.004158442541142755</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.0003008556130213227</v>
+        <v>0.0003008556130213228</v>
       </c>
       <c r="AY15" t="n">
         <v>0.04587665502870054</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.0006984881929291482</v>
+        <v>0.0006984881929291485</v>
       </c>
       <c r="BA15" t="n">
         <v>8.07237950688219e-05</v>
@@ -8048,7 +8048,7 @@
         <v>0.0009797499173313465</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.01506785459261033</v>
+        <v>0.01506785459261034</v>
       </c>
       <c r="BI15" t="n">
         <v>0.0004403800931488896</v>
@@ -8066,13 +8066,13 @@
         <v>0.02676316527816209</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.001470240048366573</v>
+        <v>0.001470240048366572</v>
       </c>
       <c r="BO15" t="n">
         <v>4.663668000446173e-05</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.0002459305129433456</v>
+        <v>0.0002459305129433457</v>
       </c>
       <c r="BQ15" t="n">
         <v>0.0004906792905206947</v>
@@ -8090,7 +8090,7 @@
         <v>0.003272191200050852</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.003408138637985754</v>
+        <v>0.003408138637985755</v>
       </c>
       <c r="BW15" t="n">
         <v>6.291442630911805e-06</v>
@@ -8105,7 +8105,7 @@
         <v>0.004599006275810364</v>
       </c>
       <c r="CA15" t="n">
-        <v>9.980536536734841e-05</v>
+        <v>9.980536536734845e-05</v>
       </c>
       <c r="CB15" t="n">
         <v>0.0003215918056576125</v>
@@ -8120,7 +8120,7 @@
         <v>0.008436647723431433</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.001464901281796551</v>
+        <v>0.001464901281796552</v>
       </c>
       <c r="CG15" t="n">
         <v>0.002878440557859495</v>
@@ -8138,7 +8138,7 @@
         <v>9.072213996944829e-06</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.0003819229468996528</v>
+        <v>0.0003819229468996525</v>
       </c>
       <c r="CM15" t="n">
         <v>2.36763084507809e-05</v>
@@ -8180,7 +8180,7 @@
         <v>0.0001051140167921165</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.0002158337331433299</v>
+        <v>0.00021583373314333</v>
       </c>
       <c r="DA15" t="n">
         <v>0.0002549295218814002</v>
@@ -8198,7 +8198,7 @@
         <v>7.839394225268833e-06</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.0004317813060713909</v>
+        <v>0.0004317813060713912</v>
       </c>
       <c r="DG15" t="n">
         <v>0.004799503675923678</v>
@@ -8228,7 +8228,7 @@
         <v>0.00097493685741852</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.1346390487985742</v>
+        <v>0.1346390487985743</v>
       </c>
       <c r="DQ15" t="n">
         <v>5.04801871112189e-06</v>
@@ -8273,7 +8273,7 @@
         <v>6.953013573797032e-06</v>
       </c>
       <c r="EE15" t="n">
-        <v>8.843325095809088e-05</v>
+        <v>8.843325095809092e-05</v>
       </c>
       <c r="EF15" t="n">
         <v>2.528636188503109e-06</v>
@@ -8394,25 +8394,25 @@
         <v>0.01152061079266303</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2127694780042606</v>
+        <v>0.2127694780042603</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5904443920865803</v>
+        <v>0.5904443920865795</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2363497748289705</v>
+        <v>0.2363497748289706</v>
       </c>
       <c r="I16" t="n">
-        <v>0.07416612364991566</v>
+        <v>0.07416612364991571</v>
       </c>
       <c r="J16" t="n">
         <v>0.02424358493697039</v>
       </c>
       <c r="K16" t="n">
-        <v>0.09744389765855112</v>
+        <v>0.09744389765855113</v>
       </c>
       <c r="L16" t="n">
-        <v>0.03019499682207241</v>
+        <v>0.0301949968220724</v>
       </c>
       <c r="M16" t="n">
         <v>0.004379473002777735</v>
@@ -8433,10 +8433,10 @@
         <v>0.006222182609674423</v>
       </c>
       <c r="S16" t="n">
-        <v>0.004442398884272197</v>
+        <v>0.004442398884272193</v>
       </c>
       <c r="T16" t="n">
-        <v>0.01583746084156089</v>
+        <v>0.01583746084156087</v>
       </c>
       <c r="U16" t="n">
         <v>2.995293942142188e-05</v>
@@ -8457,13 +8457,13 @@
         <v>0.003151270616164604</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.03415193149873701</v>
+        <v>0.03415193149873699</v>
       </c>
       <c r="AB16" t="n">
         <v>0.0007439409127351945</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.02764663667531706</v>
+        <v>0.02764663667531705</v>
       </c>
       <c r="AD16" t="n">
         <v>3.865836164654035e-05</v>
@@ -8475,7 +8475,7 @@
         <v>0.06348683252896321</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.02657628991224793</v>
+        <v>0.02657628991224794</v>
       </c>
       <c r="AH16" t="n">
         <v>0.001796625002757096</v>
@@ -8496,7 +8496,7 @@
         <v>0.000341819294878001</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.0002952406702490838</v>
+        <v>0.0002952406702490839</v>
       </c>
       <c r="AO16" t="n">
         <v>0.0005156322371297279</v>
@@ -8532,16 +8532,16 @@
         <v>0.04765013814228587</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.0006409902506775121</v>
+        <v>0.0006409902506775118</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.720283711517966e-05</v>
+        <v>7.720283711517969e-05</v>
       </c>
       <c r="BB16" t="n">
         <v>0.0449431200457082</v>
       </c>
       <c r="BC16" t="n">
-        <v>0.007289456104182892</v>
+        <v>0.007289456104182888</v>
       </c>
       <c r="BD16" t="n">
         <v>0.02609169648087678</v>
@@ -8550,7 +8550,7 @@
         <v>0.000477921057088554</v>
       </c>
       <c r="BF16" t="n">
-        <v>0.0007424728586599112</v>
+        <v>0.0007424728586599115</v>
       </c>
       <c r="BG16" t="n">
         <v>0.0009463407274249001</v>
@@ -8568,10 +8568,10 @@
         <v>0.008325147604889659</v>
       </c>
       <c r="BL16" t="n">
-        <v>8.271855164940514e-05</v>
+        <v>8.27185516494052e-05</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.02385791986934216</v>
+        <v>0.02385791986934217</v>
       </c>
       <c r="BN16" t="n">
         <v>0.001575435492814617</v>
@@ -8589,7 +8589,7 @@
         <v>0.0001003335179018672</v>
       </c>
       <c r="BS16" t="n">
-        <v>0.01950772879508408</v>
+        <v>0.01950772879508409</v>
       </c>
       <c r="BT16" t="n">
         <v>0.005707164836676754</v>
@@ -8658,7 +8658,7 @@
         <v>0.0005476144445495923</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.000590924900313925</v>
+        <v>0.0005909249003139253</v>
       </c>
       <c r="CQ16" t="n">
         <v>0.0006230567426738979</v>
@@ -8673,7 +8673,7 @@
         <v>0.0002041728062131509</v>
       </c>
       <c r="CU16" t="n">
-        <v>0.000106927666878267</v>
+        <v>0.0001069276668782671</v>
       </c>
       <c r="CV16" t="n">
         <v>0.0003274659057504117</v>
@@ -8685,10 +8685,10 @@
         <v>0.00279219894633889</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.0001135633171057593</v>
+        <v>0.0001135633171057592</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.000213814215210132</v>
+        <v>0.0002138142152101319</v>
       </c>
       <c r="DA16" t="n">
         <v>0.0002357166992260036</v>
@@ -8709,7 +8709,7 @@
         <v>0.0003352321035562029</v>
       </c>
       <c r="DG16" t="n">
-        <v>0.004840394505408675</v>
+        <v>0.004840394505408672</v>
       </c>
       <c r="DH16" t="n">
         <v>0.0004541330741694497</v>
@@ -8727,7 +8727,7 @@
         <v>0.0002297292812005106</v>
       </c>
       <c r="DM16" t="n">
-        <v>0.000209133756394277</v>
+        <v>0.0002091337563942769</v>
       </c>
       <c r="DN16" t="n">
         <v>3.702142003373666e-05</v>
@@ -8757,7 +8757,7 @@
         <v>8.96823993884053e-05</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.0004420284609873082</v>
+        <v>0.0004420284609873087</v>
       </c>
       <c r="DX16" t="n">
         <v>0.0006042562446612362</v>
@@ -8790,10 +8790,10 @@
         <v>5.938930979330267e-05</v>
       </c>
       <c r="EH16" t="n">
-        <v>3.498908955599258e-05</v>
+        <v>3.498908955599257e-05</v>
       </c>
       <c r="EI16" t="n">
-        <v>2.73519475480262e-05</v>
+        <v>2.735194754802619e-05</v>
       </c>
       <c r="EJ16" t="n">
         <v>2.914089604983801e-05</v>
@@ -8890,7 +8890,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.3592142414100321</v>
+        <v>0.3592142414100329</v>
       </c>
       <c r="C17" t="n">
         <v>0.0005797234571972056</v>
@@ -8902,13 +8902,13 @@
         <v>0.01032920301830001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2148342306962203</v>
+        <v>0.2148342306962205</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6093015405986165</v>
+        <v>0.6093015405986162</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2434412493288412</v>
+        <v>0.2434412493288413</v>
       </c>
       <c r="I17" t="n">
         <v>0.07707292660978328</v>
@@ -8920,25 +8920,25 @@
         <v>0.1014235631803267</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02616500361033504</v>
+        <v>0.02616500361033506</v>
       </c>
       <c r="M17" t="n">
-        <v>0.002898387044709068</v>
+        <v>0.002898387044709071</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0126434414871194</v>
+        <v>0.01264344148711941</v>
       </c>
       <c r="O17" t="n">
         <v>0.00305907635596417</v>
       </c>
       <c r="P17" t="n">
-        <v>0.00436210476141869</v>
+        <v>0.004362104761418687</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.004671378986097246</v>
+        <v>0.004671378986097249</v>
       </c>
       <c r="R17" t="n">
-        <v>0.005722387961358265</v>
+        <v>0.005722387961358269</v>
       </c>
       <c r="S17" t="n">
         <v>0.004088979659470145</v>
@@ -8956,13 +8956,13 @@
         <v>0.04779620990327637</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0003199810516451335</v>
+        <v>0.0003199810516451339</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.003138312495932897</v>
+        <v>0.003138312495932894</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.002655807928927975</v>
+        <v>0.002655807928927973</v>
       </c>
       <c r="AA17" t="n">
         <v>0.03762579335559059</v>
@@ -8971,7 +8971,7 @@
         <v>0.0006412815292484092</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.0235267407597898</v>
+        <v>0.02352674075978979</v>
       </c>
       <c r="AD17" t="n">
         <v>4.343386356842002e-05</v>
@@ -8983,7 +8983,7 @@
         <v>0.06708997719205463</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.02375014221362074</v>
+        <v>0.02375014221362073</v>
       </c>
       <c r="AH17" t="n">
         <v>0.001904074238955246</v>
@@ -9016,7 +9016,7 @@
         <v>0.001210809985791676</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.006353666379225844</v>
+        <v>0.006353666379225841</v>
       </c>
       <c r="AS17" t="n">
         <v>0.0001363404171545517</v>
@@ -9037,7 +9037,7 @@
         <v>0.0002829044346950708</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.05359375051953088</v>
+        <v>0.05359375051953085</v>
       </c>
       <c r="AZ17" t="n">
         <v>0.000552082732991472</v>
@@ -9049,10 +9049,10 @@
         <v>0.04886657998433273</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.006804386168348159</v>
+        <v>0.006804386168348163</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.02214202986634855</v>
+        <v>0.02214202986634854</v>
       </c>
       <c r="BE17" t="n">
         <v>0.000383400056248179</v>
@@ -9073,7 +9073,7 @@
         <v>7.955291607649624e-05</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.008065754923530405</v>
+        <v>0.008065754923530401</v>
       </c>
       <c r="BL17" t="n">
         <v>7.891635247581617e-05</v>
@@ -9088,7 +9088,7 @@
         <v>3.790217554829133e-05</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.0002080555588645427</v>
+        <v>0.0002080555588645426</v>
       </c>
       <c r="BQ17" t="n">
         <v>0.0004929698411740952</v>
@@ -9100,13 +9100,13 @@
         <v>0.01681993792424363</v>
       </c>
       <c r="BT17" t="n">
-        <v>0.005939143501909484</v>
+        <v>0.005939143501909487</v>
       </c>
       <c r="BU17" t="n">
         <v>0.002702769091263287</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.003032612141934244</v>
+        <v>0.003032612141934242</v>
       </c>
       <c r="BW17" t="n">
         <v>5.050147252675561e-06</v>
@@ -9118,28 +9118,28 @@
         <v>0.000104682592842036</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.003408499243218248</v>
+        <v>0.003408499243218245</v>
       </c>
       <c r="CA17" t="n">
-        <v>8.635270826925171e-05</v>
+        <v>8.635270826925168e-05</v>
       </c>
       <c r="CB17" t="n">
         <v>0.0003294409049942673</v>
       </c>
       <c r="CC17" t="n">
-        <v>8.472291645198791e-05</v>
+        <v>8.472291645198798e-05</v>
       </c>
       <c r="CD17" t="n">
         <v>0.0001626668326362286</v>
       </c>
       <c r="CE17" t="n">
-        <v>0.006908618965249382</v>
+        <v>0.00690861896524938</v>
       </c>
       <c r="CF17" t="n">
-        <v>0.001249841231396708</v>
+        <v>0.001249841231396709</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.001971092077951117</v>
+        <v>0.001971092077951116</v>
       </c>
       <c r="CH17" t="n">
         <v>0.0003664682219733398</v>
@@ -9154,7 +9154,7 @@
         <v>8.381395480228596e-06</v>
       </c>
       <c r="CL17" t="n">
-        <v>0.0003453961352067599</v>
+        <v>0.0003453961352067602</v>
       </c>
       <c r="CM17" t="n">
         <v>2.16030551501902e-05</v>
@@ -9163,7 +9163,7 @@
         <v>0.0002209741481720769</v>
       </c>
       <c r="CO17" t="n">
-        <v>0.0009520600251581215</v>
+        <v>0.0009520600251581208</v>
       </c>
       <c r="CP17" t="n">
         <v>0.0005674705423025673</v>
@@ -9178,7 +9178,7 @@
         <v>8.866520999326356e-05</v>
       </c>
       <c r="CT17" t="n">
-        <v>0.0001845267536657609</v>
+        <v>0.0001845267536657608</v>
       </c>
       <c r="CU17" t="n">
         <v>9.918040746000986e-05</v>
@@ -9211,7 +9211,7 @@
         <v>0.001069807747485388</v>
       </c>
       <c r="DE17" t="n">
-        <v>6.873481766846091e-06</v>
+        <v>6.873481766846088e-06</v>
       </c>
       <c r="DF17" t="n">
         <v>0.0003679999278624259</v>
@@ -9226,7 +9226,7 @@
         <v>8.019102470218472e-05</v>
       </c>
       <c r="DJ17" t="n">
-        <v>5.451735285236106e-05</v>
+        <v>5.451735285236109e-05</v>
       </c>
       <c r="DK17" t="n">
         <v>0.001051630613939794</v>
@@ -9277,7 +9277,7 @@
         <v>0.0001753688878877511</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.0003620587947878514</v>
+        <v>0.0003620587947878517</v>
       </c>
       <c r="EB17" t="n">
         <v>0.0002096576720597361</v>
@@ -9289,13 +9289,13 @@
         <v>5.17398005304692e-06</v>
       </c>
       <c r="EE17" t="n">
-        <v>8.23224639372107e-05</v>
+        <v>8.232246393721071e-05</v>
       </c>
       <c r="EF17" t="n">
         <v>2.001559751650579e-06</v>
       </c>
       <c r="EG17" t="n">
-        <v>5.03538601898024e-05</v>
+        <v>5.035386018980238e-05</v>
       </c>
       <c r="EH17" t="n">
         <v>1.937457294514608e-05</v>
@@ -9404,19 +9404,19 @@
         <v>0.0005696592021732335</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0007697300571981607</v>
+        <v>0.0007697300571981612</v>
       </c>
       <c r="E18" t="n">
         <v>0.01020828125458456</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2217892661567526</v>
+        <v>0.2217892661567528</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6105417468267413</v>
+        <v>0.610541746826741</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2585679992503967</v>
+        <v>0.2585679992503969</v>
       </c>
       <c r="I18" t="n">
         <v>0.0810766574926836</v>
@@ -9428,7 +9428,7 @@
         <v>0.1179860134543248</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0268737032878702</v>
+        <v>0.02687370328787018</v>
       </c>
       <c r="M18" t="n">
         <v>0.002940163620158978</v>
@@ -9443,13 +9443,13 @@
         <v>0.004274422958892725</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.004481745631244778</v>
+        <v>0.004481745631244775</v>
       </c>
       <c r="R18" t="n">
-        <v>0.006512777118788152</v>
+        <v>0.006512777118788149</v>
       </c>
       <c r="S18" t="n">
-        <v>0.004019155835911671</v>
+        <v>0.004019155835911675</v>
       </c>
       <c r="T18" t="n">
         <v>0.01323227985844572</v>
@@ -9479,28 +9479,28 @@
         <v>0.0006198666288863056</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.02275738719670906</v>
+        <v>0.02275738719670907</v>
       </c>
       <c r="AD18" t="n">
         <v>2.7527559007701e-05</v>
       </c>
       <c r="AE18" t="n">
-        <v>8.00412023892052e-06</v>
+        <v>8.004120238920518e-06</v>
       </c>
       <c r="AF18" t="n">
         <v>0.06692209692445332</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.02280353246081933</v>
+        <v>0.02280353246081934</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.001856459899621282</v>
+        <v>0.001856459899621281</v>
       </c>
       <c r="AI18" t="n">
         <v>0.001174407523124253</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.002491523520162362</v>
+        <v>0.002491523520162363</v>
       </c>
       <c r="AK18" t="n">
         <v>0.01164600652073184</v>
@@ -9518,13 +9518,13 @@
         <v>0.000442374258158029</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.0003273634475817145</v>
+        <v>0.0003273634475817142</v>
       </c>
       <c r="AQ18" t="n">
         <v>0.00130025567812156</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.006760586455906059</v>
+        <v>0.006760586455906063</v>
       </c>
       <c r="AS18" t="n">
         <v>0.0001540966347736209</v>
@@ -9533,7 +9533,7 @@
         <v>4.363284252150871e-05</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.0002657731735858922</v>
+        <v>0.0002657731735858921</v>
       </c>
       <c r="AV18" t="n">
         <v>0.003935888420612569</v>
@@ -9545,10 +9545,10 @@
         <v>0.0002920348459138466</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.0552111968303122</v>
+        <v>0.05521119683031222</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.0005271878128941191</v>
+        <v>0.0005271878128941193</v>
       </c>
       <c r="BA18" t="n">
         <v>6.214241074019171e-05</v>
@@ -9557,7 +9557,7 @@
         <v>0.05022123900681674</v>
       </c>
       <c r="BC18" t="n">
-        <v>0.006784337228342121</v>
+        <v>0.006784337228342118</v>
       </c>
       <c r="BD18" t="n">
         <v>0.02323241079605995</v>
@@ -9569,10 +9569,10 @@
         <v>0.0006208978186005704</v>
       </c>
       <c r="BG18" t="n">
-        <v>0.0007142882419329292</v>
+        <v>0.0007142882419329288</v>
       </c>
       <c r="BH18" t="n">
-        <v>0.01410614445461149</v>
+        <v>0.01410614445461148</v>
       </c>
       <c r="BI18" t="n">
         <v>0.0004348511587189965</v>
@@ -9608,10 +9608,10 @@
         <v>0.01668610559968934</v>
       </c>
       <c r="BT18" t="n">
-        <v>0.004829788899865069</v>
+        <v>0.004829788899865072</v>
       </c>
       <c r="BU18" t="n">
-        <v>0.002561413536539373</v>
+        <v>0.002561413536539372</v>
       </c>
       <c r="BV18" t="n">
         <v>0.002735029861005963</v>
@@ -9629,13 +9629,13 @@
         <v>0.002334293038453719</v>
       </c>
       <c r="CA18" t="n">
-        <v>8.155429384044716e-05</v>
+        <v>8.155429384044714e-05</v>
       </c>
       <c r="CB18" t="n">
         <v>0.0003354746820972779</v>
       </c>
       <c r="CC18" t="n">
-        <v>7.806456318332051e-05</v>
+        <v>7.806456318332048e-05</v>
       </c>
       <c r="CD18" t="n">
         <v>0.0001504825622307543</v>
@@ -9668,7 +9668,7 @@
         <v>1.851754231460183e-05</v>
       </c>
       <c r="CN18" t="n">
-        <v>0.0001863843521935319</v>
+        <v>0.0001863843521935318</v>
       </c>
       <c r="CO18" t="n">
         <v>0.001522778292561195</v>
@@ -9686,7 +9686,7 @@
         <v>8.735176577761552e-05</v>
       </c>
       <c r="CT18" t="n">
-        <v>0.0001663489749297676</v>
+        <v>0.0001663489749297677</v>
       </c>
       <c r="CU18" t="n">
         <v>8.839561430257429e-05</v>
@@ -9716,7 +9716,7 @@
         <v>0.0001087398369159846</v>
       </c>
       <c r="DD18" t="n">
-        <v>0.0009220510069087657</v>
+        <v>0.000922051006908766</v>
       </c>
       <c r="DE18" t="n">
         <v>7.154360387530015e-06</v>
@@ -9725,7 +9725,7 @@
         <v>0.00045197793748535</v>
       </c>
       <c r="DG18" t="n">
-        <v>0.004317910988237221</v>
+        <v>0.004317910988237223</v>
       </c>
       <c r="DH18" t="n">
         <v>0.0003997466693822759</v>
@@ -9779,7 +9779,7 @@
         <v>0.0005041738044867757</v>
       </c>
       <c r="DY18" t="n">
-        <v>0.0002369804197105962</v>
+        <v>0.0002369804197105963</v>
       </c>
       <c r="DZ18" t="n">
         <v>0.0001603662093148674</v>
@@ -9797,13 +9797,13 @@
         <v>4.175063976824209e-06</v>
       </c>
       <c r="EE18" t="n">
-        <v>7.756022564998826e-05</v>
+        <v>7.756022564998829e-05</v>
       </c>
       <c r="EF18" t="n">
         <v>1.745565880593482e-06</v>
       </c>
       <c r="EG18" t="n">
-        <v>4.504922890370274e-05</v>
+        <v>4.504922890370271e-05</v>
       </c>
       <c r="EH18" t="n">
         <v>2.720933235499135e-05</v>
@@ -9918,13 +9918,13 @@
         <v>0.01030822963792791</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2099842098305724</v>
+        <v>0.2099842098305722</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6027095015948645</v>
+        <v>0.6027095015948658</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2402872979684584</v>
+        <v>0.2402872979684581</v>
       </c>
       <c r="I19" t="n">
         <v>0.07232194509890615</v>
@@ -9948,7 +9948,7 @@
         <v>0.003148384273029454</v>
       </c>
       <c r="P19" t="n">
-        <v>0.004622816887055404</v>
+        <v>0.004622816887055406</v>
       </c>
       <c r="Q19" t="n">
         <v>0.004965720391699337</v>
@@ -9957,7 +9957,7 @@
         <v>0.006738566044440671</v>
       </c>
       <c r="S19" t="n">
-        <v>0.004082339378923248</v>
+        <v>0.00408233937892325</v>
       </c>
       <c r="T19" t="n">
         <v>0.01519179964967387</v>
@@ -9984,7 +9984,7 @@
         <v>0.03816464914869597</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.0006626274530067977</v>
+        <v>0.0006626274530067974</v>
       </c>
       <c r="AC19" t="n">
         <v>0.02520750419250734</v>
@@ -9993,25 +9993,25 @@
         <v>2.818519636219284e-05</v>
       </c>
       <c r="AE19" t="n">
-        <v>9.968723616546825e-06</v>
+        <v>9.968723616546827e-06</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.06379879681704455</v>
+        <v>0.06379879681704456</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.02356429643839769</v>
+        <v>0.0235642964383977</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.001820519767030029</v>
+        <v>0.001820519767030028</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.001225896456566014</v>
+        <v>0.001225896456566013</v>
       </c>
       <c r="AJ19" t="n">
         <v>0.002579585357292189</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.01348574368262261</v>
+        <v>0.01348574368262262</v>
       </c>
       <c r="AL19" t="n">
         <v>0.0007091833770896643</v>
@@ -10035,7 +10035,7 @@
         <v>0.007062580459950529</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.000150788777677652</v>
+        <v>0.0001507887776776519</v>
       </c>
       <c r="AT19" t="n">
         <v>5.619932723971792e-05</v>
@@ -10077,10 +10077,10 @@
         <v>0.0006174331599326156</v>
       </c>
       <c r="BG19" t="n">
-        <v>0.0008232866915907141</v>
+        <v>0.0008232866915907143</v>
       </c>
       <c r="BH19" t="n">
-        <v>0.01477229576818847</v>
+        <v>0.01477229576818848</v>
       </c>
       <c r="BI19" t="n">
         <v>0.0004027621489522623</v>
@@ -10092,13 +10092,13 @@
         <v>0.007041476123928042</v>
       </c>
       <c r="BL19" t="n">
-        <v>8.572481697708279e-05</v>
+        <v>8.572481697708277e-05</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.02376213370278343</v>
+        <v>0.02376213370278344</v>
       </c>
       <c r="BN19" t="n">
-        <v>0.001256181450895547</v>
+        <v>0.001256181450895546</v>
       </c>
       <c r="BO19" t="n">
         <v>3.556478857712248e-05</v>
@@ -10116,7 +10116,7 @@
         <v>0.01721048914019958</v>
       </c>
       <c r="BT19" t="n">
-        <v>0.006198510844197337</v>
+        <v>0.00619851084419734</v>
       </c>
       <c r="BU19" t="n">
         <v>0.002624017943035063</v>
@@ -10149,7 +10149,7 @@
         <v>0.0001736089479613229</v>
       </c>
       <c r="CE19" t="n">
-        <v>0.007016298094291307</v>
+        <v>0.007016298094291305</v>
       </c>
       <c r="CF19" t="n">
         <v>0.001368413499015502</v>
@@ -10191,13 +10191,13 @@
         <v>0.0005202029619048229</v>
       </c>
       <c r="CS19" t="n">
-        <v>9.080536273001793e-05</v>
+        <v>9.080536273001795e-05</v>
       </c>
       <c r="CT19" t="n">
         <v>0.0001808557801543137</v>
       </c>
       <c r="CU19" t="n">
-        <v>9.071251955530111e-05</v>
+        <v>9.071251955530113e-05</v>
       </c>
       <c r="CV19" t="n">
         <v>0.0002993265871351347</v>
@@ -10212,7 +10212,7 @@
         <v>9.002282199120107e-05</v>
       </c>
       <c r="CZ19" t="n">
-        <v>0.0001926772358799487</v>
+        <v>0.0001926772358799488</v>
       </c>
       <c r="DA19" t="n">
         <v>0.0001984907695600887</v>
@@ -10248,7 +10248,7 @@
         <v>0.001008256212106966</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.0002080158694365899</v>
+        <v>0.00020801586943659</v>
       </c>
       <c r="DM19" t="n">
         <v>0.0002558688760493804</v>
@@ -10257,10 +10257,10 @@
         <v>3.241507591503502e-05</v>
       </c>
       <c r="DO19" t="n">
-        <v>0.0007871505645623628</v>
+        <v>0.0007871505645623626</v>
       </c>
       <c r="DP19" t="n">
-        <v>0.1531311298536745</v>
+        <v>0.1531311298536746</v>
       </c>
       <c r="DQ19" t="n">
         <v>4.962742212964996e-06</v>
@@ -10281,7 +10281,7 @@
         <v>8.69225642515611e-05</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.0003909976173068616</v>
+        <v>0.0003909976173068613</v>
       </c>
       <c r="DX19" t="n">
         <v>0.0004518049084657726</v>

--- a/data/proteomics/ratio_of_organelle_volume_to_total_protein_volume.xlsx
+++ b/data/proteomics/ratio_of_organelle_volume_to_total_protein_volume.xlsx
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4514011107868155</v>
+        <v>0.4514011107868162</v>
       </c>
       <c r="C2" t="n">
         <v>0.001138145322776525</v>
@@ -1279,76 +1279,76 @@
         <v>0.0007564024983106602</v>
       </c>
       <c r="E2" t="n">
-        <v>0.009598240105774959</v>
+        <v>0.009598240105774961</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2647587701603148</v>
+        <v>0.2647587701603152</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5835637813424226</v>
+        <v>0.5835637813424236</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2807620873832241</v>
+        <v>0.2807620873832242</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08811556074491009</v>
+        <v>0.0881155607449101</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02301410843838039</v>
+        <v>0.0230141084383804</v>
       </c>
       <c r="K2" t="n">
         <v>0.1238652254207412</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03168293346528697</v>
+        <v>0.03168293346528692</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004368911114365766</v>
+        <v>0.004368911114365767</v>
       </c>
       <c r="N2" t="n">
-        <v>0.02187998626371158</v>
+        <v>0.02187998626371159</v>
       </c>
       <c r="O2" t="n">
         <v>0.003299161701704414</v>
       </c>
       <c r="P2" t="n">
-        <v>0.004943010874955365</v>
+        <v>0.004943010874955369</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0072991492786783</v>
+        <v>0.004050608426140868</v>
       </c>
       <c r="R2" t="n">
-        <v>0.006440636546360097</v>
+        <v>0.006440636546360101</v>
       </c>
       <c r="S2" t="n">
         <v>0.004349487013014682</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01245148353819309</v>
+        <v>0.0124514835381931</v>
       </c>
       <c r="U2" t="n">
-        <v>2.659021963756566e-05</v>
+        <v>2.659021963756567e-05</v>
       </c>
       <c r="V2" t="n">
         <v>0.001673429335754054</v>
       </c>
       <c r="W2" t="n">
-        <v>0.05663180859787954</v>
+        <v>0.05663180859787957</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0002561871569803065</v>
+        <v>0.0002561871569803066</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003445284789320332</v>
+        <v>0.003445284789320333</v>
       </c>
       <c r="Z2" t="n">
         <v>0.003091116167185114</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.02044826382745893</v>
+        <v>0.02044826382745895</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0008307916238502617</v>
+        <v>0.0008307916238502621</v>
       </c>
       <c r="AC2" t="n">
         <v>0.03615553610610975</v>
@@ -1360,16 +1360,16 @@
         <v>1.370749101543504e-05</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.05163401771683859</v>
+        <v>0.05163401771683863</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.03398950311822548</v>
+        <v>0.0339895031182255</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.001819325671496336</v>
+        <v>0.001819325671496337</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.001088840188651876</v>
+        <v>0.001088840188651877</v>
       </c>
       <c r="AJ2" t="n">
         <v>0.002717652373286961</v>
@@ -1378,16 +1378,16 @@
         <v>0.01621749541868758</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.000969098409233749</v>
+        <v>0.00096909840923375</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.0004082609748373423</v>
+        <v>0.0004082609748373424</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.0003148811135487376</v>
+        <v>0.0003148811135487378</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.0006209891212877011</v>
+        <v>0.0006209891212877013</v>
       </c>
       <c r="AP2" t="n">
         <v>0.0005618771491061518</v>
@@ -1396,49 +1396,49 @@
         <v>0.001237985231383709</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.006803721620284387</v>
+        <v>0.006803721620284388</v>
       </c>
       <c r="AS2" t="n">
         <v>0.0001529218598010382</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.160717838412477e-05</v>
+        <v>7.160717838412478e-05</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.0004193415969839526</v>
+        <v>0.0004193415969839527</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.004496829762004332</v>
+        <v>0.004496829762004333</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.002690212388466481</v>
+        <v>0.002690212388466482</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.0002606926879356991</v>
+        <v>0.0002606926879356992</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.02564207079487959</v>
+        <v>0.0256420707948796</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.0006302258720994086</v>
+        <v>0.0006302258720994087</v>
       </c>
       <c r="BA2" t="n">
         <v>0.00011278566634715</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.05068208213166548</v>
+        <v>0.0506820821316655</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.008037157056752332</v>
+        <v>0.008037157056752335</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.02162496282749279</v>
+        <v>0.0216249628274928</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.0004993351953941975</v>
+        <v>0.0004993351953941976</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.0008176347941044791</v>
+        <v>0.0008176347941044794</v>
       </c>
       <c r="BG2" t="n">
         <v>0.00102113772531999</v>
@@ -1453,7 +1453,7 @@
         <v>0.0001898789649306993</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.02259081292718941</v>
+        <v>0.02259081292718942</v>
       </c>
       <c r="BL2" t="n">
         <v>5.814966281408395e-05</v>
@@ -1462,43 +1462,43 @@
         <v>0.03927082716343987</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.001514882179045458</v>
+        <v>0.001514882179045459</v>
       </c>
       <c r="BO2" t="n">
-        <v>8.122049296627733e-05</v>
+        <v>8.122049296627735e-05</v>
       </c>
       <c r="BP2" t="n">
         <v>0.0002506051290756247</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.0004009095635308535</v>
+        <v>0.0004009095635308536</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.000415942347649958</v>
+        <v>0.0004159423476499581</v>
       </c>
       <c r="BS2" t="n">
         <v>0.02563426646094737</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.005115191182953885</v>
+        <v>0.005115191182953886</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.003659725236897286</v>
+        <v>0.003659725236897287</v>
       </c>
       <c r="BV2" t="n">
         <v>0.003339001830252153</v>
       </c>
       <c r="BW2" t="n">
-        <v>9.935573353947257e-06</v>
+        <v>9.935573353947259e-06</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.002471027620689084</v>
+        <v>0.002471027620689082</v>
       </c>
       <c r="BY2" t="n">
         <v>6.626471018563796e-05</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.00809651840137781</v>
+        <v>0.008096518401377812</v>
       </c>
       <c r="CA2" t="n">
         <v>0.0001235397509145508</v>
@@ -1513,25 +1513,25 @@
         <v>0.0001286269832270554</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.004296770464568454</v>
+        <v>0.004296770464568455</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.0007661800678651387</v>
+        <v>0.0007661800678651388</v>
       </c>
       <c r="CG2" t="n">
         <v>0.003388467444963671</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.0004302386434430936</v>
+        <v>0.0004302386434430937</v>
       </c>
       <c r="CI2" t="n">
-        <v>6.059673848522342e-05</v>
+        <v>6.059673848522343e-05</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.007534733357598618</v>
+        <v>0.007534733357598619</v>
       </c>
       <c r="CK2" t="n">
-        <v>7.956493022428301e-06</v>
+        <v>7.956493022428302e-06</v>
       </c>
       <c r="CL2" t="n">
         <v>0.0004665695480942268</v>
@@ -1540,13 +1540,13 @@
         <v>2.858461671242168e-05</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.0002094064012606915</v>
+        <v>0.0002094064012606916</v>
       </c>
       <c r="CO2" t="n">
         <v>0.001531535818213803</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.0009813364237371248</v>
+        <v>0.000981336423737125</v>
       </c>
       <c r="CQ2" t="n">
         <v>0.00112688745832265</v>
@@ -1555,10 +1555,10 @@
         <v>0.0004745486677151287</v>
       </c>
       <c r="CS2" t="n">
-        <v>6.663681591795404e-05</v>
+        <v>6.663681591795405e-05</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.0001564733439512218</v>
+        <v>0.0001564733439512219</v>
       </c>
       <c r="CU2" t="n">
         <v>7.532030353908455e-05</v>
@@ -1567,10 +1567,10 @@
         <v>0.0003661675537906993</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.0004454556700479366</v>
+        <v>0.0004454556700479368</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.004115811913481494</v>
+        <v>0.004115811913481495</v>
       </c>
       <c r="CY2" t="n">
         <v>0.0001169367282664049</v>
@@ -1582,34 +1582,34 @@
         <v>0.0002839159308649934</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.0004597132695445061</v>
+        <v>0.0004597132695445062</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.0001041755937865376</v>
+        <v>0.0001041755937865377</v>
       </c>
       <c r="DD2" t="n">
         <v>0.001380144299891289</v>
       </c>
       <c r="DE2" t="n">
-        <v>8.454404152643127e-06</v>
+        <v>8.454404152643129e-06</v>
       </c>
       <c r="DF2" t="n">
         <v>0.0004404436602171758</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.006184904806043987</v>
+        <v>0.00618490480604399</v>
       </c>
       <c r="DH2" t="n">
         <v>0.0004726616705908946</v>
       </c>
       <c r="DI2" t="n">
-        <v>9.891434610827142e-05</v>
+        <v>9.891434610827145e-05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>4.688250196906363e-05</v>
+        <v>4.688250196906364e-05</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.0009800760325524318</v>
+        <v>0.000980076032552432</v>
       </c>
       <c r="DL2" t="n">
         <v>0.000298191878641569</v>
@@ -1621,34 +1621,34 @@
         <v>2.906212981932881e-05</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.0007246314682725262</v>
+        <v>0.0007246314682725261</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.07177026400670201</v>
+        <v>0.07177026400670204</v>
       </c>
       <c r="DQ2" t="n">
         <v>1.060362453724319e-05</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.677817925081206e-05</v>
+        <v>8.677817925081208e-05</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.003214630711446549</v>
+        <v>0.00321463071144655</v>
       </c>
       <c r="DT2" t="n">
         <v>0.001541411060769444</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.003431163814563673</v>
+        <v>0.003431163814563674</v>
       </c>
       <c r="DV2" t="n">
-        <v>8.069318543692785e-05</v>
+        <v>8.069318543692787e-05</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.0002891579234470403</v>
+        <v>0.0002891579234470404</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.0007470332889742125</v>
+        <v>0.0007470332889742126</v>
       </c>
       <c r="DY2" t="n">
         <v>0.0002454521307436832</v>
@@ -1657,10 +1657,10 @@
         <v>0.0001971339033407866</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.0003546170403251804</v>
+        <v>0.0003546170403251805</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.0002406498059713006</v>
+        <v>0.0002406498059713007</v>
       </c>
       <c r="EC2" t="n">
         <v>0.003676410595097742</v>
@@ -1669,22 +1669,22 @@
         <v>1.015823243849561e-05</v>
       </c>
       <c r="EE2" t="n">
-        <v>9.456002879613841e-05</v>
+        <v>9.456002879613842e-05</v>
       </c>
       <c r="EF2" t="n">
         <v>3.817206466792038e-06</v>
       </c>
       <c r="EG2" t="n">
-        <v>5.726454534572673e-05</v>
+        <v>5.726454534572675e-05</v>
       </c>
       <c r="EH2" t="n">
-        <v>3.447405095807094e-05</v>
+        <v>3.447405095807096e-05</v>
       </c>
       <c r="EI2" t="n">
         <v>2.396033981212264e-05</v>
       </c>
       <c r="EJ2" t="n">
-        <v>3.844110222705206e-05</v>
+        <v>3.844110222705207e-05</v>
       </c>
       <c r="EK2" t="n">
         <v>1.155692549812429</v>
@@ -1778,157 +1778,157 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.4536859217675871</v>
+        <v>0.4536859217675874</v>
       </c>
       <c r="C3" t="n">
         <v>0.001190017355736136</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0007680449174261289</v>
+        <v>0.0007680449174261293</v>
       </c>
       <c r="E3" t="n">
-        <v>0.009765240334658519</v>
+        <v>0.009765240334658525</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2672907387193527</v>
+        <v>0.2672907387193532</v>
       </c>
       <c r="G3" t="n">
-        <v>0.585179012736452</v>
+        <v>0.5851790127364521</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2726503286665412</v>
+        <v>0.2726503286665414</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09036794060833289</v>
+        <v>0.09036794060833292</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02245936352087538</v>
+        <v>0.02245936352087539</v>
       </c>
       <c r="K3" t="n">
         <v>0.1205266605731308</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0315731230613462</v>
+        <v>0.03157312306134623</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004179979268314905</v>
+        <v>0.004179979268314906</v>
       </c>
       <c r="N3" t="n">
-        <v>0.02367136443682706</v>
+        <v>0.02367136443682707</v>
       </c>
       <c r="O3" t="n">
-        <v>0.003524899145616539</v>
+        <v>0.00352489914561654</v>
       </c>
       <c r="P3" t="n">
-        <v>0.005156969452704177</v>
+        <v>0.005156969452704181</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.006422106503573298</v>
+        <v>0.003391380642675688</v>
       </c>
       <c r="R3" t="n">
-        <v>0.006227037417604293</v>
+        <v>0.006227037417604294</v>
       </c>
       <c r="S3" t="n">
-        <v>0.004299354733573926</v>
+        <v>0.004299354733573928</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01193291693481766</v>
+        <v>0.01193291693481768</v>
       </c>
       <c r="U3" t="n">
-        <v>2.344965061995989e-05</v>
+        <v>2.34496506199599e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001642170582954896</v>
+        <v>0.001642170582954897</v>
       </c>
       <c r="W3" t="n">
-        <v>0.05083355610080138</v>
+        <v>0.0508335561008014</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0002906983035505651</v>
+        <v>0.0002906983035505653</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.003458154648143777</v>
+        <v>0.003458154648143778</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.003130223312450443</v>
+        <v>0.003130223312450445</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01935157965516325</v>
+        <v>0.01935157965516326</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0008482564582939524</v>
+        <v>0.0008482564582939527</v>
       </c>
       <c r="AC3" t="n">
         <v>0.03833206522084406</v>
       </c>
       <c r="AD3" t="n">
-        <v>5.418479544510544e-05</v>
+        <v>5.418479544510546e-05</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.471318062254832e-05</v>
+        <v>1.471318062254833e-05</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.05246860807705809</v>
+        <v>0.05246860807705814</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.03319886772038113</v>
+        <v>0.03319886772038114</v>
       </c>
       <c r="AH3" t="n">
         <v>0.001747255584688527</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.001153402767956103</v>
+        <v>0.001153402767956104</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.002682065259628815</v>
+        <v>0.002682065259628818</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.01509147944556134</v>
+        <v>0.01509147944556135</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0009970353294941196</v>
+        <v>0.00099703532949412</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.0004384494781152532</v>
+        <v>0.0004384494781152533</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.0002664835091614188</v>
+        <v>0.0002664835091614189</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.0005537462201997649</v>
+        <v>0.0005537462201997651</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.0004672320248287168</v>
+        <v>0.000467232024828717</v>
       </c>
       <c r="AQ3" t="n">
         <v>0.00119834135674627</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.006463141014695297</v>
+        <v>0.006463141014695298</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.0001437077421570678</v>
+        <v>0.0001437077421570679</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.683415719273801e-05</v>
+        <v>7.683415719273804e-05</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.0005348421243772473</v>
+        <v>0.0005348421243772475</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.004107042457794598</v>
+        <v>0.0041070424577946</v>
       </c>
       <c r="AW3" t="n">
         <v>0.002666325041698565</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.000243036508133451</v>
+        <v>0.0002430365081334511</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.02473302936598019</v>
+        <v>0.0247330293659802</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.0006290142213496073</v>
+        <v>0.0006290142213496075</v>
       </c>
       <c r="BA3" t="n">
         <v>0.0001196051086679883</v>
@@ -1937,82 +1937,82 @@
         <v>0.05064121076697334</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.007728441673491691</v>
+        <v>0.007728441673491696</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.02115811677003063</v>
+        <v>0.02115811677003064</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.0004833924087487742</v>
+        <v>0.0004833924087487745</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.0008330070072213022</v>
+        <v>0.0008330070072213026</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.0008030265690028719</v>
+        <v>0.0008030265690028724</v>
       </c>
       <c r="BH3" t="n">
         <v>0.01287181406900986</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.0006197372534777153</v>
+        <v>0.0006197372534777156</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.264342697978812e-05</v>
+        <v>1.264342697978813e-05</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.02454992913682944</v>
+        <v>0.02454992913682945</v>
       </c>
       <c r="BL3" t="n">
-        <v>5.624979226651411e-05</v>
+        <v>5.624979226651413e-05</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.04127160724100061</v>
+        <v>0.04127160724100063</v>
       </c>
       <c r="BN3" t="n">
         <v>0.001462551414528014</v>
       </c>
       <c r="BO3" t="n">
-        <v>8.20592095957948e-05</v>
+        <v>8.205920959579484e-05</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.0002575998682265277</v>
+        <v>0.0002575998682265278</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.0003689030018054226</v>
+        <v>0.0003689030018054229</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.0004661094874081806</v>
+        <v>0.0004661094874081807</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.02683856183379417</v>
+        <v>0.02683856183379418</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.005205724415336601</v>
+        <v>0.005205724415336604</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.00375616535301888</v>
+        <v>0.003756165353018882</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.003388614769110951</v>
+        <v>0.003388614769110952</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.500637622412701e-06</v>
+        <v>9.500637622412703e-06</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.002394312049834817</v>
+        <v>0.002394312049834818</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.247644866621364e-05</v>
+        <v>7.247644866621367e-05</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.009033079992113497</v>
+        <v>0.0090330799921135</v>
       </c>
       <c r="CA3" t="n">
         <v>0.0001324388756764031</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0002596116406838069</v>
+        <v>0.000259611640683807</v>
       </c>
       <c r="CC3" t="n">
         <v>0.0001492136711217892</v>
@@ -2021,178 +2021,178 @@
         <v>0.0001310347869908101</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.004286052694668727</v>
+        <v>0.004286052694668729</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.0007854655454547286</v>
+        <v>0.0007854655454547291</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.003174827065466134</v>
+        <v>0.003174827065466135</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.000443847732881097</v>
+        <v>0.0004438477328810972</v>
       </c>
       <c r="CI3" t="n">
-        <v>5.981299816791831e-05</v>
+        <v>5.981299816791834e-05</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.007720746186446582</v>
+        <v>0.007720746186446584</v>
       </c>
       <c r="CK3" t="n">
-        <v>8.727305418555207e-06</v>
+        <v>8.727305418555211e-06</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.0004486990294781687</v>
+        <v>0.0004486990294781688</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.658435963637778e-05</v>
+        <v>2.65843596363778e-05</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.0002064370694548268</v>
+        <v>0.0002064370694548269</v>
       </c>
       <c r="CO3" t="n">
         <v>0.001442538034624295</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.001104545556367649</v>
+        <v>0.00110454555636765</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.001135010553992823</v>
+        <v>0.001135010553992824</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.0004250304910871536</v>
+        <v>0.0004250304910871539</v>
       </c>
       <c r="CS3" t="n">
-        <v>7.708486578627711e-05</v>
+        <v>7.708486578627713e-05</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.0001635017911214542</v>
+        <v>0.0001635017911214543</v>
       </c>
       <c r="CU3" t="n">
-        <v>7.209128241335163e-05</v>
+        <v>7.209128241335165e-05</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.000360829288433987</v>
+        <v>0.0003608292884339872</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.0004812388623252395</v>
+        <v>0.0004812388623252397</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.003900378018905862</v>
+        <v>0.003900378018905864</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.000124126258843698</v>
+        <v>0.0001241262588436981</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.0002634086221198147</v>
+        <v>0.0002634086221198148</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.0002846268238302533</v>
+        <v>0.0002846268238302534</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.0004780552672017843</v>
+        <v>0.0004780552672017845</v>
       </c>
       <c r="DC3" t="n">
-        <v>9.88962309093616e-05</v>
+        <v>9.889623090936174e-05</v>
       </c>
       <c r="DD3" t="n">
         <v>0.001378170334893687</v>
       </c>
       <c r="DE3" t="n">
-        <v>7.839559348316287e-06</v>
+        <v>7.83955934831629e-06</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.0004425536508744434</v>
+        <v>0.0004425536508744436</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.00621126046004099</v>
+        <v>0.006211260460040992</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.0004541151718643715</v>
+        <v>0.0004541151718643719</v>
       </c>
       <c r="DI3" t="n">
-        <v>7.344831446231966e-05</v>
+        <v>7.344831446231969e-05</v>
       </c>
       <c r="DJ3" t="n">
-        <v>5.387454541560061e-05</v>
+        <v>5.387454541560064e-05</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.0009699797078465398</v>
+        <v>0.0009699797078465402</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.0002934917652170637</v>
+        <v>0.0002934917652170639</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.0001251137037567987</v>
+        <v>0.0001251137037567988</v>
       </c>
       <c r="DN3" t="n">
-        <v>2.846700890089106e-05</v>
+        <v>2.846700890089107e-05</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.0006712545820733941</v>
+        <v>0.0006712545820733943</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.06891074474912708</v>
+        <v>0.0689107447491271</v>
       </c>
       <c r="DQ3" t="n">
-        <v>1.064454081914529e-05</v>
+        <v>1.06445408191453e-05</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.566710355794177e-05</v>
+        <v>9.566710355794181e-05</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.003265706118986035</v>
+        <v>0.003265706118986036</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.001457081899758114</v>
+        <v>0.001457081899758115</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.003462906833552784</v>
+        <v>0.003462906833552785</v>
       </c>
       <c r="DV3" t="n">
-        <v>7.246451096549651e-05</v>
+        <v>7.246451096549653e-05</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.0002803526681551384</v>
+        <v>0.0002803526681551385</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.0007711207898277211</v>
+        <v>0.0007711207898277214</v>
       </c>
       <c r="DY3" t="n">
         <v>0.0002248942708778208</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.000200115438332615</v>
+        <v>0.0002001154383326151</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.0003538086068002064</v>
+        <v>0.0003538086068002065</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.0002196544707489353</v>
+        <v>0.0002196544707489354</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.003629469191233235</v>
+        <v>0.003629469191233236</v>
       </c>
       <c r="ED3" t="n">
-        <v>9.015863926024504e-06</v>
+        <v>9.015863926024509e-06</v>
       </c>
       <c r="EE3" t="n">
-        <v>9.761269031304296e-05</v>
+        <v>9.7612690313043e-05</v>
       </c>
       <c r="EF3" t="n">
-        <v>4.128544232240534e-06</v>
+        <v>4.128544232240535e-06</v>
       </c>
       <c r="EG3" t="n">
-        <v>5.695606790626441e-05</v>
+        <v>5.695606790626444e-05</v>
       </c>
       <c r="EH3" t="n">
-        <v>3.534571896786012e-05</v>
+        <v>3.534571896786014e-05</v>
       </c>
       <c r="EI3" t="n">
-        <v>2.550314938926626e-05</v>
+        <v>2.550314938926627e-05</v>
       </c>
       <c r="EJ3" t="n">
-        <v>3.851633171982105e-05</v>
+        <v>3.851633171982107e-05</v>
       </c>
       <c r="EK3" t="n">
         <v>1.051318643827377</v>
@@ -2286,424 +2286,424 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.4546769531128738</v>
+        <v>0.4546769531128732</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001036090688825052</v>
+        <v>0.001036090688825051</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007873251321465185</v>
+        <v>0.0007873251321465175</v>
       </c>
       <c r="E4" t="n">
-        <v>0.009531187683197603</v>
+        <v>0.009531187683197591</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2704048328691835</v>
+        <v>0.2704048328691828</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5778917462687793</v>
+        <v>0.5778917462687789</v>
       </c>
       <c r="H4" t="n">
-        <v>0.255821182078385</v>
+        <v>0.2558211820783847</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07947888368535576</v>
+        <v>0.07947888368535565</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02271766915324992</v>
+        <v>0.02271766915324989</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1009001715220335</v>
+        <v>0.1009001715220334</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03003470011600452</v>
+        <v>0.0300347001160045</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0041699906214876</v>
+        <v>0.004169990621487596</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02616070204960105</v>
+        <v>0.02616070204960102</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003599261445777716</v>
+        <v>0.003599261445777711</v>
       </c>
       <c r="P4" t="n">
-        <v>0.004701502298385577</v>
+        <v>0.004701502298385571</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.006494758845649594</v>
+        <v>0.003443302753071008</v>
       </c>
       <c r="R4" t="n">
-        <v>0.005792361057911629</v>
+        <v>0.005792361057911623</v>
       </c>
       <c r="S4" t="n">
-        <v>0.004266624905191249</v>
+        <v>0.004266624905191246</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01280280326897848</v>
+        <v>0.01280280326897846</v>
       </c>
       <c r="U4" t="n">
-        <v>2.007242008489368e-05</v>
+        <v>2.007242008489365e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001611825193917325</v>
+        <v>0.001611825193917323</v>
       </c>
       <c r="W4" t="n">
-        <v>0.04436376656898493</v>
+        <v>0.04436376656898489</v>
       </c>
       <c r="X4" t="n">
-        <v>0.000334954037722334</v>
+        <v>0.0003349540377223338</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.003466525320207539</v>
+        <v>0.003466525320207535</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.00291322575477225</v>
+        <v>0.002913225754772246</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.02024379977189249</v>
+        <v>0.02024379977189245</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0009228730472713828</v>
+        <v>0.0009228730472713809</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0393056011395655</v>
+        <v>0.03930560113956545</v>
       </c>
       <c r="AD4" t="n">
-        <v>5.802075169389524e-05</v>
+        <v>5.802075169389517e-05</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.578473002420768e-05</v>
+        <v>1.578473002420766e-05</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.06482912571748298</v>
+        <v>0.06482912571748291</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.03962589797069917</v>
+        <v>0.03962589797069911</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.001709215079799333</v>
+        <v>0.001709215079799331</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.001055320420934921</v>
+        <v>0.001055320420934919</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.002642914915330515</v>
+        <v>0.002642914915330512</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.01603931407200479</v>
+        <v>0.01603931407200478</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.001019689985894212</v>
+        <v>0.001019689985894211</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0004689816751697237</v>
+        <v>0.0004689816751697231</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.0002779340070911843</v>
+        <v>0.0002779340070911841</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.0005590296744873176</v>
+        <v>0.000559029674487317</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.000477246650954863</v>
+        <v>0.0004772466509548625</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.001227862258222554</v>
+        <v>0.001227862258222552</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.005829649317944522</v>
+        <v>0.00582964931794452</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.0001438831992132121</v>
+        <v>0.0001438831992132119</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.365631256124362e-05</v>
+        <v>8.365631256124354e-05</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.000398995456393626</v>
+        <v>0.0003989954563936256</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.00375009234020505</v>
+        <v>0.003750092340205046</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.002395017850861185</v>
+        <v>0.002395017850861182</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0002517308230112055</v>
+        <v>0.0002517308230112052</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.02374874757143995</v>
+        <v>0.02374874757143992</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.0006107485110117163</v>
+        <v>0.0006107485110117156</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.000114261125826021</v>
+        <v>0.0001142611258260209</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.04983176326419915</v>
+        <v>0.04983176326419907</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.007896109753469778</v>
+        <v>0.007896109753469769</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.02116731265853498</v>
+        <v>0.02116731265853496</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.0005785731792104751</v>
+        <v>0.0005785731792104745</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.0008181678991504551</v>
+        <v>0.0008181678991504545</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.0009868729972667602</v>
+        <v>0.0009868729972667598</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.0142493442945973</v>
+        <v>0.01424934429459728</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.0004567447713269001</v>
+        <v>0.0004567447713268994</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.0002016347786902534</v>
+        <v>0.0002016347786902533</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.02364571808258182</v>
+        <v>0.02364571808258178</v>
       </c>
       <c r="BL4" t="n">
-        <v>6.753914185495205e-05</v>
+        <v>6.753914185495197e-05</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.03973282024896643</v>
+        <v>0.03973282024896638</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.001450579693027305</v>
+        <v>0.001450579693027303</v>
       </c>
       <c r="BO4" t="n">
-        <v>7.662702977880793e-05</v>
+        <v>7.662702977880783e-05</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.0002423757442130722</v>
+        <v>0.0002423757442130719</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0003386536608254527</v>
+        <v>0.0003386536608254523</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.0004392452439893001</v>
+        <v>0.0004392452439892995</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.03065569737681552</v>
+        <v>0.03065569737681548</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.005056887233924069</v>
+        <v>0.005056887233924062</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.003544995891757778</v>
+        <v>0.003544995891757774</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.003452831585003978</v>
+        <v>0.003452831585003975</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.037294469037091e-05</v>
+        <v>1.037294469037089e-05</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.002200815177906516</v>
+        <v>0.002200815177906514</v>
       </c>
       <c r="BY4" t="n">
-        <v>6.33521601827009e-05</v>
+        <v>6.335216018270083e-05</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.008178217921525311</v>
+        <v>0.0081782179215253</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.0001245319921969533</v>
+        <v>0.0001245319921969531</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.0002517170632457233</v>
+        <v>0.000251717063245723</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.000145661773098678</v>
+        <v>0.0001456617730986779</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.0001256360401556166</v>
+        <v>0.0001256360401556165</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.004087267274938041</v>
+        <v>0.004087267274938036</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.0008787308039256302</v>
+        <v>0.0008787308039256291</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.003170612888506208</v>
+        <v>0.003170612888506204</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0004205276441955875</v>
+        <v>0.0004205276441955871</v>
       </c>
       <c r="CI4" t="n">
-        <v>6.446543949698325e-05</v>
+        <v>6.446543949698317e-05</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.008602033057261954</v>
+        <v>0.008602033057261944</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.006326532812664e-05</v>
+        <v>1.006326532812662e-05</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.0005500904405957281</v>
+        <v>0.0005500904405957274</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.795311737742906e-05</v>
+        <v>2.795311737742903e-05</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0002029557264847398</v>
+        <v>0.0002029557264847396</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.001572267326053859</v>
+        <v>0.001572267326053858</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.0009568727315293146</v>
+        <v>0.0009568727315293134</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.00118214726855154</v>
+        <v>0.001182147268551539</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.0004018979955411816</v>
+        <v>0.0004018979955411811</v>
       </c>
       <c r="CS4" t="n">
-        <v>6.657676969777368e-05</v>
+        <v>6.657676969777361e-05</v>
       </c>
       <c r="CT4" t="n">
         <v>0.0001513424192276226</v>
       </c>
       <c r="CU4" t="n">
-        <v>8.859966220996152e-05</v>
+        <v>8.859966220996141e-05</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0003892256446475494</v>
+        <v>0.0003892256446475489</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.0004298065647087271</v>
+        <v>0.0004298065647087265</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.003793568264295546</v>
+        <v>0.003793568264295541</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.0001179787916173633</v>
+        <v>0.0001179787916173631</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0002448763264696966</v>
+        <v>0.0002448763264696964</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0002524120901579198</v>
+        <v>0.0002524120901579195</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.0005324967557723864</v>
+        <v>0.0005324967557723858</v>
       </c>
       <c r="DC4" t="n">
-        <v>7.592779161251314e-05</v>
+        <v>7.592779161251303e-05</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.001386644903557045</v>
+        <v>0.001386644903557043</v>
       </c>
       <c r="DE4" t="n">
-        <v>8.75232022967903e-06</v>
+        <v>8.752320229679019e-06</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.0003658479336120572</v>
+        <v>0.0003658479336120568</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.00618124515601599</v>
+        <v>0.006181245156015982</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.0005544673486470455</v>
+        <v>0.0005544673486470448</v>
       </c>
       <c r="DI4" t="n">
-        <v>7.597458918222001e-05</v>
+        <v>7.597458918221991e-05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>4.25350803238105e-05</v>
+        <v>4.253508032381045e-05</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.0009519100974202372</v>
+        <v>0.000951910097420236</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0002972217646922552</v>
+        <v>0.0002972217646922549</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.0001183785616395543</v>
+        <v>0.0001183785616395541</v>
       </c>
       <c r="DN4" t="n">
-        <v>2.392159993273484e-05</v>
+        <v>2.392159993273481e-05</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.0007119959987661358</v>
+        <v>0.0007119959987661349</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.07038673500289599</v>
+        <v>0.07038673500289593</v>
       </c>
       <c r="DQ4" t="n">
-        <v>1.114338984082168e-05</v>
+        <v>1.114338984082167e-05</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.88409976803437e-05</v>
+        <v>8.88409976803436e-05</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.003242113559274936</v>
+        <v>0.003242113559274933</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.001443633501436199</v>
+        <v>0.001443633501436197</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.003059734845920151</v>
+        <v>0.003059734845920147</v>
       </c>
       <c r="DV4" t="n">
-        <v>6.408431369588347e-05</v>
+        <v>6.408431369588337e-05</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0002374235572865494</v>
+        <v>0.0002374235572865491</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.0007142886983465173</v>
+        <v>0.0007142886983465165</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.000218800674057082</v>
+        <v>0.0002188006740570817</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0001866394080211563</v>
+        <v>0.0001866394080211561</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.0003588851571833872</v>
+        <v>0.0003588851571833868</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.000204286661530635</v>
+        <v>0.0002042866615306347</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.004156555709306313</v>
+        <v>0.004156555709306307</v>
       </c>
       <c r="ED4" t="n">
-        <v>1.128021600501435e-05</v>
+        <v>1.128021600501434e-05</v>
       </c>
       <c r="EE4" t="n">
-        <v>8.989315256237303e-05</v>
+        <v>8.989315256237292e-05</v>
       </c>
       <c r="EF4" t="n">
-        <v>4.209032238781583e-06</v>
+        <v>4.209032238781578e-06</v>
       </c>
       <c r="EG4" t="n">
-        <v>6.966171439874387e-05</v>
+        <v>6.966171439874378e-05</v>
       </c>
       <c r="EH4" t="n">
-        <v>2.676649847454218e-05</v>
+        <v>2.676649847454215e-05</v>
       </c>
       <c r="EI4" t="n">
-        <v>1.767327629730496e-05</v>
+        <v>1.767327629730493e-05</v>
       </c>
       <c r="EJ4" t="n">
-        <v>3.819440673377658e-05</v>
+        <v>3.819440673377654e-05</v>
       </c>
       <c r="EK4" t="n">
-        <v>1.089951957320836</v>
+        <v>1.089951957320837</v>
       </c>
       <c r="EL4" t="inlineStr">
         <is>
@@ -2794,424 +2794,424 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.426393658716793</v>
+        <v>0.4263936587167935</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001086987898536733</v>
+        <v>0.001086987898536736</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0008835042779916192</v>
+        <v>0.0008835042779916216</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01145152515317253</v>
+        <v>0.01145152515317256</v>
       </c>
       <c r="F5" t="n">
-        <v>0.251075615965874</v>
+        <v>0.2510756159658747</v>
       </c>
       <c r="G5" t="n">
-        <v>0.566317503860951</v>
+        <v>0.5663175038609527</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2676788059523421</v>
+        <v>0.2676788059523424</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08267061513837012</v>
+        <v>0.08267061513837035</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02897958412384954</v>
+        <v>0.02897958412384962</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1063878023397976</v>
+        <v>0.1063878023397979</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0329607619698535</v>
+        <v>0.03296076196985358</v>
       </c>
       <c r="M5" t="n">
-        <v>0.005103602078365277</v>
+        <v>0.00510360207836529</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0202226482561819</v>
+        <v>0.02022264825618196</v>
       </c>
       <c r="O5" t="n">
-        <v>0.003359929859780819</v>
+        <v>0.003359929859780828</v>
       </c>
       <c r="P5" t="n">
-        <v>0.00589582029116055</v>
+        <v>0.005895820291160563</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.007365026049752812</v>
+        <v>0.003668913367292928</v>
       </c>
       <c r="R5" t="n">
-        <v>0.00654916253638194</v>
+        <v>0.006549162536381953</v>
       </c>
       <c r="S5" t="n">
-        <v>0.005024181085500316</v>
+        <v>0.005024181085500324</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01395492599191237</v>
+        <v>0.0139549259919124</v>
       </c>
       <c r="U5" t="n">
-        <v>2.594829509045112e-05</v>
+        <v>2.594829509045119e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001818364429166239</v>
+        <v>0.001818364429166244</v>
       </c>
       <c r="W5" t="n">
-        <v>0.04569397711134843</v>
+        <v>0.04569397711134853</v>
       </c>
       <c r="X5" t="n">
-        <v>0.000346434045829995</v>
+        <v>0.0003464340458299958</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.003709320322272919</v>
+        <v>0.003709320322272929</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.003775004523656916</v>
+        <v>0.003775004523656927</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02314008062746433</v>
+        <v>0.02314008062746439</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0009489254109138447</v>
+        <v>0.000948925410913847</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.03725046939883495</v>
+        <v>0.03725046939883505</v>
       </c>
       <c r="AD5" t="n">
-        <v>5.57077748176851e-05</v>
+        <v>5.570777481768524e-05</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.50342817885009e-05</v>
+        <v>1.503428178850094e-05</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.05533502255064026</v>
+        <v>0.05533502255064041</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.03951862230956375</v>
+        <v>0.03951862230956386</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.001794264421421018</v>
+        <v>0.001794264421421024</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.001142437232772119</v>
+        <v>0.001142437232772122</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.002926093992258347</v>
+        <v>0.002926093992258356</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.01661330218879135</v>
+        <v>0.01661330218879139</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0009959285386042711</v>
+        <v>0.0009959285386042735</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0004505326355780037</v>
+        <v>0.0004505326355780048</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.0002913856093048322</v>
+        <v>0.000291385609304833</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0006268675586784514</v>
+        <v>0.000626867558678453</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.0005309033432393475</v>
+        <v>0.0005309033432393488</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.001368009506652417</v>
+        <v>0.00136800950665242</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.006777427524272307</v>
+        <v>0.006777427524272324</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.0001529538731269049</v>
+        <v>0.0001529538731269052</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.305051973989203e-05</v>
+        <v>8.305051973989226e-05</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.0004347594291988383</v>
+        <v>0.0004347594291988394</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.00346035931239486</v>
+        <v>0.003460359312394869</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.003096544947320878</v>
+        <v>0.003096544947320886</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.0002546016405701657</v>
+        <v>0.0002546016405701664</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.02786407035277116</v>
+        <v>0.02786407035277124</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0007123157257704508</v>
+        <v>0.000712315725770453</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.0001130125046276351</v>
+        <v>0.0001130125046276354</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.04316816359047596</v>
+        <v>0.04316816359047607</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.009081159626295385</v>
+        <v>0.009081159626295408</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.02833203554007145</v>
+        <v>0.02833203554007152</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.0005431514543861904</v>
+        <v>0.0005431514543861917</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.0009011511308431916</v>
+        <v>0.0009011511308431939</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.0008672758183233376</v>
+        <v>0.0008672758183233398</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.01886638236493761</v>
+        <v>0.01886638236493766</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.000532002414147426</v>
+        <v>0.0005320024141474274</v>
       </c>
       <c r="BJ5" t="n">
-        <v>5.664095147336091e-06</v>
+        <v>5.664095147336105e-06</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.01865760314305323</v>
+        <v>0.01865760314305328</v>
       </c>
       <c r="BL5" t="n">
-        <v>7.333118624573398e-05</v>
+        <v>7.333118624573419e-05</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.02554726705622574</v>
+        <v>0.02554726705622579</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.001551270622380146</v>
+        <v>0.00155127062238015</v>
       </c>
       <c r="BO5" t="n">
-        <v>8.051745426837372e-05</v>
+        <v>8.051745426837391e-05</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.0002739858649026024</v>
+        <v>0.0002739858649026031</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.0004185690042235619</v>
+        <v>0.0004185690042235629</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.0003056389124976321</v>
+        <v>0.0003056389124976329</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.0280225020457372</v>
+        <v>0.02802250204573727</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.005515556241707839</v>
+        <v>0.005515556241707852</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.003766606529781044</v>
+        <v>0.003766606529781054</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.003386697658783601</v>
+        <v>0.003386697658783609</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.076583434027208e-05</v>
+        <v>1.076583434027211e-05</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.002528397896113923</v>
+        <v>0.00252839789611393</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.651104004021184e-05</v>
+        <v>8.651104004021206e-05</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.009512952866026598</v>
+        <v>0.00951295286602662</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.0001305955461502732</v>
+        <v>0.0001305955461502735</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.0003008267780234965</v>
+        <v>0.0003008267780234973</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.0001288630198552905</v>
+        <v>0.0001288630198552908</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.0001673573638653699</v>
+        <v>0.0001673573638653704</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.005732652547067399</v>
+        <v>0.005732652547067413</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.000975955120932971</v>
+        <v>0.0009759551209329734</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.003856918905163178</v>
+        <v>0.003856918905163188</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.0004550513373468719</v>
+        <v>0.0004550513373468729</v>
       </c>
       <c r="CI5" t="n">
-        <v>8.271887595369813e-05</v>
+        <v>8.271887595369833e-05</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.008662849156083868</v>
+        <v>0.008662849156083891</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.013994484564103e-05</v>
+        <v>1.013994484564106e-05</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.0005073825807525252</v>
+        <v>0.0005073825807525265</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.858312715415653e-05</v>
+        <v>2.85831271541566e-05</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0002176112779424776</v>
+        <v>0.0002176112779424783</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.001279569521459332</v>
+        <v>0.001279569521459336</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.0008902051093832293</v>
+        <v>0.0008902051093832316</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.001117470662754544</v>
+        <v>0.001117470662754547</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.0004787372356143592</v>
+        <v>0.0004787372356143605</v>
       </c>
       <c r="CS5" t="n">
-        <v>8.268069879698985e-05</v>
+        <v>8.268069879699007e-05</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.0001997205532182193</v>
+        <v>0.0001997205532182198</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.0001015853022629581</v>
+        <v>0.0001015853022629583</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.0003864954127770403</v>
+        <v>0.0003864954127770413</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.0004041246547790937</v>
+        <v>0.0004041246547790947</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.003806225640316246</v>
+        <v>0.003806225640316256</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.0001398352788191573</v>
+        <v>0.0001398352788191577</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0002905581085579407</v>
+        <v>0.0002905581085579415</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.0002940751215136195</v>
+        <v>0.0002940751215136202</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.0005082608838572749</v>
+        <v>0.0005082608838572762</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.0001199288122377834</v>
+        <v>0.0001199288122377837</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.001495316833425644</v>
+        <v>0.001495316833425647</v>
       </c>
       <c r="DE5" t="n">
-        <v>9.034826622501904e-06</v>
+        <v>9.034826622501926e-06</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.0004459959125028116</v>
+        <v>0.0004459959125028127</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.006131116771282704</v>
+        <v>0.00613111677128272</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.000514182782969576</v>
+        <v>0.0005141827829695774</v>
       </c>
       <c r="DI5" t="n">
-        <v>8.205786339171997e-05</v>
+        <v>8.205786339172018e-05</v>
       </c>
       <c r="DJ5" t="n">
-        <v>5.70685716540379e-05</v>
+        <v>5.706857165403805e-05</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.001083648649387747</v>
+        <v>0.001083648649387749</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.0003136936430466919</v>
+        <v>0.0003136936430466927</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.0001576833920140224</v>
+        <v>0.0001576833920140228</v>
       </c>
       <c r="DN5" t="n">
-        <v>3.365077072887017e-05</v>
+        <v>3.365077072887024e-05</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.0009604147927331545</v>
+        <v>0.0009604147927331572</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.07920413304493254</v>
+        <v>0.07920413304493276</v>
       </c>
       <c r="DQ5" t="n">
-        <v>1.002737830444164e-05</v>
+        <v>1.002737830444167e-05</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.0001012746531056964</v>
+        <v>0.0001012746531056966</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.003198487867061366</v>
+        <v>0.003198487867061373</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.001663417256651596</v>
+        <v>0.0016634172566516</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.003885417341094933</v>
+        <v>0.003885417341094943</v>
       </c>
       <c r="DV5" t="n">
-        <v>8.785095693233644e-05</v>
+        <v>8.785095693233666e-05</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.0003461417547028039</v>
+        <v>0.0003461417547028048</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.0007990926380037986</v>
+        <v>0.0007990926380038006</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.000233705076129715</v>
+        <v>0.0002337050761297156</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.0001993502567594431</v>
+        <v>0.0001993502567594436</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.000420560112981014</v>
+        <v>0.000420560112981015</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.0002580396522472383</v>
+        <v>0.0002580396522472389</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.005365205032086627</v>
+        <v>0.00536520503208664</v>
       </c>
       <c r="ED5" t="n">
-        <v>1.133325090666739e-05</v>
+        <v>1.133325090666742e-05</v>
       </c>
       <c r="EE5" t="n">
-        <v>7.460112489559568e-05</v>
+        <v>7.460112489559589e-05</v>
       </c>
       <c r="EF5" t="n">
-        <v>4.804658657057016e-06</v>
+        <v>4.804658657057028e-06</v>
       </c>
       <c r="EG5" t="n">
-        <v>9.835533551432515e-05</v>
+        <v>9.835533551432539e-05</v>
       </c>
       <c r="EH5" t="n">
-        <v>4.081434470971468e-05</v>
+        <v>4.081434470971479e-05</v>
       </c>
       <c r="EI5" t="n">
-        <v>2.837847993465128e-05</v>
+        <v>2.837847993465135e-05</v>
       </c>
       <c r="EJ5" t="n">
-        <v>4.280733588173251e-05</v>
+        <v>4.280733588173262e-05</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.9219426959090961</v>
+        <v>0.9219426959090937</v>
       </c>
       <c r="EL5" t="inlineStr">
         <is>
@@ -3302,91 +3302,91 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.4227352516911569</v>
+        <v>0.4227352516911566</v>
       </c>
       <c r="C6" t="n">
         <v>0.001066704132296637</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0008726615853132887</v>
+        <v>0.0008726615853132881</v>
       </c>
       <c r="E6" t="n">
         <v>0.01111363487178603</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2515811101390256</v>
+        <v>0.2515811101390258</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5663702387268813</v>
+        <v>0.5663702387268796</v>
       </c>
       <c r="H6" t="n">
         <v>0.2614041969077067</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08257671045228986</v>
+        <v>0.0825767104522898</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02815547285160128</v>
+        <v>0.02815547285160127</v>
       </c>
       <c r="K6" t="n">
-        <v>0.103011272284949</v>
+        <v>0.1030112722849489</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03438301543595159</v>
+        <v>0.03438301543595162</v>
       </c>
       <c r="M6" t="n">
-        <v>0.005601051590717518</v>
+        <v>0.005601051590717516</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02206054957389996</v>
+        <v>0.02206054957389997</v>
       </c>
       <c r="O6" t="n">
-        <v>0.003474109133720713</v>
+        <v>0.003474109133720712</v>
       </c>
       <c r="P6" t="n">
-        <v>0.005688818709110314</v>
+        <v>0.005688818709110313</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.008061015446207557</v>
+        <v>0.003798670792781531</v>
       </c>
       <c r="R6" t="n">
-        <v>0.006791665756680058</v>
+        <v>0.006791665756680055</v>
       </c>
       <c r="S6" t="n">
         <v>0.004924852278047216</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01428681168309995</v>
+        <v>0.01428681168309994</v>
       </c>
       <c r="U6" t="n">
-        <v>2.378946652085053e-05</v>
+        <v>2.378946652085052e-05</v>
       </c>
       <c r="V6" t="n">
         <v>0.001799195799451699</v>
       </c>
       <c r="W6" t="n">
-        <v>0.04164456228130257</v>
+        <v>0.04164456228130258</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0003022099131444274</v>
+        <v>0.0003022099131444273</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.003793012992107941</v>
+        <v>0.003793012992107939</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.003594781959460518</v>
+        <v>0.003594781959460517</v>
       </c>
       <c r="AA6" t="n">
         <v>0.02207652046551524</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0009343019799458826</v>
+        <v>0.000934301979945882</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.04069959670922148</v>
+        <v>0.04069959670922146</v>
       </c>
       <c r="AD6" t="n">
-        <v>6.224528430332484e-05</v>
+        <v>6.224528430332483e-05</v>
       </c>
       <c r="AE6" t="n">
         <v>1.352337795305108e-05</v>
@@ -3398,124 +3398,124 @@
         <v>0.03869845786108607</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.001821636454842894</v>
+        <v>0.001821636454842893</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.001109019574415851</v>
+        <v>0.00110901957441585</v>
       </c>
       <c r="AJ6" t="n">
         <v>0.002808019728542689</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.0166109160805794</v>
+        <v>0.01661091608057941</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.0009570577564899213</v>
+        <v>0.0009570577564899208</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.0003981695691104413</v>
+        <v>0.0003981695691104411</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.0002984231423511101</v>
+        <v>0.0002984231423511099</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.0006060281983793638</v>
+        <v>0.0006060281983793637</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.0005263893586533082</v>
+        <v>0.0005263893586533079</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.001415472210854034</v>
+        <v>0.001415472210854033</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.006985426191517972</v>
+        <v>0.006985426191517969</v>
       </c>
       <c r="AS6" t="n">
         <v>0.0001425997639309064</v>
       </c>
       <c r="AT6" t="n">
-        <v>7.596556041771319e-05</v>
+        <v>7.596556041771317e-05</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.0004229866361296773</v>
+        <v>0.0004229866361296772</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.003969169471052272</v>
+        <v>0.003969169471052271</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.002805786450383379</v>
+        <v>0.002805786450383378</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.0002550161853322615</v>
+        <v>0.0002550161853322614</v>
       </c>
       <c r="AY6" t="n">
         <v>0.02627862706672282</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.0007139173525756071</v>
+        <v>0.0007139173525756066</v>
       </c>
       <c r="BA6" t="n">
         <v>0.0001118038964318673</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.04688263262378842</v>
+        <v>0.0468826326237884</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.009107309064640237</v>
+        <v>0.009107309064640233</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.02799779567923098</v>
+        <v>0.02799779567923097</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.000548128291267283</v>
+        <v>0.0005481282912672828</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.0009330877553775715</v>
+        <v>0.0009330877553775709</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.0011245813849962</v>
+        <v>0.001124581384996199</v>
       </c>
       <c r="BH6" t="n">
         <v>0.01713220518042309</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.0005092520778577369</v>
+        <v>0.0005092520778577367</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.0002313847828477033</v>
+        <v>0.0002313847828477032</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.0219041196173692</v>
+        <v>0.02190411961736921</v>
       </c>
       <c r="BL6" t="n">
-        <v>7.576919944009848e-05</v>
+        <v>7.576919944009847e-05</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.02603943026841241</v>
+        <v>0.0260394302684124</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.001613566072645129</v>
+        <v>0.001613566072645128</v>
       </c>
       <c r="BO6" t="n">
-        <v>8.177430860095533e-05</v>
+        <v>8.17743086009553e-05</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.0002565053564945373</v>
+        <v>0.0002565053564945371</v>
       </c>
       <c r="BQ6" t="n">
         <v>0.0004010741386646004</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.0003353607314505782</v>
+        <v>0.0003353607314505781</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.02782908661553873</v>
+        <v>0.02782908661553871</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.005121530463081878</v>
+        <v>0.005121530463081873</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.003769445650886081</v>
+        <v>0.003769445650886079</v>
       </c>
       <c r="BV6" t="n">
         <v>0.00333777449456618</v>
@@ -3524,19 +3524,19 @@
         <v>1.054412450191566e-05</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.002395879143432657</v>
+        <v>0.002395879143432655</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.716267927988565e-05</v>
+        <v>8.716267927988563e-05</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.01152695072129932</v>
+        <v>0.01152695072129931</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.0001229187363685428</v>
+        <v>0.0001229187363685427</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.0002996847235903553</v>
+        <v>0.0002996847235903551</v>
       </c>
       <c r="CC6" t="n">
         <v>0.0001299054710828738</v>
@@ -3545,106 +3545,106 @@
         <v>0.0001684721696928851</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.005544851793944127</v>
+        <v>0.005544851793944125</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.0009932124789159393</v>
+        <v>0.0009932124789159389</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.004416257370812521</v>
+        <v>0.004416257370812519</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.0004516806323105955</v>
+        <v>0.0004516806323105953</v>
       </c>
       <c r="CI6" t="n">
-        <v>4.971801122583898e-05</v>
+        <v>4.971801122583896e-05</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.009546984340395047</v>
+        <v>0.009546984340395045</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.090205390824516e-05</v>
+        <v>1.090205390824515e-05</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.0005111837286438041</v>
+        <v>0.0005111837286438039</v>
       </c>
       <c r="CM6" t="n">
-        <v>3.075676744909168e-05</v>
+        <v>3.075676744909167e-05</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.0002268634859295727</v>
+        <v>0.0002268634859295726</v>
       </c>
       <c r="CO6" t="n">
         <v>0.001284429072469377</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.0009703338827003326</v>
+        <v>0.0009703338827003323</v>
       </c>
       <c r="CQ6" t="n">
         <v>0.001164733289791738</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.000509320767969408</v>
+        <v>0.0005093207679694077</v>
       </c>
       <c r="CS6" t="n">
-        <v>8.26268060354619e-05</v>
+        <v>8.262680603546189e-05</v>
       </c>
       <c r="CT6" t="n">
         <v>0.0001831861232492419</v>
       </c>
       <c r="CU6" t="n">
-        <v>9.85630996684478e-05</v>
+        <v>9.856309966844776e-05</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.0003632450680907215</v>
+        <v>0.0003632450680907214</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.0004555790365386943</v>
+        <v>0.0004555790365386941</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.003694441908169485</v>
+        <v>0.003694441908169484</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.0001212824903189612</v>
+        <v>0.0001212824903189611</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.0002833889747667166</v>
+        <v>0.0002833889747667165</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.0002912877747387425</v>
+        <v>0.0002912877747387426</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.0005351462774161596</v>
+        <v>0.0005351462774161595</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.0001242588648592677</v>
+        <v>0.0001242588648592676</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.001480312618808335</v>
+        <v>0.001480312618808334</v>
       </c>
       <c r="DE6" t="n">
-        <v>9.457898017753402e-06</v>
+        <v>9.457898017753398e-06</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.000483594658682301</v>
+        <v>0.0004835946586823008</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.006213387027245723</v>
+        <v>0.006213387027245719</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.0005163818081614936</v>
+        <v>0.0005163818081614933</v>
       </c>
       <c r="DI6" t="n">
-        <v>7.67157452725074e-05</v>
+        <v>7.671574527250738e-05</v>
       </c>
       <c r="DJ6" t="n">
         <v>5.16660228108218e-05</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.001064257804534139</v>
+        <v>0.001064257804534138</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.0003189893933449249</v>
+        <v>0.0003189893933449248</v>
       </c>
       <c r="DM6" t="n">
         <v>0.0001161518803692998</v>
@@ -3653,73 +3653,73 @@
         <v>3.071635165533999e-05</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.0009615572421100846</v>
+        <v>0.0009615572421100841</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.07581372615487005</v>
+        <v>0.07581372615487002</v>
       </c>
       <c r="DQ6" t="n">
-        <v>1.034858085341082e-05</v>
+        <v>1.034858085341081e-05</v>
       </c>
       <c r="DR6" t="n">
-        <v>9.938606093281591e-05</v>
+        <v>9.938606093281587e-05</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.003129998497811821</v>
+        <v>0.00312999849781182</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.001772297936858553</v>
+        <v>0.001772297936858552</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.003615452291658844</v>
+        <v>0.003615452291658843</v>
       </c>
       <c r="DV6" t="n">
-        <v>8.571568568734518e-05</v>
+        <v>8.571568568734515e-05</v>
       </c>
       <c r="DW6" t="n">
         <v>0.0003307579825897911</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.0008145095895362592</v>
+        <v>0.0008145095895362588</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.0002220324034119361</v>
+        <v>0.000222032403411936</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.0001935972120078755</v>
+        <v>0.0001935972120078754</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.0004171336797433172</v>
+        <v>0.0004171336797433171</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.0002534792228651192</v>
+        <v>0.0002534792228651191</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.005498616458218948</v>
+        <v>0.005498616458218947</v>
       </c>
       <c r="ED6" t="n">
         <v>1.131372619051006e-05</v>
       </c>
       <c r="EE6" t="n">
-        <v>8.012324544205515e-05</v>
+        <v>8.012324544205513e-05</v>
       </c>
       <c r="EF6" t="n">
-        <v>4.915847761438418e-06</v>
+        <v>4.915847761438416e-06</v>
       </c>
       <c r="EG6" t="n">
-        <v>9.491487454593311e-05</v>
+        <v>9.491487454593307e-05</v>
       </c>
       <c r="EH6" t="n">
-        <v>4.020648351617218e-05</v>
+        <v>4.020648351617216e-05</v>
       </c>
       <c r="EI6" t="n">
-        <v>2.896654366541917e-05</v>
+        <v>2.896654366541915e-05</v>
       </c>
       <c r="EJ6" t="n">
-        <v>4.513677188067991e-05</v>
+        <v>4.51367718806799e-05</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.9760304097609779</v>
+        <v>0.9760304097609782</v>
       </c>
       <c r="EL6" t="inlineStr">
         <is>
@@ -3810,25 +3810,25 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4512088687422479</v>
+        <v>0.4512088687422486</v>
       </c>
       <c r="C7" t="n">
-        <v>0.000729645546505433</v>
+        <v>0.0007296455465054329</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0006821625563865076</v>
+        <v>0.000682162556386508</v>
       </c>
       <c r="E7" t="n">
         <v>0.01116522728610826</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2574374059033813</v>
+        <v>0.2574374059033803</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5881230487205842</v>
+        <v>0.5881230487205847</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3024792976751285</v>
+        <v>0.3024792976751283</v>
       </c>
       <c r="I7" t="n">
         <v>0.09046949771030434</v>
@@ -3843,25 +3843,25 @@
         <v>0.02573062721388295</v>
       </c>
       <c r="M7" t="n">
-        <v>0.00321457763481158</v>
+        <v>0.003214577634811579</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02099467207685321</v>
+        <v>0.0209946720768532</v>
       </c>
       <c r="O7" t="n">
         <v>0.005505219917798488</v>
       </c>
       <c r="P7" t="n">
-        <v>0.003699955521931143</v>
+        <v>0.003699955521931142</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.005330180751681558</v>
+        <v>0.002981649953652854</v>
       </c>
       <c r="R7" t="n">
-        <v>0.004714260085010939</v>
+        <v>0.00471426008501094</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003910361819797151</v>
+        <v>0.003910361819797152</v>
       </c>
       <c r="T7" t="n">
         <v>0.01388764138730869</v>
@@ -3879,10 +3879,10 @@
         <v>0.0003261793016035722</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.00401308279098334</v>
+        <v>0.004013082790983339</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.00224417209371354</v>
+        <v>0.002244172093713539</v>
       </c>
       <c r="AA7" t="n">
         <v>0.02289387107701318</v>
@@ -3891,7 +3891,7 @@
         <v>0.0006848128999392874</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.02594043055284689</v>
+        <v>0.02594043055284687</v>
       </c>
       <c r="AD7" t="n">
         <v>4.884138244872699e-05</v>
@@ -3900,7 +3900,7 @@
         <v>1.110510761988632e-05</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.05922247508711111</v>
+        <v>0.05922247508711113</v>
       </c>
       <c r="AG7" t="n">
         <v>0.03584183200582444</v>
@@ -3924,10 +3924,10 @@
         <v>0.0003128133575532776</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.0002579357859064336</v>
+        <v>0.0002579357859064337</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.0007408390812711942</v>
+        <v>0.0007408390812711941</v>
       </c>
       <c r="AP7" t="n">
         <v>0.0005471863218728763</v>
@@ -3948,16 +3948,16 @@
         <v>0.0003524624301213608</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.003174735619087906</v>
+        <v>0.003174735619087907</v>
       </c>
       <c r="AW7" t="n">
         <v>0.002955062960795952</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0002416101699192543</v>
+        <v>0.0002416101699192542</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.02679733946509781</v>
+        <v>0.0267973394650978</v>
       </c>
       <c r="AZ7" t="n">
         <v>0.0006728257790560733</v>
@@ -3975,7 +3975,7 @@
         <v>0.02179742698384157</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.0004147373625067788</v>
+        <v>0.0004147373625067786</v>
       </c>
       <c r="BF7" t="n">
         <v>0.0005474327035618077</v>
@@ -3993,7 +3993,7 @@
         <v>0.0001375810939115557</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.01915456682004773</v>
+        <v>0.01915456682004774</v>
       </c>
       <c r="BL7" t="n">
         <v>6.627433425225078e-05</v>
@@ -4011,7 +4011,7 @@
         <v>0.0002278380859693068</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.0004470505037050659</v>
+        <v>0.0004470505037050658</v>
       </c>
       <c r="BR7" t="n">
         <v>0.0001530673755720467</v>
@@ -4020,7 +4020,7 @@
         <v>0.02432615682297292</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.004306153892978661</v>
+        <v>0.00430615389297866</v>
       </c>
       <c r="BU7" t="n">
         <v>0.003628611241928438</v>
@@ -4041,7 +4041,7 @@
         <v>0.005234130413610691</v>
       </c>
       <c r="CA7" t="n">
-        <v>7.018585448767362e-05</v>
+        <v>7.018585448767363e-05</v>
       </c>
       <c r="CB7" t="n">
         <v>0.0002766740289433301</v>
@@ -4068,13 +4068,13 @@
         <v>7.577190797293083e-05</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.006189827850683231</v>
+        <v>0.006189827850683229</v>
       </c>
       <c r="CK7" t="n">
         <v>7.173158778315475e-06</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.0003920728963800897</v>
+        <v>0.0003920728963800896</v>
       </c>
       <c r="CM7" t="n">
         <v>1.879690236546644e-05</v>
@@ -4098,7 +4098,7 @@
         <v>5.676328476822275e-05</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.0001685847910219153</v>
+        <v>0.0001685847910219154</v>
       </c>
       <c r="CU7" t="n">
         <v>9.118132404188215e-05</v>
@@ -4107,7 +4107,7 @@
         <v>0.0003422272076665877</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.0003077211116929092</v>
+        <v>0.0003077211116929093</v>
       </c>
       <c r="CX7" t="n">
         <v>0.003766102357410377</v>
@@ -4119,7 +4119,7 @@
         <v>0.0001803329831529484</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.0002296314162457405</v>
+        <v>0.0002296314162457404</v>
       </c>
       <c r="DB7" t="n">
         <v>0.0004491181097675201</v>
@@ -4128,7 +4128,7 @@
         <v>0.0001167440199967674</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.00130084784089735</v>
+        <v>0.001300847840897349</v>
       </c>
       <c r="DE7" t="n">
         <v>1.020652109401776e-05</v>
@@ -4137,7 +4137,7 @@
         <v>0.0003368678465904926</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.005640154976530079</v>
+        <v>0.005640154976530075</v>
       </c>
       <c r="DH7" t="n">
         <v>0.0003976638085500405</v>
@@ -4146,7 +4146,7 @@
         <v>0.000100416437033503</v>
       </c>
       <c r="DJ7" t="n">
-        <v>6.711676852233647e-05</v>
+        <v>6.711676852233648e-05</v>
       </c>
       <c r="DK7" t="n">
         <v>0.0008727259950441484</v>
@@ -4161,7 +4161,7 @@
         <v>2.274274325243181e-05</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.000706821198163366</v>
+        <v>0.0007068211981633659</v>
       </c>
       <c r="DP7" t="n">
         <v>0.08225486092525927</v>
@@ -4188,13 +4188,13 @@
         <v>0.0002421559554248663</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.0004524944138670601</v>
+        <v>0.00045249441386706</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.0002223111673012862</v>
+        <v>0.0002223111673012861</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.0001416230246961461</v>
+        <v>0.000141623024696146</v>
       </c>
       <c r="EA7" t="n">
         <v>0.0003091519681715799</v>
@@ -4218,7 +4218,7 @@
         <v>7.233880403028733e-05</v>
       </c>
       <c r="EH7" t="n">
-        <v>2.570755751536342e-05</v>
+        <v>2.570755751536343e-05</v>
       </c>
       <c r="EI7" t="n">
         <v>2.112448643991745e-05</v>
@@ -4318,424 +4318,424 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.4185874707716742</v>
+        <v>0.418587470771675</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0009182979219400753</v>
+        <v>0.0009182979219400767</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0008646926985152683</v>
+        <v>0.0008646926985152696</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01257891601691838</v>
+        <v>0.0125789160169184</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2420739616294409</v>
+        <v>0.2420739616294412</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5603785905562932</v>
+        <v>0.5603785905562939</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2665094618397649</v>
+        <v>0.2665094618397651</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07736590648399899</v>
+        <v>0.07736590648399912</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03054117140331474</v>
+        <v>0.03054117140331479</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1094202738713886</v>
+        <v>0.1094202738713888</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0349557020052672</v>
+        <v>0.03495570200526722</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005832361432074206</v>
+        <v>0.005832361432074214</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02245896656909779</v>
+        <v>0.02245896656909782</v>
       </c>
       <c r="O8" t="n">
-        <v>0.00501597224756269</v>
+        <v>0.005015972247562697</v>
       </c>
       <c r="P8" t="n">
-        <v>0.005792914826887284</v>
+        <v>0.005792914826887294</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.00856179080204846</v>
+        <v>0.004076456503138364</v>
       </c>
       <c r="R8" t="n">
-        <v>0.006855887057705695</v>
+        <v>0.006855887057705704</v>
       </c>
       <c r="S8" t="n">
-        <v>0.005095442367488779</v>
+        <v>0.005095442367488789</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01456310661122788</v>
+        <v>0.01456310661122791</v>
       </c>
       <c r="U8" t="n">
-        <v>3.196061731174844e-05</v>
+        <v>3.196061731174848e-05</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001826443480112325</v>
+        <v>0.001826443480112328</v>
       </c>
       <c r="W8" t="n">
-        <v>0.05804575346060426</v>
+        <v>0.05804575346060437</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0003969114223776121</v>
+        <v>0.0003969114223776127</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.003705618171910457</v>
+        <v>0.003705618171910461</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.003733877196616809</v>
+        <v>0.003733877196616815</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02445430028984909</v>
+        <v>0.02445430028984913</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0008665426211706415</v>
+        <v>0.0008665426211706423</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.03310241668819731</v>
+        <v>0.03310241668819737</v>
       </c>
       <c r="AD8" t="n">
-        <v>4.859171621027023e-05</v>
+        <v>4.859171621027031e-05</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.282288369708415e-05</v>
+        <v>1.282288369708417e-05</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0548146713518688</v>
+        <v>0.05481467135186887</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.03515864598957492</v>
+        <v>0.03515864598957496</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.002053349307396323</v>
+        <v>0.002053349307396326</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0014194851335409</v>
+        <v>0.001419485133540903</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.002877338380008577</v>
+        <v>0.002877338380008581</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.01951746144543203</v>
+        <v>0.01951746144543206</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0009178527375708037</v>
+        <v>0.0009178527375708057</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0003989387867221434</v>
+        <v>0.0003989387867221441</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.0003177212584909771</v>
+        <v>0.0003177212584909776</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.0006177232733068818</v>
+        <v>0.0006177232733068826</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0005141124502169301</v>
+        <v>0.0005141124502169308</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.001529182633522035</v>
+        <v>0.001529182633522038</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.007245729782458282</v>
+        <v>0.007245729782458294</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.0001637749903268359</v>
+        <v>0.0001637749903268361</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.495240889889956e-05</v>
+        <v>8.495240889889961e-05</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.000419808839330227</v>
+        <v>0.0004198088393302277</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.003792155694872007</v>
+        <v>0.003792155694872013</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.003953502031771572</v>
+        <v>0.003953502031771578</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0002691290903528688</v>
+        <v>0.0002691290903528692</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.03092193403290283</v>
+        <v>0.03092193403290288</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.0008044312323735831</v>
+        <v>0.0008044312323735844</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.961741918484205e-05</v>
+        <v>9.961741918484221e-05</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.04155325052245558</v>
+        <v>0.04155325052245565</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.009546392941887702</v>
+        <v>0.009546392941887716</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.03114882908089268</v>
+        <v>0.03114882908089272</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.0004879574728392893</v>
+        <v>0.0004879574728392899</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.0008422914445381055</v>
+        <v>0.000842291444538107</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.001102754645701424</v>
+        <v>0.001102754645701425</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.02026350484763654</v>
+        <v>0.02026350484763656</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0005591894142024214</v>
+        <v>0.000559189414202422</v>
       </c>
       <c r="BJ8" t="n">
-        <v>4.778988036757449e-06</v>
+        <v>4.778988036757456e-06</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.01727514885387627</v>
+        <v>0.0172751488538763</v>
       </c>
       <c r="BL8" t="n">
-        <v>7.587271765914685e-05</v>
+        <v>7.587271765914696e-05</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.02704966738291015</v>
+        <v>0.02704966738291019</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.001786668846033129</v>
+        <v>0.001786668846033132</v>
       </c>
       <c r="BO8" t="n">
-        <v>6.398629006414612e-05</v>
+        <v>6.39862900641462e-05</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0002915317364965984</v>
+        <v>0.0002915317364965989</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.0005019102571873975</v>
+        <v>0.0005019102571873983</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.0002064377192702194</v>
+        <v>0.0002064377192702198</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.0286893967721906</v>
+        <v>0.02868939677219064</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.005601280858091071</v>
+        <v>0.005601280858091078</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.003942398452163197</v>
+        <v>0.003942398452163203</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.003728086787280035</v>
+        <v>0.00372808678728004</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.97568254422909e-06</v>
+        <v>9.975682544229105e-06</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.002589003894222869</v>
+        <v>0.002589003894222873</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.935463151683942e-05</v>
+        <v>9.935463151683957e-05</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.006261692918330436</v>
+        <v>0.006261692918330446</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.0001172876929700365</v>
+        <v>0.0001172876929700367</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0003382253801087039</v>
+        <v>0.0003382253801087044</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.0001159194207873469</v>
+        <v>0.0001159194207873472</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.0001872214042859456</v>
+        <v>0.0001872214042859459</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.007279134879733542</v>
+        <v>0.007279134879733553</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.001208180454770268</v>
+        <v>0.00120818045477027</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.004630124880982715</v>
+        <v>0.004630124880982721</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0004901590318621084</v>
+        <v>0.0004901590318621091</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.0001349790568316243</v>
+        <v>0.0001349790568316245</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.008994925818108627</v>
+        <v>0.008994925818108641</v>
       </c>
       <c r="CK8" t="n">
-        <v>8.918499860381597e-06</v>
+        <v>8.918499860381611e-06</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.0004547532637707502</v>
+        <v>0.0004547532637707508</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.568389699582835e-05</v>
+        <v>2.568389699582839e-05</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.000212143546922692</v>
+        <v>0.0002121435469226924</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.001462287738870989</v>
+        <v>0.001462287738870991</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.0008086051421775624</v>
+        <v>0.0008086051421775637</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.0010716183696145</v>
+        <v>0.001071618369614502</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.0005772208703116492</v>
+        <v>0.0005772208703116501</v>
       </c>
       <c r="CS8" t="n">
-        <v>8.392174428003303e-05</v>
+        <v>8.392174428003317e-05</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.0002059257995501268</v>
+        <v>0.0002059257995501271</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.000115953559111907</v>
+        <v>0.0001159535591119071</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.0003865187223967765</v>
+        <v>0.0003865187223967771</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.0004735773807275566</v>
+        <v>0.0004735773807275574</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.003969444865231082</v>
+        <v>0.003969444865231088</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.0001313501623837471</v>
+        <v>0.0001313501623837473</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.0002621734757694375</v>
+        <v>0.000262173475769438</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.000301689152101585</v>
+        <v>0.0003016891521015855</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.0005236531152600403</v>
+        <v>0.0005236531152600411</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.0001135563554548111</v>
+        <v>0.0001135563554548113</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.001441824689007381</v>
+        <v>0.001441824689007383</v>
       </c>
       <c r="DE8" t="n">
-        <v>8.887681861744466e-06</v>
+        <v>8.887681861744479e-06</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.0004865141747124761</v>
+        <v>0.0004865141747124769</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.00615401198298411</v>
+        <v>0.00615401198298412</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.0004619320225859645</v>
+        <v>0.0004619320225859652</v>
       </c>
       <c r="DI8" t="n">
-        <v>8.837917000834815e-05</v>
+        <v>8.837917000834829e-05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>5.505224729798111e-05</v>
+        <v>5.505224729798119e-05</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.001104272551395457</v>
+        <v>0.001104272551395459</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.0002905561949696736</v>
+        <v>0.0002905561949696741</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.0002104684940903178</v>
+        <v>0.0002104684940903181</v>
       </c>
       <c r="DN8" t="n">
-        <v>3.58798571110611e-05</v>
+        <v>3.587985711106116e-05</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.001105469475121426</v>
+        <v>0.001105469475121428</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.08960722933550004</v>
+        <v>0.08960722933550018</v>
       </c>
       <c r="DQ8" t="n">
-        <v>7.635395976985982e-06</v>
+        <v>7.635395976985993e-06</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.461491645797574e-05</v>
+        <v>8.461491645797586e-05</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.003316283066055466</v>
+        <v>0.003316283066055471</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.001466811591181674</v>
+        <v>0.001466811591181676</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.003711888286404482</v>
+        <v>0.003711888286404488</v>
       </c>
       <c r="DV8" t="n">
-        <v>8.636757879583031e-05</v>
+        <v>8.636757879583045e-05</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0003730503173947233</v>
+        <v>0.0003730503173947239</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.0007634818975727921</v>
+        <v>0.0007634818975727933</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.0002646861951934606</v>
+        <v>0.000264686195193461</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.000198008284222198</v>
+        <v>0.0001980082842221983</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.000417939639297417</v>
+        <v>0.0004179396392974176</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.0002683390819392805</v>
+        <v>0.000268339081939281</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.005892593751221537</v>
+        <v>0.005892593751221547</v>
       </c>
       <c r="ED8" t="n">
-        <v>9.325579665987011e-06</v>
+        <v>9.325579665987024e-06</v>
       </c>
       <c r="EE8" t="n">
-        <v>7.316567849146406e-05</v>
+        <v>7.316567849146417e-05</v>
       </c>
       <c r="EF8" t="n">
-        <v>3.85411824550084e-06</v>
+        <v>3.854118245500846e-06</v>
       </c>
       <c r="EG8" t="n">
-        <v>8.159689207490149e-05</v>
+        <v>8.159689207490162e-05</v>
       </c>
       <c r="EH8" t="n">
-        <v>3.930680540322751e-05</v>
+        <v>3.930680540322757e-05</v>
       </c>
       <c r="EI8" t="n">
-        <v>2.859634109038066e-05</v>
+        <v>2.85963410903807e-05</v>
       </c>
       <c r="EJ8" t="n">
-        <v>3.66993010686303e-05</v>
+        <v>3.669930106863036e-05</v>
       </c>
       <c r="EK8" t="n">
-        <v>1.428537871252159</v>
+        <v>1.428537871252156</v>
       </c>
       <c r="EL8" t="inlineStr">
         <is>
@@ -4826,25 +4826,25 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4206230090933055</v>
+        <v>0.4206230090933053</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0008861545834932984</v>
+        <v>0.0008861545834932986</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0008390192501406715</v>
+        <v>0.0008390192501406716</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01247913185216071</v>
+        <v>0.01247913185216072</v>
       </c>
       <c r="F9" t="n">
         <v>0.2471561411295324</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5584154370198481</v>
+        <v>0.558415437019847</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2701226509151341</v>
+        <v>0.2701226509151339</v>
       </c>
       <c r="I9" t="n">
         <v>0.07900965566410829</v>
@@ -4856,7 +4856,7 @@
         <v>0.1099627838772212</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03457142741800372</v>
+        <v>0.03457142741800378</v>
       </c>
       <c r="M9" t="n">
         <v>0.005481639076710339</v>
@@ -4865,19 +4865,19 @@
         <v>0.02218574555128189</v>
       </c>
       <c r="O9" t="n">
-        <v>0.005074721046069027</v>
+        <v>0.005074721046069028</v>
       </c>
       <c r="P9" t="n">
         <v>0.005538328073384968</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.008178306797290607</v>
+        <v>0.004015573468840234</v>
       </c>
       <c r="R9" t="n">
-        <v>0.006605363965043277</v>
+        <v>0.006605363965043275</v>
       </c>
       <c r="S9" t="n">
-        <v>0.005230095749707736</v>
+        <v>0.005230095749707737</v>
       </c>
       <c r="T9" t="n">
         <v>0.01465627153899893</v>
@@ -4886,106 +4886,106 @@
         <v>3.208849545458228e-05</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001902801944076173</v>
+        <v>0.001902801944076172</v>
       </c>
       <c r="W9" t="n">
-        <v>0.05663733234435006</v>
+        <v>0.0566373323443501</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0003867427853699841</v>
+        <v>0.0003867427853699842</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.003764931573672967</v>
+        <v>0.003764931573672968</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.003550377360484213</v>
+        <v>0.003550377360484214</v>
       </c>
       <c r="AA9" t="n">
         <v>0.02430260618052312</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0008675842159623827</v>
+        <v>0.0008675842159623829</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.03285569065337133</v>
+        <v>0.03285569065337134</v>
       </c>
       <c r="AD9" t="n">
-        <v>5.171796060828524e-05</v>
+        <v>5.171796060828526e-05</v>
       </c>
       <c r="AE9" t="n">
         <v>1.354079471067649e-05</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.05533985609095332</v>
+        <v>0.05533985609095336</v>
       </c>
       <c r="AG9" t="n">
         <v>0.03841670912756601</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.002034546116294713</v>
+        <v>0.002034546116294714</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.001357246287497028</v>
+        <v>0.001357246287497029</v>
       </c>
       <c r="AJ9" t="n">
         <v>0.002919035942770773</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.02009532077634887</v>
+        <v>0.02009532077634888</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0008939568989356217</v>
+        <v>0.0008939568989356219</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0003866345430199421</v>
+        <v>0.0003866345430199422</v>
       </c>
       <c r="AN9" t="n">
         <v>0.0003253531080503999</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.0006109455163645365</v>
+        <v>0.0006109455163645366</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.0004988703066538926</v>
+        <v>0.0004988703066538927</v>
       </c>
       <c r="AQ9" t="n">
         <v>0.00144445030885603</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.007336963951999352</v>
+        <v>0.007336963951999353</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.000162216684470874</v>
+        <v>0.0001622166844708741</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.738001686039255e-05</v>
+        <v>8.738001686039265e-05</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.0004064401179867325</v>
+        <v>0.0004064401179867326</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.00370079472983485</v>
+        <v>0.003700794729834851</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.003839133010820785</v>
+        <v>0.003839133010820786</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0002821960810717486</v>
+        <v>0.0002821960810717487</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.03069738614254763</v>
+        <v>0.03069738614254762</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.0008079864315854585</v>
+        <v>0.0008079864315854586</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.464275449122245e-05</v>
+        <v>9.464275449122239e-05</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.03927097684150835</v>
+        <v>0.03927097684150838</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.009638331446216694</v>
+        <v>0.009638331446216696</v>
       </c>
       <c r="BD9" t="n">
         <v>0.03080030862609279</v>
@@ -4994,7 +4994,7 @@
         <v>0.0005464423400826754</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.0008283976088964431</v>
+        <v>0.0008283976088964433</v>
       </c>
       <c r="BG9" t="n">
         <v>0.00123571626574189</v>
@@ -5003,25 +5003,25 @@
         <v>0.02088968558715002</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.0005530355400359759</v>
+        <v>0.000553035540035976</v>
       </c>
       <c r="BJ9" t="n">
         <v>0.0001984838200449529</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.01807001660112404</v>
+        <v>0.01807001660112405</v>
       </c>
       <c r="BL9" t="n">
-        <v>7.746115098640579e-05</v>
+        <v>7.74611509864058e-05</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.02744036884264833</v>
+        <v>0.02744036884264834</v>
       </c>
       <c r="BN9" t="n">
         <v>0.001771729597464905</v>
       </c>
       <c r="BO9" t="n">
-        <v>6.284282435804147e-05</v>
+        <v>6.284282435804148e-05</v>
       </c>
       <c r="BP9" t="n">
         <v>0.0002706966659756605</v>
@@ -5036,16 +5036,16 @@
         <v>0.02901067621456173</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.005379728394837002</v>
+        <v>0.005379728394837</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.003743452435176627</v>
+        <v>0.003743452435176628</v>
       </c>
       <c r="BV9" t="n">
         <v>0.003755422488185731</v>
       </c>
       <c r="BW9" t="n">
-        <v>9.521104269836174e-06</v>
+        <v>9.521104269836176e-06</v>
       </c>
       <c r="BX9" t="n">
         <v>0.002562713718571358</v>
@@ -5054,28 +5054,28 @@
         <v>0.0001002374466436981</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.006652324590659373</v>
+        <v>0.006652324590659374</v>
       </c>
       <c r="CA9" t="n">
         <v>0.000120020768916203</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.000340501776407284</v>
+        <v>0.0003405017764072841</v>
       </c>
       <c r="CC9" t="n">
         <v>0.0001165114703230358</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.0001772445490583476</v>
+        <v>0.0001772445490583477</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.007239378611006458</v>
+        <v>0.007239378611006459</v>
       </c>
       <c r="CF9" t="n">
         <v>0.001276952497685258</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.004301071270503579</v>
+        <v>0.00430107127050358</v>
       </c>
       <c r="CH9" t="n">
         <v>0.0005058538204923151</v>
@@ -5084,16 +5084,16 @@
         <v>0.000105131592714</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.007712362303394356</v>
+        <v>0.007712362303394358</v>
       </c>
       <c r="CK9" t="n">
-        <v>9.298743096496996e-06</v>
+        <v>9.298743096496997e-06</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.0005142752676663607</v>
+        <v>0.0005142752676663608</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.473825696082727e-05</v>
+        <v>2.473825696082728e-05</v>
       </c>
       <c r="CN9" t="n">
         <v>0.0002249550186030346</v>
@@ -5108,37 +5108,37 @@
         <v>0.001079676578914765</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.0006241783273996556</v>
+        <v>0.0006241783273996558</v>
       </c>
       <c r="CS9" t="n">
-        <v>8.467774710673943e-05</v>
+        <v>8.467774710673945e-05</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.0001941249192287875</v>
+        <v>0.0001941249192287876</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.0001223872540965595</v>
+        <v>0.0001223872540965596</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0003829302297349509</v>
+        <v>0.000382930229734951</v>
       </c>
       <c r="CW9" t="n">
         <v>0.0004317382070254632</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.004261356402639937</v>
+        <v>0.004261356402639938</v>
       </c>
       <c r="CY9" t="n">
         <v>0.0001335940481559821</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0002605784200409152</v>
+        <v>0.0002605784200409153</v>
       </c>
       <c r="DA9" t="n">
         <v>0.0003087262306103854</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.0005197055237990333</v>
+        <v>0.0005197055237990334</v>
       </c>
       <c r="DC9" t="n">
         <v>0.0001200091853552031</v>
@@ -5147,10 +5147,10 @@
         <v>0.001492433081800799</v>
       </c>
       <c r="DE9" t="n">
-        <v>9.914575114237189e-06</v>
+        <v>9.91457511423719e-06</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.0004720250126189642</v>
+        <v>0.0004720250126189643</v>
       </c>
       <c r="DG9" t="n">
         <v>0.006020903563259796</v>
@@ -5159,58 +5159,58 @@
         <v>0.0005201630302955506</v>
       </c>
       <c r="DI9" t="n">
-        <v>8.954577866067325e-05</v>
+        <v>8.954577866067328e-05</v>
       </c>
       <c r="DJ9" t="n">
-        <v>5.388600886628509e-05</v>
+        <v>5.38860088662851e-05</v>
       </c>
       <c r="DK9" t="n">
         <v>0.00112876847831033</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.0002821323570914248</v>
+        <v>0.0002821323570914249</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.0001803365840873641</v>
+        <v>0.0001803365840873642</v>
       </c>
       <c r="DN9" t="n">
-        <v>3.762604587046796e-05</v>
+        <v>3.762604587046797e-05</v>
       </c>
       <c r="DO9" t="n">
         <v>0.001102041170522931</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.08812788461993747</v>
+        <v>0.08812788461993748</v>
       </c>
       <c r="DQ9" t="n">
-        <v>7.591238229265887e-06</v>
+        <v>7.591238229265889e-06</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.110347342272652e-05</v>
+        <v>9.110347342272654e-05</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.003444699056094736</v>
+        <v>0.003444699056094737</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.001456093857529799</v>
+        <v>0.0014560938575298</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.003447447219291095</v>
+        <v>0.003447447219291096</v>
       </c>
       <c r="DV9" t="n">
-        <v>9.4808575618102e-05</v>
+        <v>9.480857561810202e-05</v>
       </c>
       <c r="DW9" t="n">
         <v>0.0003661441393884099</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0006899229174348936</v>
+        <v>0.0006899229174348937</v>
       </c>
       <c r="DY9" t="n">
         <v>0.0002644892628782009</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.0001980238905267615</v>
+        <v>0.0001980238905267616</v>
       </c>
       <c r="EA9" t="n">
         <v>0.0004150350141639595</v>
@@ -5219,22 +5219,22 @@
         <v>0.0002593212095877368</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.005958819351875369</v>
+        <v>0.005958819351875371</v>
       </c>
       <c r="ED9" t="n">
-        <v>9.643944624101778e-06</v>
+        <v>9.643944624101788e-06</v>
       </c>
       <c r="EE9" t="n">
-        <v>7.36023491243284e-05</v>
+        <v>7.360234912432841e-05</v>
       </c>
       <c r="EF9" t="n">
-        <v>3.842423521804625e-06</v>
+        <v>3.842423521804626e-06</v>
       </c>
       <c r="EG9" t="n">
         <v>6.86623352261418e-05</v>
       </c>
       <c r="EH9" t="n">
-        <v>3.434640813969186e-05</v>
+        <v>3.434640813969187e-05</v>
       </c>
       <c r="EI9" t="n">
         <v>2.587103487495073e-05</v>
@@ -5334,424 +5334,424 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4224183149283155</v>
+        <v>0.4224183149283141</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0009731771207667356</v>
+        <v>0.0009731771207667321</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0008181621756732727</v>
+        <v>0.0008181621756732704</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0125445729801706</v>
+        <v>0.01254457298017057</v>
       </c>
       <c r="F10" t="n">
-        <v>0.242425979004579</v>
+        <v>0.2424259790045779</v>
       </c>
       <c r="G10" t="n">
-        <v>0.558331092490337</v>
+        <v>0.5583310924903353</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2668216473034422</v>
+        <v>0.2668216473034414</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08078289204983499</v>
+        <v>0.08078289204983476</v>
       </c>
       <c r="J10" t="n">
-        <v>0.03173046446839898</v>
+        <v>0.03173046446839889</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1108189839690889</v>
+        <v>0.1108189839690886</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03610005043046509</v>
+        <v>0.03610005043046501</v>
       </c>
       <c r="M10" t="n">
-        <v>0.006098691506406944</v>
+        <v>0.006098691506406926</v>
       </c>
       <c r="N10" t="n">
-        <v>0.02146263184778546</v>
+        <v>0.0214626318477854</v>
       </c>
       <c r="O10" t="n">
-        <v>0.004566701305922618</v>
+        <v>0.004566701305922606</v>
       </c>
       <c r="P10" t="n">
-        <v>0.005843396852143966</v>
+        <v>0.00584339685214395</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.007265777880520761</v>
+        <v>0.002654386813780169</v>
       </c>
       <c r="R10" t="n">
-        <v>0.00731367006324473</v>
+        <v>0.007313670063244714</v>
       </c>
       <c r="S10" t="n">
-        <v>0.005152783280174681</v>
+        <v>0.005152783280174663</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01477913247216642</v>
+        <v>0.01477913247216638</v>
       </c>
       <c r="U10" t="n">
-        <v>3.195283446445601e-05</v>
+        <v>3.195283446445592e-05</v>
       </c>
       <c r="V10" t="n">
-        <v>0.001883565828390125</v>
+        <v>0.001883565828390118</v>
       </c>
       <c r="W10" t="n">
-        <v>0.05245883400314948</v>
+        <v>0.05245883400314932</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0003696715529890334</v>
+        <v>0.0003696715529890324</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.003936618385454477</v>
+        <v>0.003936618385454465</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.003927550294526613</v>
+        <v>0.003927550294526602</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.02331116474217443</v>
+        <v>0.02331116474217436</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.000880553244149592</v>
+        <v>0.0008805532441495895</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.0352845223875896</v>
+        <v>0.03528452238758948</v>
       </c>
       <c r="AD10" t="n">
-        <v>4.527773046452795e-05</v>
+        <v>4.527773046452781e-05</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.36001569327293e-05</v>
+        <v>1.360015693272927e-05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.05496989529383837</v>
+        <v>0.05496989529383819</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.03541799792337919</v>
+        <v>0.0354179979233791</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.002033741985302728</v>
+        <v>0.002033741985302723</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.001370294402035811</v>
+        <v>0.001370294402035807</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.002914495986741724</v>
+        <v>0.002914495986741715</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.02023254251055912</v>
+        <v>0.02023254251055906</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.0009005478167920223</v>
+        <v>0.0009005478167920197</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.0003771744642404498</v>
+        <v>0.0003771744642404487</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.0003062675937544332</v>
+        <v>0.0003062675937544324</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.00061930771429243</v>
+        <v>0.0006193077142924284</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.0005079866712448635</v>
+        <v>0.0005079866712448621</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.001583712811869542</v>
+        <v>0.001583712811869538</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.007491056713606628</v>
+        <v>0.007491056713606608</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.0001781226744022355</v>
+        <v>0.000178122674402235</v>
       </c>
       <c r="AT10" t="n">
-        <v>8.850361794302431e-05</v>
+        <v>8.850361794302405e-05</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.0003418303309742502</v>
+        <v>0.0003418303309742492</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.004250953948004394</v>
+        <v>0.004250953948004382</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.003636454412703787</v>
+        <v>0.003636454412703777</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.0002690710198120019</v>
+        <v>0.0002690710198120011</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.02985257127980491</v>
+        <v>0.02985257127980481</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.0008080001615336799</v>
+        <v>0.0008080001615336776</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.885941869999438e-05</v>
+        <v>9.885941869999409e-05</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.03905999606694455</v>
+        <v>0.03905999606694444</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.009626261157134294</v>
+        <v>0.009626261157134268</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.03246017506296602</v>
+        <v>0.03246017506296595</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.0005062653919237684</v>
+        <v>0.000506265391923767</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.0008451935192772079</v>
+        <v>0.0008451935192772054</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.00110584709710229</v>
+        <v>0.001105847097102288</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.02053384157675798</v>
+        <v>0.02053384157675792</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.0004797574582327135</v>
+        <v>0.0004797574582327121</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.390907258648706e-05</v>
+        <v>1.390907258648702e-05</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.0177508131150068</v>
+        <v>0.01775081311500674</v>
       </c>
       <c r="BL10" t="n">
-        <v>7.525438999177853e-05</v>
+        <v>7.525438999177833e-05</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.02811287951840209</v>
+        <v>0.02811287951840201</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.001749536479925363</v>
+        <v>0.001749536479925358</v>
       </c>
       <c r="BO10" t="n">
-        <v>6.859411962778271e-05</v>
+        <v>6.859411962778252e-05</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.0003012526461364932</v>
+        <v>0.0003012526461364924</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.0004755001180563814</v>
+        <v>0.00047550011805638</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.0002174458233726279</v>
+        <v>0.0002174458233726273</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.02838277124216843</v>
+        <v>0.02838277124216835</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.005754444108481574</v>
+        <v>0.005754444108481556</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.004031524492878664</v>
+        <v>0.004031524492878653</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.003494756723867277</v>
+        <v>0.003494756723867267</v>
       </c>
       <c r="BW10" t="n">
-        <v>9.565092530312235e-06</v>
+        <v>9.565092530312208e-06</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.002604902053818582</v>
+        <v>0.002604902053818574</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.0001006079352047671</v>
+        <v>0.0001006079352047669</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.008090933752555157</v>
+        <v>0.008090933752555133</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.0001256060188514192</v>
+        <v>0.0001256060188514189</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.0003194197344847168</v>
+        <v>0.0003194197344847159</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.0001197999713527574</v>
+        <v>0.0001197999713527569</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.000187088570063471</v>
+        <v>0.0001870885700634705</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.007148207512631613</v>
+        <v>0.007148207512631593</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.001184034169540992</v>
+        <v>0.001184034169540988</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.004767333586638608</v>
+        <v>0.004767333586638595</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.0004804863598406772</v>
+        <v>0.000480486359840676</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.0001344048853553475</v>
+        <v>0.0001344048853553472</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.008580245825197702</v>
+        <v>0.008580245825197678</v>
       </c>
       <c r="CK10" t="n">
-        <v>9.593521988830433e-06</v>
+        <v>9.593521988830406e-06</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.0004718884182203335</v>
+        <v>0.0004718884182203322</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.583608757101105e-05</v>
+        <v>2.583608757101097e-05</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.0002296812786545581</v>
+        <v>0.0002296812786545574</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.00132904007450485</v>
+        <v>0.001329040074504846</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.0008654116170708709</v>
+        <v>0.0008654116170708684</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.001126456309141461</v>
+        <v>0.001126456309141458</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.0006226681561362795</v>
+        <v>0.0006226681561362778</v>
       </c>
       <c r="CS10" t="n">
-        <v>8.505491759945778e-05</v>
+        <v>8.505491759945753e-05</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.0002025330533468306</v>
+        <v>0.00020253305334683</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.0001117937682366517</v>
+        <v>0.0001117937682366513</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.0003754577264816678</v>
+        <v>0.0003754577264816668</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.0005011393458739697</v>
+        <v>0.0005011393458739683</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.004118925798625317</v>
+        <v>0.004118925798625305</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.0001327815171343886</v>
+        <v>0.0001327815171343882</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.0002682017299453542</v>
+        <v>0.0002682017299453534</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.0002963172412260385</v>
+        <v>0.0002963172412260377</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.0005130964019832039</v>
+        <v>0.0005130964019832024</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.0001171456798137446</v>
+        <v>0.0001171456798137443</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.001486520842079869</v>
+        <v>0.001486520842079865</v>
       </c>
       <c r="DE10" t="n">
-        <v>8.999166901350645e-06</v>
+        <v>8.999166901350619e-06</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.0004822603137053306</v>
+        <v>0.0004822603137053292</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.006207471292888288</v>
+        <v>0.006207471292888271</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.000479813772761703</v>
+        <v>0.0004798137727617018</v>
       </c>
       <c r="DI10" t="n">
-        <v>8.508608771697038e-05</v>
+        <v>8.508608771697014e-05</v>
       </c>
       <c r="DJ10" t="n">
-        <v>5.874514354711446e-05</v>
+        <v>5.874514354711429e-05</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.001132270706881734</v>
+        <v>0.00113227070688173</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.0002979893456883849</v>
+        <v>0.000297989345688384</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.0002095913366250654</v>
+        <v>0.0002095913366250648</v>
       </c>
       <c r="DN10" t="n">
-        <v>3.271250636896177e-05</v>
+        <v>3.271250636896168e-05</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.001136243286093226</v>
+        <v>0.001136243286093224</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.08525067786572045</v>
+        <v>0.0852506778657202</v>
       </c>
       <c r="DQ10" t="n">
-        <v>7.702385588332861e-06</v>
+        <v>7.702385588332839e-06</v>
       </c>
       <c r="DR10" t="n">
-        <v>9.6896916094861e-05</v>
+        <v>9.689691609486071e-05</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.003380988911157813</v>
+        <v>0.003380988911157804</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.001691869639363836</v>
+        <v>0.001691869639363831</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.003890576237390472</v>
+        <v>0.003890576237390461</v>
       </c>
       <c r="DV10" t="n">
-        <v>8.564667677345881e-05</v>
+        <v>8.564667677345856e-05</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.0003878465813253056</v>
+        <v>0.0003878465813253044</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.0007773268213553178</v>
+        <v>0.0007773268213553157</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.000254587269969222</v>
+        <v>0.0002545872699692213</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.0002131062271508131</v>
+        <v>0.0002131062271508125</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.0004215291283359198</v>
+        <v>0.0004215291283359186</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.000261828937378869</v>
+        <v>0.0002618289373788682</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.005681897934782785</v>
+        <v>0.005681897934782769</v>
       </c>
       <c r="ED10" t="n">
-        <v>7.725339143622216e-06</v>
+        <v>7.725339143622194e-06</v>
       </c>
       <c r="EE10" t="n">
-        <v>7.27774545625532e-05</v>
+        <v>7.277745456255302e-05</v>
       </c>
       <c r="EF10" t="n">
-        <v>4.567730043560163e-06</v>
+        <v>4.56773004356015e-06</v>
       </c>
       <c r="EG10" t="n">
-        <v>9.098495134581753e-05</v>
+        <v>9.098495134581728e-05</v>
       </c>
       <c r="EH10" t="n">
-        <v>3.926780325619684e-05</v>
+        <v>3.926780325619673e-05</v>
       </c>
       <c r="EI10" t="n">
-        <v>2.794455247663429e-05</v>
+        <v>2.794455247663421e-05</v>
       </c>
       <c r="EJ10" t="n">
-        <v>3.627131720215831e-05</v>
+        <v>3.627131720215821e-05</v>
       </c>
       <c r="EK10" t="n">
-        <v>1.239796368527286</v>
+        <v>1.23979636852729</v>
       </c>
       <c r="EL10" t="inlineStr">
         <is>
@@ -5842,424 +5842,424 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3927613042226931</v>
+        <v>0.3927613042226921</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0009001040096423587</v>
+        <v>0.0009001040096423579</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0008305757230112748</v>
+        <v>0.0008305757230112727</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01313612873128284</v>
+        <v>0.01313612873128282</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2168672546525009</v>
+        <v>0.2168672546525004</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5621063130926708</v>
+        <v>0.5621063130926709</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2271299957274628</v>
+        <v>0.2271299957274625</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0630458811484674</v>
+        <v>0.06304588114846731</v>
       </c>
       <c r="J11" t="n">
-        <v>0.03050113451124808</v>
+        <v>0.03050113451124803</v>
       </c>
       <c r="K11" t="n">
-        <v>0.08428064805080884</v>
+        <v>0.0842806480508087</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03615107707992395</v>
+        <v>0.03615107707992389</v>
       </c>
       <c r="M11" t="n">
-        <v>0.006119210245762084</v>
+        <v>0.006119210245762075</v>
       </c>
       <c r="N11" t="n">
-        <v>0.020706359709996</v>
+        <v>0.02070635970999598</v>
       </c>
       <c r="O11" t="n">
-        <v>0.004174605431637816</v>
+        <v>0.004174605431637808</v>
       </c>
       <c r="P11" t="n">
-        <v>0.00621920604839001</v>
+        <v>0.006219206048390001</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.008609782022464625</v>
+        <v>0.004025580911326662</v>
       </c>
       <c r="R11" t="n">
-        <v>0.007130942413629641</v>
+        <v>0.007130942413629629</v>
       </c>
       <c r="S11" t="n">
-        <v>0.005285492137918932</v>
+        <v>0.005285492137918919</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01571429964967857</v>
+        <v>0.01571429964967856</v>
       </c>
       <c r="U11" t="n">
-        <v>3.191156495598179e-05</v>
+        <v>3.191156495598174e-05</v>
       </c>
       <c r="V11" t="n">
-        <v>0.001915841828425005</v>
+        <v>0.001915841828425003</v>
       </c>
       <c r="W11" t="n">
-        <v>0.04213679849349709</v>
+        <v>0.04213679849349703</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0003713405638182861</v>
+        <v>0.0003713405638182854</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.00401253850174765</v>
+        <v>0.004012538501747644</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.004022306898270747</v>
+        <v>0.004022306898270739</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.0279955435465396</v>
+        <v>0.02799554354653955</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.0008599745103255551</v>
+        <v>0.0008599745103255537</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.03443275662752714</v>
+        <v>0.03443275662752709</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.457734340344005e-05</v>
+        <v>4.457734340343997e-05</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.325747948049829e-05</v>
+        <v>1.325747948049826e-05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.05760200694387686</v>
+        <v>0.05760200694387677</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.02849765431307862</v>
+        <v>0.02849765431307858</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.002064999519383479</v>
+        <v>0.002064999519383474</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.001330297068098717</v>
+        <v>0.001330297068098715</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.002877478242600884</v>
+        <v>0.00287747824260088</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.0197396477769612</v>
+        <v>0.01973964777696118</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.0009300757349534783</v>
+        <v>0.0009300757349534767</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.0004027652107424812</v>
+        <v>0.0004027652107424805</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.00032384043371095</v>
+        <v>0.0003238404337109494</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.0007277565025931612</v>
+        <v>0.00072775650259316</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.0006170387923389534</v>
+        <v>0.0006170387923389525</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.001570538545976574</v>
+        <v>0.001570538545976571</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.007605122230494715</v>
+        <v>0.007605122230494702</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.0001733944772282221</v>
+        <v>0.0001733944772282218</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.208110753530205e-05</v>
+        <v>8.208110753530191e-05</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.0003995464359297444</v>
+        <v>0.0003995464359297436</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.003859721402552269</v>
+        <v>0.003859721402552262</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.003987252068719941</v>
+        <v>0.003987252068719934</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.0002994552230864008</v>
+        <v>0.0002994552230864004</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.03680807347342493</v>
+        <v>0.03680807347342486</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.0008122347629909497</v>
+        <v>0.0008122347629909483</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.75565242763699e-05</v>
+        <v>9.755652427636974e-05</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.03641294508856616</v>
+        <v>0.03641294508856611</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.008740826116006363</v>
+        <v>0.008740826116006347</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.03414532986281129</v>
+        <v>0.03414532986281123</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.0004949413218739314</v>
+        <v>0.0004949413218739305</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.000870408766239314</v>
+        <v>0.0008704087662393125</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.001141862375317599</v>
+        <v>0.001141862375317597</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.01989926728436671</v>
+        <v>0.01989926728436668</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.0005153012396921024</v>
+        <v>0.0005153012396921015</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.0001509650074374186</v>
+        <v>0.0001509650074374184</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.01369892831667568</v>
+        <v>0.01369892831667566</v>
       </c>
       <c r="BL11" t="n">
-        <v>8.280298130543375e-05</v>
+        <v>8.28029813054336e-05</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.0285343785252392</v>
+        <v>0.02853437852523915</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.00164696855611096</v>
+        <v>0.001646968556110957</v>
       </c>
       <c r="BO11" t="n">
-        <v>6.250574451173411e-05</v>
+        <v>6.250574451173401e-05</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.0002834036871648271</v>
+        <v>0.0002834036871648266</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.0004762631390579143</v>
+        <v>0.0004762631390579135</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.0001912408626727468</v>
+        <v>0.0001912408626727465</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.02689858911952969</v>
+        <v>0.02689858911952964</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.006102111442644785</v>
+        <v>0.006102111442644774</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.004013259743547978</v>
+        <v>0.004013259743547971</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.003548447570473684</v>
+        <v>0.003548447570473678</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.129186916551695e-05</v>
+        <v>1.129186916551693e-05</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.00255554181496695</v>
+        <v>0.002555541814966946</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.0001071546841740086</v>
+        <v>0.0001071546841740084</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.007419180794728255</v>
+        <v>0.007419180794728242</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.0001226812600958493</v>
+        <v>0.0001226812600958491</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.0003208402555335389</v>
+        <v>0.0003208402555335384</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.0001155254250924167</v>
+        <v>0.0001155254250924165</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.0002536014918296584</v>
+        <v>0.0002536014918296579</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.007963372675573427</v>
+        <v>0.007963372675573422</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.001310710215707495</v>
+        <v>0.001310710215707493</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.004750916997842078</v>
+        <v>0.004750916997842069</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.0004762516942216756</v>
+        <v>0.0004762516942216748</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.0001211388013362684</v>
+        <v>0.0001211388013362682</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.008195279573858382</v>
+        <v>0.008195279573858369</v>
       </c>
       <c r="CK11" t="n">
-        <v>9.34041368332001e-06</v>
+        <v>9.340413683319995e-06</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.0004597715940457976</v>
+        <v>0.0004597715940457969</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.971656928120091e-05</v>
+        <v>2.971656928120086e-05</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.0002501096042022537</v>
+        <v>0.0002501096042022533</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.001252013336108305</v>
+        <v>0.001252013336108303</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.0008594883833523979</v>
+        <v>0.0008594883833523964</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.001079446701380623</v>
+        <v>0.001079446701380621</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.0006341580920162707</v>
+        <v>0.0006341580920162697</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.0001044221102583587</v>
+        <v>0.0001044221102583586</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.000223846175598477</v>
+        <v>0.0002238461755984766</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.0001153784751674855</v>
+        <v>0.0001153784751674852</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.0003798559105146192</v>
+        <v>0.0003798559105146186</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.0004799794891722266</v>
+        <v>0.0004799794891722257</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.003965858793580521</v>
+        <v>0.003965858793580514</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.0001330037344401154</v>
+        <v>0.0001330037344401152</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.0002680896461431859</v>
+        <v>0.0002680896461431854</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.0002863402837606557</v>
+        <v>0.0002863402837606552</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.0004895380513683734</v>
+        <v>0.0004895380513683725</v>
       </c>
       <c r="DC11" t="n">
-        <v>9.620238397662191e-05</v>
+        <v>9.620238397662175e-05</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.001437836655588649</v>
+        <v>0.001437836655588646</v>
       </c>
       <c r="DE11" t="n">
-        <v>9.59667047045813e-06</v>
+        <v>9.596670470458115e-06</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.0004713688735576574</v>
+        <v>0.0004713688735576566</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.005987424797261562</v>
+        <v>0.005987424797261552</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.0004685544578870908</v>
+        <v>0.00046855445788709</v>
       </c>
       <c r="DI11" t="n">
-        <v>9.047099772942506e-05</v>
+        <v>9.047099772942491e-05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>5.725516971195822e-05</v>
+        <v>5.725516971195812e-05</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.00123702173374867</v>
+        <v>0.001237021733748667</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.0002750897902734979</v>
+        <v>0.0002750897902734974</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.0001986860184315947</v>
+        <v>0.0001986860184315943</v>
       </c>
       <c r="DN11" t="n">
-        <v>3.526199971019964e-05</v>
+        <v>3.526199971019958e-05</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.001171078146748624</v>
+        <v>0.001171078146748622</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.1070592906061595</v>
+        <v>0.1070592906061594</v>
       </c>
       <c r="DQ11" t="n">
-        <v>7.684925633990661e-06</v>
+        <v>7.684925633990647e-06</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.806277679587057e-05</v>
+        <v>8.806277679587042e-05</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.003519826232231614</v>
+        <v>0.003519826232231608</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.001563637756484061</v>
+        <v>0.001563637756484059</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.003798184652619325</v>
+        <v>0.003798184652619319</v>
       </c>
       <c r="DV11" t="n">
-        <v>9.245782750407802e-05</v>
+        <v>9.245782750407786e-05</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.0004047109211893159</v>
+        <v>0.0004047109211893152</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.000732144011803329</v>
+        <v>0.0007321440118033277</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.0002642546309753003</v>
+        <v>0.0002642546309752998</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.0001858875067641603</v>
+        <v>0.00018588750676416</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.0004559851256000365</v>
+        <v>0.0004559851256000357</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.0002733419312668523</v>
+        <v>0.0002733419312668518</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.006487760531014647</v>
+        <v>0.006487760531014635</v>
       </c>
       <c r="ED11" t="n">
-        <v>1.026978227562515e-05</v>
+        <v>1.026978227562514e-05</v>
       </c>
       <c r="EE11" t="n">
-        <v>8.316795621474065e-05</v>
+        <v>8.31679562147405e-05</v>
       </c>
       <c r="EF11" t="n">
-        <v>4.644339006768289e-06</v>
+        <v>4.644339006768281e-06</v>
       </c>
       <c r="EG11" t="n">
-        <v>9.576665807439037e-05</v>
+        <v>9.576665807439021e-05</v>
       </c>
       <c r="EH11" t="n">
-        <v>4.019069890351101e-05</v>
+        <v>4.019069890351093e-05</v>
       </c>
       <c r="EI11" t="n">
-        <v>2.787982865855126e-05</v>
+        <v>2.787982865855122e-05</v>
       </c>
       <c r="EJ11" t="n">
-        <v>3.534730802663559e-05</v>
+        <v>3.534730802663553e-05</v>
       </c>
       <c r="EK11" t="n">
-        <v>1.424838377476533</v>
+        <v>1.424838377476535</v>
       </c>
       <c r="EL11" t="inlineStr">
         <is>
@@ -6350,424 +6350,424 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.3997486739716909</v>
+        <v>0.3997486739716923</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0009033436859297453</v>
+        <v>0.0009033436859297472</v>
       </c>
       <c r="D12" t="n">
-        <v>0.000879506191178701</v>
+        <v>0.0008795061911787028</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01338985403059623</v>
+        <v>0.01338985403059626</v>
       </c>
       <c r="F12" t="n">
-        <v>0.224459297938406</v>
+        <v>0.2244592979384065</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5587847287484478</v>
+        <v>0.558784728748449</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2366756784218133</v>
+        <v>0.2366756784218136</v>
       </c>
       <c r="I12" t="n">
-        <v>0.06437983001709732</v>
+        <v>0.06437983001709745</v>
       </c>
       <c r="J12" t="n">
-        <v>0.02944351516413556</v>
+        <v>0.02944351516413562</v>
       </c>
       <c r="K12" t="n">
-        <v>0.08995119039757772</v>
+        <v>0.08995119039757792</v>
       </c>
       <c r="L12" t="n">
-        <v>0.03448166045904137</v>
+        <v>0.03448166045904144</v>
       </c>
       <c r="M12" t="n">
-        <v>0.005467910157767718</v>
+        <v>0.005467910157767731</v>
       </c>
       <c r="N12" t="n">
-        <v>0.02010098911995819</v>
+        <v>0.02010098911995824</v>
       </c>
       <c r="O12" t="n">
-        <v>0.003947184133550461</v>
+        <v>0.00394718413355047</v>
       </c>
       <c r="P12" t="n">
-        <v>0.006140956599595909</v>
+        <v>0.00614095659959592</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.007863725633610657</v>
+        <v>0.003934394609204707</v>
       </c>
       <c r="R12" t="n">
-        <v>0.006988193368375384</v>
+        <v>0.006988193368375402</v>
       </c>
       <c r="S12" t="n">
-        <v>0.005220563071132268</v>
+        <v>0.005220563071132281</v>
       </c>
       <c r="T12" t="n">
-        <v>0.01618095493951034</v>
+        <v>0.01618095493951037</v>
       </c>
       <c r="U12" t="n">
-        <v>3.415047346663751e-05</v>
+        <v>3.415047346663758e-05</v>
       </c>
       <c r="V12" t="n">
-        <v>0.001898374748548179</v>
+        <v>0.001898374748548183</v>
       </c>
       <c r="W12" t="n">
-        <v>0.04745493410170753</v>
+        <v>0.04745493410170762</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0004058413406473971</v>
+        <v>0.0004058413406473979</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.004015078534447646</v>
+        <v>0.004015078534447652</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.003835943853716995</v>
+        <v>0.003835943853717004</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.02751956947394897</v>
+        <v>0.02751956947394903</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.0009017637555758249</v>
+        <v>0.0009017637555758267</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.03325049923838819</v>
+        <v>0.03325049923838826</v>
       </c>
       <c r="AD12" t="n">
-        <v>5.129036994829747e-05</v>
+        <v>5.129036994829759e-05</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.332304912318153e-05</v>
+        <v>1.332304912318156e-05</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.05977984331822753</v>
+        <v>0.05977984331822769</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.03035020629215674</v>
+        <v>0.0303502062921568</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.002019583431817152</v>
+        <v>0.002019583431817155</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.00131557204864932</v>
+        <v>0.001315572048649323</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.002768329354524335</v>
+        <v>0.002768329354524341</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.0197297339094225</v>
+        <v>0.01972973390942254</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.0009143583335266284</v>
+        <v>0.0009143583335266302</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.0003935483532908249</v>
+        <v>0.0003935483532908258</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.000308349445085905</v>
+        <v>0.0003083494450859057</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.0006290918541944785</v>
+        <v>0.0006290918541944799</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.0005090088078499096</v>
+        <v>0.0005090088078499106</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.001537502041263434</v>
+        <v>0.001537502041263437</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.007326607119040073</v>
+        <v>0.007326607119040087</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.0001537706405058203</v>
+        <v>0.0001537706405058206</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.176846637502431e-05</v>
+        <v>8.176846637502449e-05</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.0003953813216756066</v>
+        <v>0.0003953813216756075</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.003968232090307462</v>
+        <v>0.003968232090307468</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.003664251799648766</v>
+        <v>0.003664251799648774</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.0003047866443877397</v>
+        <v>0.0003047866443877403</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.0361187160626933</v>
+        <v>0.03611871606269338</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.0008117901024291548</v>
+        <v>0.0008117901024291565</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.967358397406383e-05</v>
+        <v>9.967358397406403e-05</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.03813886188839967</v>
+        <v>0.03813886188839974</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.008957913426307779</v>
+        <v>0.008957913426307798</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.03347918221537485</v>
+        <v>0.03347918221537492</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.0005347441704871735</v>
+        <v>0.0005347441704871747</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.0008449117668520592</v>
+        <v>0.0008449117668520602</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.001174644739498</v>
+        <v>0.001174644739498002</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.01968156157277993</v>
+        <v>0.01968156157277997</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.0005101810000587029</v>
+        <v>0.000510181000058704</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.0001446075906485954</v>
+        <v>0.0001446075906485957</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.01455330497681615</v>
+        <v>0.01455330497681619</v>
       </c>
       <c r="BL12" t="n">
-        <v>8.362561340918776e-05</v>
+        <v>8.362561340918792e-05</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.02795911587176632</v>
+        <v>0.02795911587176637</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.001706782475754271</v>
+        <v>0.001706782475754275</v>
       </c>
       <c r="BO12" t="n">
-        <v>5.882040609289753e-05</v>
+        <v>5.882040609289766e-05</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.0002883122975055694</v>
+        <v>0.00028831229750557</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.0004862548341672526</v>
+        <v>0.0004862548341672537</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.0001715573896471926</v>
+        <v>0.000171557389647193</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.02610345237148766</v>
+        <v>0.0261034523714877</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.005673609264695536</v>
+        <v>0.005673609264695548</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.003997431894849598</v>
+        <v>0.003997431894849608</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.003674748284135634</v>
+        <v>0.003674748284135642</v>
       </c>
       <c r="BW12" t="n">
-        <v>9.17223735062505e-06</v>
+        <v>9.172237350625068e-06</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.002415835133672107</v>
+        <v>0.002415835133672112</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.0001141096942874263</v>
+        <v>0.0001141096942874266</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.00716678063337877</v>
+        <v>0.007166780633378785</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.000118424488939753</v>
+        <v>0.0001184244889397533</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.0003230366572765042</v>
+        <v>0.0003230366572765048</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.000117387932312703</v>
+        <v>0.0001173879323127033</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.0002107169891007605</v>
+        <v>0.000210716989100761</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.008275633827228016</v>
+        <v>0.008275633827228034</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.001356160475948376</v>
+        <v>0.001356160475948379</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.00409420793376985</v>
+        <v>0.004094207933769858</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.0004834215933922567</v>
+        <v>0.0004834215933922576</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.0001171573199042424</v>
+        <v>0.0001171573199042426</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.007930663163655195</v>
+        <v>0.007930663163655212</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.001630004239213e-05</v>
+        <v>1.001630004239215e-05</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.0004998428177388662</v>
+        <v>0.0004998428177388673</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.943958849561442e-05</v>
+        <v>2.943958849561448e-05</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.0002564919588333965</v>
+        <v>0.0002564919588333971</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.001238610473057252</v>
+        <v>0.001238610473057254</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.0007693415391109539</v>
+        <v>0.0007693415391109554</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.001031329465382625</v>
+        <v>0.001031329465382627</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.0006299375902063252</v>
+        <v>0.0006299375902063265</v>
       </c>
       <c r="CS12" t="n">
-        <v>9.807575971655792e-05</v>
+        <v>9.807575971655812e-05</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.0002231431594818224</v>
+        <v>0.0002231431594818228</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.0001139152886241386</v>
+        <v>0.0001139152886241388</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.0003763773381144624</v>
+        <v>0.0003763773381144632</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.000518844048356127</v>
+        <v>0.000518844048356128</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.003877707026888942</v>
+        <v>0.00387770702688895</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.0001391202016086064</v>
+        <v>0.0001391202016086067</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.0002640033504175462</v>
+        <v>0.0002640033504175468</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.0002953919780069211</v>
+        <v>0.0002953919780069217</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.000509292126743105</v>
+        <v>0.0005092921267431061</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.0001120362953362746</v>
+        <v>0.0001120362953362748</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.001446811132529484</v>
+        <v>0.001446811132529487</v>
       </c>
       <c r="DE12" t="n">
-        <v>1.024279847932551e-05</v>
+        <v>1.024279847932553e-05</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.0004656094689275634</v>
+        <v>0.0004656094689275644</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.005843819453690359</v>
+        <v>0.005843819453690371</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.000506309474119771</v>
+        <v>0.0005063094741197721</v>
       </c>
       <c r="DI12" t="n">
-        <v>8.823100194475419e-05</v>
+        <v>8.823100194475436e-05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>6.35836597861006e-05</v>
+        <v>6.358365978610073e-05</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.001249280585944312</v>
+        <v>0.001249280585944314</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.0002821520781742289</v>
+        <v>0.0002821520781742295</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.0001916480400660059</v>
+        <v>0.0001916480400660063</v>
       </c>
       <c r="DN12" t="n">
-        <v>3.783204201062425e-05</v>
+        <v>3.783204201062433e-05</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.001102456084272921</v>
+        <v>0.001102456084272924</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.1062430045909735</v>
+        <v>0.1062430045909737</v>
       </c>
       <c r="DQ12" t="n">
-        <v>7.526692992133471e-06</v>
+        <v>7.526692992133488e-06</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.144068699965356e-05</v>
+        <v>8.144068699965373e-05</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.003220020524857663</v>
+        <v>0.00322002052485767</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.001684303557023463</v>
+        <v>0.001684303557023468</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.003513568585081964</v>
+        <v>0.003513568585081971</v>
       </c>
       <c r="DV12" t="n">
-        <v>9.328193196538861e-05</v>
+        <v>9.32819319653888e-05</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.0003936726312223219</v>
+        <v>0.0003936726312223227</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.0006968148020709399</v>
+        <v>0.0006968148020709414</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.0002545918432439872</v>
+        <v>0.0002545918432439878</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.0001922150708347241</v>
+        <v>0.0001922150708347245</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.0004551043571077096</v>
+        <v>0.0004551043571077103</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.0002667653291226906</v>
+        <v>0.0002667653291226911</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.006964348312134277</v>
+        <v>0.006964348312134292</v>
       </c>
       <c r="ED12" t="n">
-        <v>1.012929721638498e-05</v>
+        <v>1.0129297216385e-05</v>
       </c>
       <c r="EE12" t="n">
-        <v>8.95826991732265e-05</v>
+        <v>8.958269917322669e-05</v>
       </c>
       <c r="EF12" t="n">
-        <v>4.85264069083714e-06</v>
+        <v>4.852640690837151e-06</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.000100746330369014</v>
+        <v>0.0001007463303690142</v>
       </c>
       <c r="EH12" t="n">
-        <v>3.010490477079865e-05</v>
+        <v>3.010490477079871e-05</v>
       </c>
       <c r="EI12" t="n">
-        <v>2.093067233212045e-05</v>
+        <v>2.093067233212049e-05</v>
       </c>
       <c r="EJ12" t="n">
-        <v>3.549072800147491e-05</v>
+        <v>3.549072800147497e-05</v>
       </c>
       <c r="EK12" t="n">
-        <v>1.391297738960131</v>
+        <v>1.391297738960128</v>
       </c>
       <c r="EL12" t="inlineStr">
         <is>
@@ -6858,424 +6858,424 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.4029575683656929</v>
+        <v>0.4029575683656918</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0009911258553004885</v>
+        <v>0.0009911258553004872</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0008646978748286967</v>
+        <v>0.0008646978748286955</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0129995658995503</v>
+        <v>0.01299956589955028</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2238286445360239</v>
+        <v>0.223828644536024</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5466021605261885</v>
+        <v>0.5466021605261875</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2295755366449045</v>
+        <v>0.2295755366449044</v>
       </c>
       <c r="I13" t="n">
-        <v>0.05498120950354822</v>
+        <v>0.05498120950354815</v>
       </c>
       <c r="J13" t="n">
-        <v>0.03227010782656917</v>
+        <v>0.03227010782656912</v>
       </c>
       <c r="K13" t="n">
-        <v>0.07682420209201914</v>
+        <v>0.07682420209201903</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03661659824761723</v>
+        <v>0.03661659824761719</v>
       </c>
       <c r="M13" t="n">
-        <v>0.006257835575850979</v>
+        <v>0.00625783557585097</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0217504750601525</v>
+        <v>0.02175047506015247</v>
       </c>
       <c r="O13" t="n">
-        <v>0.00435983428079516</v>
+        <v>0.004359834280795154</v>
       </c>
       <c r="P13" t="n">
-        <v>0.006429049964392365</v>
+        <v>0.006429049964392356</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.008751836352522835</v>
+        <v>0.003992956787032835</v>
       </c>
       <c r="R13" t="n">
-        <v>0.007199549184384025</v>
+        <v>0.007199549184384015</v>
       </c>
       <c r="S13" t="n">
-        <v>0.005439338367947628</v>
+        <v>0.005439338367947622</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01448361908764585</v>
+        <v>0.01448361908764583</v>
       </c>
       <c r="U13" t="n">
-        <v>3.180229243461021e-05</v>
+        <v>3.180229243461016e-05</v>
       </c>
       <c r="V13" t="n">
-        <v>0.002050709697378437</v>
+        <v>0.002050709697378434</v>
       </c>
       <c r="W13" t="n">
-        <v>0.04331939541290297</v>
+        <v>0.04331939541290291</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0003764771683347946</v>
+        <v>0.000376477168334794</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.004009560400312625</v>
+        <v>0.004009560400312618</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.004016066603758058</v>
+        <v>0.004016066603758053</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.02772928275970313</v>
+        <v>0.02772928275970309</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.0008921494294329666</v>
+        <v>0.0008921494294329653</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.03547677419884858</v>
+        <v>0.03547677419884854</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.804965714772897e-05</v>
+        <v>4.80496571477289e-05</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.471061052444908e-05</v>
+        <v>1.471061052444906e-05</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.05554456905223483</v>
+        <v>0.05554456905223477</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.03562610501758676</v>
+        <v>0.03562610501758669</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.00201781924455335</v>
+        <v>0.002017819244553348</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.001271325317135847</v>
+        <v>0.001271325317135845</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.002875737714475123</v>
+        <v>0.002875737714475119</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.01942134328175589</v>
+        <v>0.01942134328175586</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.0009521130620154349</v>
+        <v>0.0009521130620154343</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.0004155055647836905</v>
+        <v>0.0004155055647836897</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.0003173638682255038</v>
+        <v>0.0003173638682255034</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.0006205032545987698</v>
+        <v>0.0006205032545987688</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.0005454588007786163</v>
+        <v>0.0005454588007786156</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.001590203900170766</v>
+        <v>0.001590203900170764</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.007496525398550181</v>
+        <v>0.007496525398550171</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.000158995723185645</v>
+        <v>0.0001589957231856447</v>
       </c>
       <c r="AT13" t="n">
-        <v>8.976213411042001e-05</v>
+        <v>8.97621341104198e-05</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.0004219891390979903</v>
+        <v>0.0004219891390979897</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.003971715983529561</v>
+        <v>0.003971715983529555</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.004119756903385117</v>
+        <v>0.004119756903385111</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.0002919804776659676</v>
+        <v>0.0002919804776659671</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.03357265576084897</v>
+        <v>0.03357265576084893</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.0008646884872261088</v>
+        <v>0.0008646884872261082</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.000104183049040305</v>
+        <v>0.0001041830490403047</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.03938491367778248</v>
+        <v>0.03938491367778241</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.008791296142347227</v>
+        <v>0.008791296142347221</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.03554540556336339</v>
+        <v>0.03554540556336333</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.0005179800135510524</v>
+        <v>0.0005179800135510517</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.0009205610883863398</v>
+        <v>0.0009205610883863385</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.001127055979273568</v>
+        <v>0.001127055979273567</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.02156003172107032</v>
+        <v>0.02156003172107029</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.000522527477268284</v>
+        <v>0.0005225274772682833</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.0002012482023852344</v>
+        <v>0.0002012482023852341</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.01634725120525402</v>
+        <v>0.016347251205254</v>
       </c>
       <c r="BL13" t="n">
-        <v>8.584282646736615e-05</v>
+        <v>8.584282646736595e-05</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.02833907640184907</v>
+        <v>0.02833907640184903</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.001690100885576995</v>
+        <v>0.001690100885576993</v>
       </c>
       <c r="BO13" t="n">
-        <v>6.63973715650966e-05</v>
+        <v>6.63973715650965e-05</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.0002943586909629767</v>
+        <v>0.0002943586909629762</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.0004847617474476743</v>
+        <v>0.0004847617474476736</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.0002024229207454696</v>
+        <v>0.0002024229207454693</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.0293308497852251</v>
+        <v>0.02933084978522505</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.005591853462423618</v>
+        <v>0.005591853462423611</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.00399845249137139</v>
+        <v>0.003998452491371383</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.003813845155854458</v>
+        <v>0.003813845155854452</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.026281367244737e-05</v>
+        <v>1.026281367244736e-05</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.002540010990654136</v>
+        <v>0.002540010990654132</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.0001043245587279266</v>
+        <v>0.0001043245587279265</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.008146012527988109</v>
+        <v>0.008146012527988099</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.0001343079316946659</v>
+        <v>0.0001343079316946657</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.0003203667917502421</v>
+        <v>0.0003203667917502416</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.0001286327593754402</v>
+        <v>0.0001286327593754399</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.0002217984292593931</v>
+        <v>0.0002217984292593927</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.007611217001445767</v>
+        <v>0.007611217001445757</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.001291293012292352</v>
+        <v>0.00129129301229235</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.004935002338835611</v>
+        <v>0.004935002338835604</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.0005213264688691279</v>
+        <v>0.0005213264688691271</v>
       </c>
       <c r="CI13" t="n">
-        <v>7.177216637475714e-05</v>
+        <v>7.177216637475705e-05</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.009234022102581677</v>
+        <v>0.009234022102581663</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.040136674590505e-05</v>
+        <v>1.040136674590503e-05</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.0004848174989514822</v>
+        <v>0.0004848174989514815</v>
       </c>
       <c r="CM13" t="n">
-        <v>3.084136713978189e-05</v>
+        <v>3.084136713978185e-05</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.0002539753214300381</v>
+        <v>0.0002539753214300377</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.001342448207227307</v>
+        <v>0.001342448207227305</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.0008738065943877555</v>
+        <v>0.0008738065943877543</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.001069743228782819</v>
+        <v>0.001069743228782817</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.000656211993160893</v>
+        <v>0.000656211993160892</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.0001014279990037085</v>
+        <v>0.0001014279990037084</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.0002298527577265011</v>
+        <v>0.0002298527577265008</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.0001213875442809819</v>
+        <v>0.0001213875442809817</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.0004036414633258255</v>
+        <v>0.000403641463325825</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.0004528579753936809</v>
+        <v>0.0004528579753936802</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.003835936569741179</v>
+        <v>0.003835936569741173</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.0001402406437630826</v>
+        <v>0.0001402406437630824</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.0002891792640805329</v>
+        <v>0.0002891792640805325</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.0003107929900444134</v>
+        <v>0.000310792990044413</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.0005396895539107532</v>
+        <v>0.0005396895539107524</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.0001038629239775857</v>
+        <v>0.0001038629239775856</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.001541807274034559</v>
+        <v>0.001541807274034557</v>
       </c>
       <c r="DE13" t="n">
-        <v>1.081516427792005e-05</v>
+        <v>1.081516427792004e-05</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.0004788199554279932</v>
+        <v>0.0004788199554279926</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.005899227841421142</v>
+        <v>0.005899227841421134</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.0004910635443756277</v>
+        <v>0.000491063544375627</v>
       </c>
       <c r="DI13" t="n">
-        <v>9.800187308532359e-05</v>
+        <v>9.800187308532344e-05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>5.044017312783786e-05</v>
+        <v>5.044017312783779e-05</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.001183688102568919</v>
+        <v>0.001183688102568917</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.0003024425851241055</v>
+        <v>0.0003024425851241051</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.0001472346573497985</v>
+        <v>0.0001472346573497983</v>
       </c>
       <c r="DN13" t="n">
-        <v>3.965970970984978e-05</v>
+        <v>3.965970970984972e-05</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.001218568931624897</v>
+        <v>0.001218568931624895</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.09801641926546897</v>
+        <v>0.09801641926546883</v>
       </c>
       <c r="DQ13" t="n">
-        <v>7.802759505435844e-06</v>
+        <v>7.802759505435834e-06</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.0001010017483153962</v>
+        <v>0.0001010017483153959</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.003505517034114728</v>
+        <v>0.003505517034114722</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.001673859394140202</v>
+        <v>0.0016738593941402</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.003818084873973532</v>
+        <v>0.003818084873973526</v>
       </c>
       <c r="DV13" t="n">
-        <v>9.206695437408449e-05</v>
+        <v>9.206695437408435e-05</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.0004015927359744487</v>
+        <v>0.0004015927359744481</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.0007388361720716767</v>
+        <v>0.0007388361720716756</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.0002595730256028298</v>
+        <v>0.0002595730256028293</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.00020223125588746</v>
+        <v>0.0002022312558874597</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.0004750546053657387</v>
+        <v>0.0004750546053657381</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.0002765228470999129</v>
+        <v>0.0002765228470999125</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.006316738803536396</v>
+        <v>0.006316738803536387</v>
       </c>
       <c r="ED13" t="n">
-        <v>1.035101693649796e-05</v>
+        <v>1.035101693649794e-05</v>
       </c>
       <c r="EE13" t="n">
-        <v>8.984897563598647e-05</v>
+        <v>8.984897563598634e-05</v>
       </c>
       <c r="EF13" t="n">
-        <v>4.752613380521803e-06</v>
+        <v>4.752613380521796e-06</v>
       </c>
       <c r="EG13" t="n">
-        <v>9.543218526740926e-05</v>
+        <v>9.543218526740912e-05</v>
       </c>
       <c r="EH13" t="n">
-        <v>3.873375722645692e-05</v>
+        <v>3.873375722645686e-05</v>
       </c>
       <c r="EI13" t="n">
-        <v>2.898325377309997e-05</v>
+        <v>2.898325377309993e-05</v>
       </c>
       <c r="EJ13" t="n">
-        <v>3.832275207848129e-05</v>
+        <v>3.832275207848124e-05</v>
       </c>
       <c r="EK13" t="n">
-        <v>1.400550869386972</v>
+        <v>1.400550869386974</v>
       </c>
       <c r="EL13" t="inlineStr">
         <is>
@@ -7366,424 +7366,424 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3745868375906418</v>
+        <v>0.3745868375906422</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0006606535057568974</v>
+        <v>0.0006606535057568979</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0007421043834532382</v>
+        <v>0.0007421043834532387</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01195299673536621</v>
+        <v>0.01195299673536622</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2105056703590826</v>
+        <v>0.2105056703590828</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5846018177044652</v>
+        <v>0.584601817704466</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2320566128257253</v>
+        <v>0.2320566128257254</v>
       </c>
       <c r="I14" t="n">
-        <v>0.06705542245425808</v>
+        <v>0.06705542245425818</v>
       </c>
       <c r="J14" t="n">
-        <v>0.02286413456756986</v>
+        <v>0.02286413456756988</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0922941339980769</v>
+        <v>0.09229413399807697</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02976050432801141</v>
+        <v>0.02976050432801142</v>
       </c>
       <c r="M14" t="n">
-        <v>0.004351712635042238</v>
+        <v>0.004351712635042242</v>
       </c>
       <c r="N14" t="n">
-        <v>0.01560573524435909</v>
+        <v>0.01560573524435911</v>
       </c>
       <c r="O14" t="n">
-        <v>0.003369930334073482</v>
+        <v>0.003369930334073484</v>
       </c>
       <c r="P14" t="n">
-        <v>0.004994654628512986</v>
+        <v>0.004994654628512987</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.004722456529650835</v>
+        <v>0.001781120896557198</v>
       </c>
       <c r="R14" t="n">
-        <v>0.006178693260952193</v>
+        <v>0.006178693260952198</v>
       </c>
       <c r="S14" t="n">
-        <v>0.004280649971192278</v>
+        <v>0.004280649971192281</v>
       </c>
       <c r="T14" t="n">
-        <v>0.01627764605797259</v>
+        <v>0.0162776460579726</v>
       </c>
       <c r="U14" t="n">
-        <v>2.745801347682813e-05</v>
+        <v>2.745801347682816e-05</v>
       </c>
       <c r="V14" t="n">
         <v>0.001550963388139971</v>
       </c>
       <c r="W14" t="n">
-        <v>0.04649610747190033</v>
+        <v>0.04649610747190037</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0003739052451238492</v>
+        <v>0.0003739052451238495</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.003694146372058772</v>
+        <v>0.003694146372058775</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.003030284907741911</v>
+        <v>0.003030284907741914</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.03345846546275213</v>
+        <v>0.03345846546275216</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.0007759001059731127</v>
+        <v>0.0007759001059731134</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.02724957836995044</v>
+        <v>0.02724957836995047</v>
       </c>
       <c r="AD14" t="n">
-        <v>4.231279918826416e-05</v>
+        <v>4.23127991882642e-05</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.033670711016709e-05</v>
+        <v>1.03367071101671e-05</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.06295297975981889</v>
+        <v>0.06295297975981891</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.02815930813101109</v>
+        <v>0.02815930813101113</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.001947482294071053</v>
+        <v>0.001947482294071055</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.001347969863653445</v>
+        <v>0.001347969863653447</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.002565134843833156</v>
+        <v>0.002565134843833158</v>
       </c>
       <c r="AK14" t="n">
         <v>0.0155656395217185</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.0007526310919049107</v>
+        <v>0.0007526310919049113</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.0003118875712369102</v>
+        <v>0.0003118875712369104</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.0002685192756618342</v>
+        <v>0.0002685192756618344</v>
       </c>
       <c r="AO14" t="n">
         <v>0.0005264138051664868</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.0003755585825982744</v>
+        <v>0.0003755585825982747</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.001447848844312974</v>
+        <v>0.001447848844312975</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.007090229515782497</v>
+        <v>0.007090229515782503</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.0001542832818560905</v>
+        <v>0.0001542832818560906</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.725091641984659e-05</v>
+        <v>6.725091641984665e-05</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.0002989280080127454</v>
+        <v>0.0002989280080127456</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.003614099665546478</v>
+        <v>0.003614099665546481</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.003430888200001616</v>
+        <v>0.003430888200001619</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.0002971737447005022</v>
+        <v>0.0002971737447005024</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.04607048755427436</v>
+        <v>0.0460704875542744</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.0006995317754527706</v>
+        <v>0.0006995317754527715</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.519871835081359e-05</v>
+        <v>7.519871835081361e-05</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.04706184327993634</v>
+        <v>0.04706184327993638</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.007463279767988679</v>
+        <v>0.007463279767988682</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.02919181432732508</v>
+        <v>0.0291918143273251</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.0004445582881644009</v>
+        <v>0.0004445582881644013</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.0006965227743040096</v>
+        <v>0.0006965227743040097</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.0009210921101643337</v>
+        <v>0.0009210921101643345</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.0155214008746128</v>
+        <v>0.01552140087461282</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.0004020663068146826</v>
+        <v>0.0004020663068146829</v>
       </c>
       <c r="BJ14" t="n">
-        <v>6.916426329507535e-06</v>
+        <v>6.916426329507541e-06</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.009325062347561227</v>
+        <v>0.009325062347561239</v>
       </c>
       <c r="BL14" t="n">
-        <v>9.332807583133168e-05</v>
+        <v>9.332807583133176e-05</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.02655723213902982</v>
+        <v>0.02655723213902983</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.001543112532667671</v>
+        <v>0.001543112532667672</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.368069501540106e-05</v>
+        <v>4.368069501540114e-05</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.0002500667032105463</v>
+        <v>0.0002500667032105466</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.0004472602881418303</v>
+        <v>0.0004472602881418307</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.0001038691933710558</v>
+        <v>0.0001038691933710559</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.01903107381577294</v>
+        <v>0.01903107381577296</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.00631908719916499</v>
+        <v>0.006319087199164995</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.003059636365690174</v>
+        <v>0.003059636365690176</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.003436872104061444</v>
+        <v>0.003436872104061447</v>
       </c>
       <c r="BW14" t="n">
-        <v>6.271338304517898e-06</v>
+        <v>6.271338304517904e-06</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.002186291483337851</v>
+        <v>0.002186291483337853</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.0001012031622895767</v>
+        <v>0.0001012031622895768</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.004484310194613049</v>
+        <v>0.004484310194613052</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.0001005710406002073</v>
+        <v>0.0001005710406002074</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.0002744632868822359</v>
+        <v>0.0002744632868822361</v>
       </c>
       <c r="CC14" t="n">
-        <v>9.647610229423119e-05</v>
+        <v>9.647610229423128e-05</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.000216150494926842</v>
+        <v>0.0002161504949268421</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.007871316761508519</v>
+        <v>0.007871316761508526</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.001513227631051634</v>
+        <v>0.001513227631051635</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.003083050461299973</v>
+        <v>0.003083050461299975</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.0003855379705972497</v>
+        <v>0.00038553797059725</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.0001327054403967569</v>
+        <v>0.000132705440396757</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.006166680447420028</v>
+        <v>0.006166680447420033</v>
       </c>
       <c r="CK14" t="n">
-        <v>7.471792120670884e-06</v>
+        <v>7.47179212067089e-06</v>
       </c>
       <c r="CL14" t="n">
-        <v>0.0004159552855062729</v>
+        <v>0.0004159552855062733</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.112456669591822e-05</v>
+        <v>2.112456669591823e-05</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.0002320075930228756</v>
+        <v>0.0002320075930228758</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.001057185800329673</v>
+        <v>0.001057185800329674</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.0006772122895494549</v>
+        <v>0.0006772122895494554</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.0006965640458243355</v>
+        <v>0.0006965640458243361</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.0006365493133010547</v>
+        <v>0.0006365493133010552</v>
       </c>
       <c r="CS14" t="n">
-        <v>8.70860267229283e-05</v>
+        <v>8.708602672292837e-05</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.0002076759832540763</v>
+        <v>0.0002076759832540765</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.0001072839373619627</v>
+        <v>0.0001072839373619628</v>
       </c>
       <c r="CV14" t="n">
-        <v>0.0003295741433292882</v>
+        <v>0.0003295741433292884</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.0004131431119074761</v>
+        <v>0.0004131431119074764</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.003754654820352232</v>
+        <v>0.003754654820352238</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.0001090589317925639</v>
+        <v>0.000109058931792564</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.0002171950358554697</v>
+        <v>0.0002171950358554698</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.0002291313674016834</v>
+        <v>0.0002291313674016836</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.0004037462020750773</v>
+        <v>0.0004037462020750776</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.0001048134287302648</v>
+        <v>0.0001048134287302649</v>
       </c>
       <c r="DD14" t="n">
         <v>0.00118412863881306</v>
       </c>
       <c r="DE14" t="n">
-        <v>8.061391412552294e-06</v>
+        <v>8.0613914125523e-06</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.0003938557404281357</v>
+        <v>0.000393855740428136</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.004876090302189321</v>
+        <v>0.004876090302189325</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.0004236482920608602</v>
+        <v>0.0004236482920608605</v>
       </c>
       <c r="DI14" t="n">
-        <v>8.078971475656627e-05</v>
+        <v>8.078971475656634e-05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>5.169432457051204e-05</v>
+        <v>5.169432457051208e-05</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.001103773769638699</v>
+        <v>0.0011037737696387</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.000230330662553723</v>
+        <v>0.0002303306625537232</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.0002043168700162564</v>
+        <v>0.0002043168700162566</v>
       </c>
       <c r="DN14" t="n">
-        <v>3.160777167259224e-05</v>
+        <v>3.160777167259226e-05</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.0009275555313592261</v>
+        <v>0.0009275555313592268</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.1355465752808668</v>
+        <v>0.1355465752808669</v>
       </c>
       <c r="DQ14" t="n">
-        <v>5.807179363487638e-06</v>
+        <v>5.807179363487643e-06</v>
       </c>
       <c r="DR14" t="n">
-        <v>6.101084196788745e-05</v>
+        <v>6.101084196788751e-05</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.003060481510239891</v>
+        <v>0.003060481510239894</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.001344501663793321</v>
+        <v>0.001344501663793322</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.00288266777109732</v>
+        <v>0.002882667771097324</v>
       </c>
       <c r="DV14" t="n">
-        <v>8.611169094694585e-05</v>
+        <v>8.611169094694593e-05</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.0003850057104404745</v>
+        <v>0.0003850057104404748</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.0005644636656785766</v>
+        <v>0.0005644636656785771</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.0002291910798939038</v>
+        <v>0.0002291910798939041</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.0001878243184327571</v>
+        <v>0.0001878243184327572</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.0003918527102783539</v>
+        <v>0.0003918527102783542</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.0002267895913375495</v>
+        <v>0.0002267895913375496</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.007676321166441735</v>
+        <v>0.007676321166441741</v>
       </c>
       <c r="ED14" t="n">
-        <v>4.717133476486618e-06</v>
+        <v>4.717133476486621e-06</v>
       </c>
       <c r="EE14" t="n">
-        <v>8.254727578740627e-05</v>
+        <v>8.254727578740633e-05</v>
       </c>
       <c r="EF14" t="n">
-        <v>2.511337385466305e-06</v>
+        <v>2.511337385466307e-06</v>
       </c>
       <c r="EG14" t="n">
-        <v>6.788779433892144e-05</v>
+        <v>6.78877943389215e-05</v>
       </c>
       <c r="EH14" t="n">
-        <v>3.201787449915391e-05</v>
+        <v>3.201787449915393e-05</v>
       </c>
       <c r="EI14" t="n">
-        <v>2.568017584178703e-05</v>
+        <v>2.568017584178705e-05</v>
       </c>
       <c r="EJ14" t="n">
-        <v>2.833861574078772e-05</v>
+        <v>2.833861574078774e-05</v>
       </c>
       <c r="EK14" t="n">
-        <v>2.679195184973406</v>
+        <v>2.679195184973404</v>
       </c>
       <c r="EL14" t="inlineStr">
         <is>
@@ -7874,424 +7874,424 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3742668276483801</v>
+        <v>0.3742668276483791</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0006769301927890275</v>
+        <v>0.0006769301927890258</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0007515450148729987</v>
+        <v>0.0007515450148729968</v>
       </c>
       <c r="E15" t="n">
-        <v>0.01251693699455387</v>
+        <v>0.01251693699455384</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2110347464309047</v>
+        <v>0.2110347464309041</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5819908750752426</v>
+        <v>0.5819908750752418</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2295379752627643</v>
+        <v>0.2295379752627638</v>
       </c>
       <c r="I15" t="n">
-        <v>0.06368476116144381</v>
+        <v>0.06368476116144364</v>
       </c>
       <c r="J15" t="n">
-        <v>0.02243451236328464</v>
+        <v>0.02243451236328458</v>
       </c>
       <c r="K15" t="n">
-        <v>0.09208671485886526</v>
+        <v>0.09208671485886501</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03019627805468139</v>
+        <v>0.03019627805468134</v>
       </c>
       <c r="M15" t="n">
-        <v>0.004026277802644333</v>
+        <v>0.004026277802644323</v>
       </c>
       <c r="N15" t="n">
-        <v>0.01594943919231222</v>
+        <v>0.01594943919231219</v>
       </c>
       <c r="O15" t="n">
-        <v>0.003928870594591798</v>
+        <v>0.003928870594591787</v>
       </c>
       <c r="P15" t="n">
-        <v>0.004854955675197017</v>
+        <v>0.004854955675197</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.006061649686325238</v>
+        <v>0.003323691675910308</v>
       </c>
       <c r="R15" t="n">
-        <v>0.006222076046113688</v>
+        <v>0.006222076046113672</v>
       </c>
       <c r="S15" t="n">
-        <v>0.004352289928152078</v>
+        <v>0.004352289928152067</v>
       </c>
       <c r="T15" t="n">
-        <v>0.01585275927729119</v>
+        <v>0.01585275927729115</v>
       </c>
       <c r="U15" t="n">
-        <v>2.747479263017608e-05</v>
+        <v>2.747479263017601e-05</v>
       </c>
       <c r="V15" t="n">
-        <v>0.001603428814634244</v>
+        <v>0.00160342881463424</v>
       </c>
       <c r="W15" t="n">
-        <v>0.04799296143579568</v>
+        <v>0.04799296143579559</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0003725669646492275</v>
+        <v>0.0003725669646492265</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.00362216421616804</v>
+        <v>0.003622164216168029</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.00293400925960779</v>
+        <v>0.002934009259607781</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.03532218685848586</v>
+        <v>0.03532218685848575</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.0007351061333116742</v>
+        <v>0.0007351061333116726</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.0276201248757534</v>
+        <v>0.02762012487575332</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.38334204413744e-05</v>
+        <v>4.383342044137429e-05</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.122651704093616e-05</v>
+        <v>1.122651704093613e-05</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.05967161516228275</v>
+        <v>0.05967161516228263</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.0292727812244553</v>
+        <v>0.02927278122445523</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.00187000677569149</v>
+        <v>0.001870006775691486</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.001354669259411609</v>
+        <v>0.001354669259411605</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.002741085379090142</v>
+        <v>0.002741085379090135</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.01615932771095959</v>
+        <v>0.01615932771095955</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.0007957244676842718</v>
+        <v>0.0007957244676842697</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.0003373008507095158</v>
+        <v>0.0003373008507095149</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.000261964406432798</v>
+        <v>0.0002619644064327973</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.0005538027598813423</v>
+        <v>0.0005538027598813407</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.0003987896570499901</v>
+        <v>0.000398789657049989</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.00143571761210442</v>
+        <v>0.001435717612104416</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.007433254409609012</v>
+        <v>0.007433254409608993</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.0001493383785892345</v>
+        <v>0.0001493383785892341</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.889722643436309e-05</v>
+        <v>5.889722643436293e-05</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.0003004439092998184</v>
+        <v>0.0003004439092998176</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.00381845748204248</v>
+        <v>0.00381845748204247</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.004158442541142755</v>
+        <v>0.004158442541142744</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.0003008556130213228</v>
+        <v>0.000300855613021322</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.04587665502870054</v>
+        <v>0.04587665502870046</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.0006984881929291485</v>
+        <v>0.0006984881929291463</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.07237950688219e-05</v>
+        <v>8.072379506882169e-05</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.04325090906327643</v>
+        <v>0.04325090906327632</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.007276488646914736</v>
+        <v>0.007276488646914716</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.02802716304497264</v>
+        <v>0.02802716304497257</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.0004075378006228222</v>
+        <v>0.0004075378006228211</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.0006782500113791614</v>
+        <v>0.0006782500113791597</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.0009797499173313465</v>
+        <v>0.0009797499173313439</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.01506785459261034</v>
+        <v>0.0150678545926103</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.0004403800931488896</v>
+        <v>0.0004403800931488884</v>
       </c>
       <c r="BJ15" t="n">
-        <v>8.222933000136068e-05</v>
+        <v>8.222933000136047e-05</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.009243494667487081</v>
+        <v>0.009243494667487057</v>
       </c>
       <c r="BL15" t="n">
-        <v>9.445678285724812e-05</v>
+        <v>9.445678285724786e-05</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.02676316527816209</v>
+        <v>0.02676316527816202</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.001470240048366572</v>
+        <v>0.001470240048366569</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.663668000446173e-05</v>
+        <v>4.663668000446161e-05</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.0002459305129433457</v>
+        <v>0.000245930512943345</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.0004906792905206947</v>
+        <v>0.0004906792905206934</v>
       </c>
       <c r="BR15" t="n">
-        <v>9.268741692583133e-05</v>
+        <v>9.268741692583109e-05</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.01839815932285702</v>
+        <v>0.01839815932285697</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.006577206560225426</v>
+        <v>0.006577206560225409</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.003272191200050852</v>
+        <v>0.003272191200050844</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.003408138637985755</v>
+        <v>0.003408138637985745</v>
       </c>
       <c r="BW15" t="n">
-        <v>6.291442630911805e-06</v>
+        <v>6.291442630911788e-06</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.002362419975435108</v>
+        <v>0.002362419975435102</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.0001060230784692047</v>
+        <v>0.0001060230784692044</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.004599006275810364</v>
+        <v>0.004599006275810352</v>
       </c>
       <c r="CA15" t="n">
-        <v>9.980536536734845e-05</v>
+        <v>9.980536536734819e-05</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.0003215918056576125</v>
+        <v>0.0003215918056576116</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.0001012997229443408</v>
+        <v>0.0001012997229443405</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.0002426813668230855</v>
+        <v>0.0002426813668230848</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.008436647723431433</v>
+        <v>0.008436647723431416</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.001464901281796552</v>
+        <v>0.001464901281796547</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.002878440557859495</v>
+        <v>0.002878440557859487</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.0004222278850061297</v>
+        <v>0.0004222278850061286</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.0001345172590415619</v>
+        <v>0.0001345172590415615</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.005815535178693451</v>
+        <v>0.005815535178693436</v>
       </c>
       <c r="CK15" t="n">
-        <v>9.072213996944829e-06</v>
+        <v>9.072213996944806e-06</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.0003819229468996525</v>
+        <v>0.0003819229468996514</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.36763084507809e-05</v>
+        <v>2.367630845078084e-05</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.0002031589546778017</v>
+        <v>0.0002031589546778011</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.0009412436314792715</v>
+        <v>0.000941243631479269</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.0006600875686520155</v>
+        <v>0.0006600875686520138</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.0007792519032442457</v>
+        <v>0.0007792519032442436</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.0005634966491209872</v>
+        <v>0.0005634966491209854</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.0001031149742182792</v>
+        <v>0.0001031149742182789</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.0002175406990224247</v>
+        <v>0.0002175406990224242</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.0001077853880605444</v>
+        <v>0.0001077853880605441</v>
       </c>
       <c r="CV15" t="n">
-        <v>0.0003255428341385562</v>
+        <v>0.0003255428341385554</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.0004129523555838243</v>
+        <v>0.0004129523555838232</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.003594849254041952</v>
+        <v>0.003594849254041942</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.0001051140167921165</v>
+        <v>0.0001051140167921162</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.00021583373314333</v>
+        <v>0.0002158337331433293</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.0002549295218814002</v>
+        <v>0.0002549295218813996</v>
       </c>
       <c r="DB15" t="n">
-        <v>0.0004049232846567845</v>
+        <v>0.0004049232846567834</v>
       </c>
       <c r="DC15" t="n">
-        <v>7.681631545005044e-05</v>
+        <v>7.681631545005024e-05</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.001247989705123693</v>
+        <v>0.00124798970512369</v>
       </c>
       <c r="DE15" t="n">
-        <v>7.839394225268833e-06</v>
+        <v>7.839394225268812e-06</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.0004317813060713912</v>
+        <v>0.0004317813060713897</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.004799503675923678</v>
+        <v>0.004799503675923666</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.0003886347824487948</v>
+        <v>0.0003886347824487938</v>
       </c>
       <c r="DI15" t="n">
-        <v>8.67362705024929e-05</v>
+        <v>8.673627050249267e-05</v>
       </c>
       <c r="DJ15" t="n">
-        <v>5.860746552585239e-05</v>
+        <v>5.860746552585224e-05</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.001066293412638663</v>
+        <v>0.00106629341263866</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.000230542180139594</v>
+        <v>0.0002305421801395934</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.0002127435197851497</v>
+        <v>0.0002127435197851491</v>
       </c>
       <c r="DN15" t="n">
-        <v>3.542933595249641e-05</v>
+        <v>3.542933595249631e-05</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.00097493685741852</v>
+        <v>0.0009749368574185175</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.1346390487985743</v>
+        <v>0.134639048798574</v>
       </c>
       <c r="DQ15" t="n">
-        <v>5.04801871112189e-06</v>
+        <v>5.048018711121877e-06</v>
       </c>
       <c r="DR15" t="n">
-        <v>6.587539161580064e-05</v>
+        <v>6.587539161580046e-05</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.003141453119850575</v>
+        <v>0.003141453119850567</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.001429524430717752</v>
+        <v>0.001429524430717748</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.003009452438792379</v>
+        <v>0.003009452438792371</v>
       </c>
       <c r="DV15" t="n">
-        <v>5.360459942496808e-05</v>
+        <v>5.360459942496794e-05</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.0003842562965751591</v>
+        <v>0.0003842562965751581</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.0005317627006375665</v>
+        <v>0.0005317627006375651</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.0002268538115895125</v>
+        <v>0.0002268538115895118</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.0001911524542441694</v>
+        <v>0.0001911524542441689</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.0003818068117353458</v>
+        <v>0.0003818068117353448</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.000233287762554817</v>
+        <v>0.0002332877625548163</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.007193331111141901</v>
+        <v>0.007193331111141882</v>
       </c>
       <c r="ED15" t="n">
-        <v>6.953013573797032e-06</v>
+        <v>6.953013573797013e-06</v>
       </c>
       <c r="EE15" t="n">
-        <v>8.843325095809092e-05</v>
+        <v>8.843325095809069e-05</v>
       </c>
       <c r="EF15" t="n">
-        <v>2.528636188503109e-06</v>
+        <v>2.528636188503103e-06</v>
       </c>
       <c r="EG15" t="n">
-        <v>6.957164402817957e-05</v>
+        <v>6.957164402817938e-05</v>
       </c>
       <c r="EH15" t="n">
-        <v>2.400008235441478e-05</v>
+        <v>2.400008235441471e-05</v>
       </c>
       <c r="EI15" t="n">
-        <v>1.889205348115683e-05</v>
+        <v>1.889205348115678e-05</v>
       </c>
       <c r="EJ15" t="n">
-        <v>2.761321291886752e-05</v>
+        <v>2.761321291886745e-05</v>
       </c>
       <c r="EK15" t="n">
-        <v>2.690696718497914</v>
+        <v>2.690696718497922</v>
       </c>
       <c r="EL15" t="inlineStr">
         <is>
@@ -8382,424 +8382,424 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.3657186585318448</v>
+        <v>0.3657186585318442</v>
       </c>
       <c r="C16" t="n">
-        <v>0.000683673684086022</v>
+        <v>0.0006836736840860208</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0007932092674455695</v>
+        <v>0.0007932092674455678</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01152061079266303</v>
+        <v>0.01152061079266301</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2127694780042603</v>
+        <v>0.2127694780042602</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5904443920865795</v>
+        <v>0.5904443920865788</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2363497748289706</v>
+        <v>0.2363497748289703</v>
       </c>
       <c r="I16" t="n">
-        <v>0.07416612364991571</v>
+        <v>0.07416612364991558</v>
       </c>
       <c r="J16" t="n">
-        <v>0.02424358493697039</v>
+        <v>0.02424358493697035</v>
       </c>
       <c r="K16" t="n">
-        <v>0.09744389765855113</v>
+        <v>0.09744389765855095</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0301949968220724</v>
+        <v>0.03019499682207236</v>
       </c>
       <c r="M16" t="n">
-        <v>0.004379473002777735</v>
+        <v>0.004379473002777727</v>
       </c>
       <c r="N16" t="n">
-        <v>0.01451493796630169</v>
+        <v>0.01451493796630167</v>
       </c>
       <c r="O16" t="n">
-        <v>0.003201876878918744</v>
+        <v>0.003201876878918739</v>
       </c>
       <c r="P16" t="n">
-        <v>0.00498652051533206</v>
+        <v>0.004986520515332048</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.006028028590190003</v>
+        <v>0.003140207781408251</v>
       </c>
       <c r="R16" t="n">
-        <v>0.006222182609674423</v>
+        <v>0.006222182609674411</v>
       </c>
       <c r="S16" t="n">
-        <v>0.004442398884272193</v>
+        <v>0.004442398884272185</v>
       </c>
       <c r="T16" t="n">
-        <v>0.01583746084156087</v>
+        <v>0.01583746084156085</v>
       </c>
       <c r="U16" t="n">
-        <v>2.995293942142188e-05</v>
+        <v>2.995293942142183e-05</v>
       </c>
       <c r="V16" t="n">
-        <v>0.001553299812175072</v>
+        <v>0.00155329981217507</v>
       </c>
       <c r="W16" t="n">
-        <v>0.04693906494398824</v>
+        <v>0.04693906494398816</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0003876111963242655</v>
+        <v>0.0003876111963242648</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.003486383028313553</v>
+        <v>0.003486383028313547</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.003151270616164604</v>
+        <v>0.003151270616164599</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.03415193149873699</v>
+        <v>0.03415193149873693</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.0007439409127351945</v>
+        <v>0.0007439409127351932</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.02764663667531705</v>
+        <v>0.02764663667531701</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.865836164654035e-05</v>
+        <v>3.865836164654028e-05</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.090451995233235e-05</v>
+        <v>1.090451995233233e-05</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.06348683252896321</v>
+        <v>0.06348683252896306</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.02657628991224794</v>
+        <v>0.02657628991224788</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.001796625002757096</v>
+        <v>0.001796625002757093</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.001238128688418769</v>
+        <v>0.001238128688418767</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.002831662998598645</v>
+        <v>0.00283166299859864</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.01489156401294473</v>
+        <v>0.0148915640129447</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.0008335158693714261</v>
+        <v>0.0008335158693714247</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.000341819294878001</v>
+        <v>0.0003418192948780004</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.0002952406702490839</v>
+        <v>0.0002952406702490834</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.0005156322371297279</v>
+        <v>0.000515632237129727</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.0004029490811658218</v>
+        <v>0.0004029490811658211</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.001531135079275116</v>
+        <v>0.001531135079275113</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.007496761479776949</v>
+        <v>0.007496761479776939</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.0001573364211012966</v>
+        <v>0.0001573364211012963</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.478046742938117e-05</v>
+        <v>5.478046742938107e-05</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.0003111610059706579</v>
+        <v>0.0003111610059706574</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.003422000850388406</v>
+        <v>0.0034220008503884</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.003631080257650435</v>
+        <v>0.003631080257650429</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.00031333220723601</v>
+        <v>0.0003133322072360094</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.04765013814228587</v>
+        <v>0.04765013814228579</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.0006409902506775118</v>
+        <v>0.000640990250677511</v>
       </c>
       <c r="BA16" t="n">
-        <v>7.720283711517969e-05</v>
+        <v>7.720283711517955e-05</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.0449431200457082</v>
+        <v>0.04494312004570813</v>
       </c>
       <c r="BC16" t="n">
-        <v>0.007289456104182888</v>
+        <v>0.007289456104182876</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.02609169648087678</v>
+        <v>0.02609169648087675</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.000477921057088554</v>
+        <v>0.0004779210570885531</v>
       </c>
       <c r="BF16" t="n">
-        <v>0.0007424728586599115</v>
+        <v>0.0007424728586599099</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.0009463407274249001</v>
+        <v>0.0009463407274248985</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.01662528403657262</v>
+        <v>0.01662528403657259</v>
       </c>
       <c r="BI16" t="n">
-        <v>0.0004593047518318192</v>
+        <v>0.0004593047518318185</v>
       </c>
       <c r="BJ16" t="n">
-        <v>2.755100209832139e-06</v>
+        <v>2.755100209832134e-06</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.008325147604889659</v>
+        <v>0.008325147604889643</v>
       </c>
       <c r="BL16" t="n">
-        <v>8.27185516494052e-05</v>
+        <v>8.271855164940501e-05</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.02385791986934217</v>
+        <v>0.02385791986934212</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.001575435492814617</v>
+        <v>0.001575435492814615</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.349402367809922e-05</v>
+        <v>4.349402367809915e-05</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.0002337653285914242</v>
+        <v>0.0002337653285914238</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.0004739329218598422</v>
+        <v>0.0004739329218598414</v>
       </c>
       <c r="BR16" t="n">
-        <v>0.0001003335179018672</v>
+        <v>0.0001003335179018671</v>
       </c>
       <c r="BS16" t="n">
-        <v>0.01950772879508409</v>
+        <v>0.01950772879508405</v>
       </c>
       <c r="BT16" t="n">
-        <v>0.005707164836676754</v>
+        <v>0.005707164836676744</v>
       </c>
       <c r="BU16" t="n">
-        <v>0.003056668104876041</v>
+        <v>0.003056668104876035</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.003120694906118784</v>
+        <v>0.003120694906118779</v>
       </c>
       <c r="BW16" t="n">
-        <v>7.759009356925431e-06</v>
+        <v>7.759009356925414e-06</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.002371626641604716</v>
+        <v>0.002371626641604713</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.0001260782076456296</v>
+        <v>0.0001260782076456294</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.004903408717741501</v>
+        <v>0.004903408717741492</v>
       </c>
       <c r="CA16" t="n">
-        <v>0.0001010177328303708</v>
+        <v>0.0001010177328303706</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.0003516013335337215</v>
+        <v>0.0003516013335337209</v>
       </c>
       <c r="CC16" t="n">
-        <v>8.39232128075027e-05</v>
+        <v>8.392321280750255e-05</v>
       </c>
       <c r="CD16" t="n">
-        <v>0.0001828329719946776</v>
+        <v>0.0001828329719946773</v>
       </c>
       <c r="CE16" t="n">
-        <v>0.007382286263322609</v>
+        <v>0.007382286263322596</v>
       </c>
       <c r="CF16" t="n">
-        <v>0.001350978161920743</v>
+        <v>0.00135097816192074</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.003057060948564139</v>
+        <v>0.003057060948564134</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.0003956386348537367</v>
+        <v>0.000395638634853736</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.0001455378523668287</v>
+        <v>0.0001455378523668285</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0.00544621979965967</v>
+        <v>0.005446219799659661</v>
       </c>
       <c r="CK16" t="n">
-        <v>8.556934835711411e-06</v>
+        <v>8.556934835711395e-06</v>
       </c>
       <c r="CL16" t="n">
-        <v>0.0004461721784073692</v>
+        <v>0.0004461721784073684</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.152291056115203e-05</v>
+        <v>2.152291056115199e-05</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.0002226829529576707</v>
+        <v>0.0002226829529576704</v>
       </c>
       <c r="CO16" t="n">
-        <v>0.0005476144445495923</v>
+        <v>0.0005476144445495913</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.0005909249003139253</v>
+        <v>0.0005909249003139239</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.0006230567426738979</v>
+        <v>0.0006230567426738969</v>
       </c>
       <c r="CR16" t="n">
-        <v>0.0005764139891947532</v>
+        <v>0.0005764139891947523</v>
       </c>
       <c r="CS16" t="n">
-        <v>0.0001019310341957299</v>
+        <v>0.0001019310341957297</v>
       </c>
       <c r="CT16" t="n">
-        <v>0.0002041728062131509</v>
+        <v>0.0002041728062131506</v>
       </c>
       <c r="CU16" t="n">
-        <v>0.0001069276668782671</v>
+        <v>0.0001069276668782669</v>
       </c>
       <c r="CV16" t="n">
-        <v>0.0003274659057504117</v>
+        <v>0.0003274659057504111</v>
       </c>
       <c r="CW16" t="n">
-        <v>0.0003671049326700668</v>
+        <v>0.0003671049326700661</v>
       </c>
       <c r="CX16" t="n">
-        <v>0.00279219894633889</v>
+        <v>0.002792198946338885</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.0001135633171057592</v>
+        <v>0.0001135633171057591</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.0002138142152101319</v>
+        <v>0.0002138142152101316</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.0002357166992260036</v>
+        <v>0.0002357166992260032</v>
       </c>
       <c r="DB16" t="n">
-        <v>0.0003437081002440734</v>
+        <v>0.0003437081002440728</v>
       </c>
       <c r="DC16" t="n">
-        <v>9.112173019934344e-05</v>
+        <v>9.112173019934329e-05</v>
       </c>
       <c r="DD16" t="n">
-        <v>0.001195313002672405</v>
+        <v>0.001195313002672403</v>
       </c>
       <c r="DE16" t="n">
-        <v>8.338737405079268e-06</v>
+        <v>8.338737405079253e-06</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.0003352321035562029</v>
+        <v>0.0003352321035562023</v>
       </c>
       <c r="DG16" t="n">
-        <v>0.004840394505408672</v>
+        <v>0.004840394505408663</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.0004541330741694497</v>
+        <v>0.0004541330741694494</v>
       </c>
       <c r="DI16" t="n">
-        <v>9.054859350222305e-05</v>
+        <v>9.05485935022229e-05</v>
       </c>
       <c r="DJ16" t="n">
-        <v>5.712555884213577e-05</v>
+        <v>5.712555884213567e-05</v>
       </c>
       <c r="DK16" t="n">
-        <v>0.001138868875978576</v>
+        <v>0.001138868875978574</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.0002297292812005106</v>
+        <v>0.0002297292812005102</v>
       </c>
       <c r="DM16" t="n">
-        <v>0.0002091337563942769</v>
+        <v>0.0002091337563942766</v>
       </c>
       <c r="DN16" t="n">
-        <v>3.702142003373666e-05</v>
+        <v>3.70214200337366e-05</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.0008798925066962985</v>
+        <v>0.000879892506696297</v>
       </c>
       <c r="DP16" t="n">
-        <v>0.1305533415401705</v>
+        <v>0.1305533415401703</v>
       </c>
       <c r="DQ16" t="n">
-        <v>4.660820664414338e-06</v>
+        <v>4.66082066441433e-06</v>
       </c>
       <c r="DR16" t="n">
-        <v>5.004814956522862e-05</v>
+        <v>5.004814956522854e-05</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.003638532305676408</v>
+        <v>0.003638532305676402</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.001153233730294076</v>
+        <v>0.001153233730294074</v>
       </c>
       <c r="DU16" t="n">
-        <v>0.003041172779060592</v>
+        <v>0.003041172779060586</v>
       </c>
       <c r="DV16" t="n">
-        <v>8.96823993884053e-05</v>
+        <v>8.968239938840513e-05</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.0004420284609873087</v>
+        <v>0.0004420284609873075</v>
       </c>
       <c r="DX16" t="n">
-        <v>0.0006042562446612362</v>
+        <v>0.0006042562446612352</v>
       </c>
       <c r="DY16" t="n">
-        <v>0.0002621271043185366</v>
+        <v>0.0002621271043185361</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.0001867054712096343</v>
+        <v>0.000186705471209634</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.0004049070232878364</v>
+        <v>0.0004049070232878352</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.0002451122561793789</v>
+        <v>0.0002451122561793785</v>
       </c>
       <c r="EC16" t="n">
-        <v>0.00745132515260964</v>
+        <v>0.007451325152609628</v>
       </c>
       <c r="ED16" t="n">
-        <v>5.568413747252949e-06</v>
+        <v>5.568413747252939e-06</v>
       </c>
       <c r="EE16" t="n">
-        <v>9.188427525466688e-05</v>
+        <v>9.188427525466668e-05</v>
       </c>
       <c r="EF16" t="n">
-        <v>2.345319811165469e-06</v>
+        <v>2.345319811165464e-06</v>
       </c>
       <c r="EG16" t="n">
-        <v>5.938930979330267e-05</v>
+        <v>5.938930979330257e-05</v>
       </c>
       <c r="EH16" t="n">
-        <v>3.498908955599257e-05</v>
+        <v>3.498908955599251e-05</v>
       </c>
       <c r="EI16" t="n">
-        <v>2.735194754802619e-05</v>
+        <v>2.735194754802615e-05</v>
       </c>
       <c r="EJ16" t="n">
-        <v>2.914089604983801e-05</v>
+        <v>2.914089604983796e-05</v>
       </c>
       <c r="EK16" t="n">
-        <v>2.578961921261763</v>
+        <v>2.578961921261768</v>
       </c>
       <c r="EL16" t="inlineStr">
         <is>
@@ -8890,424 +8890,424 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.3592142414100329</v>
+        <v>0.3592142414100317</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0005797234571972056</v>
+        <v>0.0005797234571972046</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0006767661585358676</v>
+        <v>0.0006767661585358663</v>
       </c>
       <c r="E17" t="n">
-        <v>0.01032920301830001</v>
+        <v>0.01032920301829999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2148342306962205</v>
+        <v>0.2148342306962201</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6093015405986162</v>
+        <v>0.6093015405986151</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2434412493288413</v>
+        <v>0.2434412493288409</v>
       </c>
       <c r="I17" t="n">
-        <v>0.07707292660978328</v>
+        <v>0.07707292660978313</v>
       </c>
       <c r="J17" t="n">
-        <v>0.02054828593629143</v>
+        <v>0.02054828593629139</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1014235631803267</v>
+        <v>0.1014235631803265</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02616500361033506</v>
+        <v>0.02616500361033498</v>
       </c>
       <c r="M17" t="n">
-        <v>0.002898387044709071</v>
+        <v>0.002898387044709063</v>
       </c>
       <c r="N17" t="n">
-        <v>0.01264344148711941</v>
+        <v>0.01264344148711938</v>
       </c>
       <c r="O17" t="n">
-        <v>0.00305907635596417</v>
+        <v>0.003059076355964164</v>
       </c>
       <c r="P17" t="n">
-        <v>0.004362104761418687</v>
+        <v>0.004362104761418679</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.004671378986097249</v>
+        <v>0.002832653168570885</v>
       </c>
       <c r="R17" t="n">
-        <v>0.005722387961358269</v>
+        <v>0.005722387961358258</v>
       </c>
       <c r="S17" t="n">
-        <v>0.004088979659470145</v>
+        <v>0.00408897965947014</v>
       </c>
       <c r="T17" t="n">
-        <v>0.01490157043620636</v>
+        <v>0.01490157043620634</v>
       </c>
       <c r="U17" t="n">
-        <v>2.865218104956496e-05</v>
+        <v>2.865218104956491e-05</v>
       </c>
       <c r="V17" t="n">
-        <v>0.001445362009544935</v>
+        <v>0.001445362009544933</v>
       </c>
       <c r="W17" t="n">
-        <v>0.04779620990327637</v>
+        <v>0.04779620990327628</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0003199810516451339</v>
+        <v>0.0003199810516451329</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.003138312495932894</v>
+        <v>0.003138312495932891</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.002655807928927973</v>
+        <v>0.002655807928927969</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.03762579335559059</v>
+        <v>0.03762579335559051</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.0006412815292484092</v>
+        <v>0.000641281529248408</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.02352674075978979</v>
+        <v>0.02352674075978973</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.343386356842002e-05</v>
+        <v>4.343386356841994e-05</v>
       </c>
       <c r="AE17" t="n">
-        <v>9.431410955766074e-06</v>
+        <v>9.431410955766057e-06</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.06708997719205463</v>
+        <v>0.06708997719205451</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.02375014221362073</v>
+        <v>0.0237501422136207</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.001904074238955246</v>
+        <v>0.001904074238955242</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.001090060926815166</v>
+        <v>0.001090060926815164</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.002363998258749109</v>
+        <v>0.002363998258749105</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.0132878048555289</v>
+        <v>0.01328780485552888</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.0007140299726111843</v>
+        <v>0.0007140299726111826</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.0002993739985333294</v>
+        <v>0.0002993739985333289</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.0002719351955504413</v>
+        <v>0.0002719351955504408</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.0004863974442671187</v>
+        <v>0.0004863974442671178</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.0003496525154971864</v>
+        <v>0.0003496525154971857</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.001210809985791676</v>
+        <v>0.001210809985791674</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.006353666379225841</v>
+        <v>0.006353666379225832</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.0001363404171545517</v>
+        <v>0.0001363404171545514</v>
       </c>
       <c r="AT17" t="n">
-        <v>4.372186742767119e-05</v>
+        <v>4.37218674276711e-05</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.0002476593081000515</v>
+        <v>0.0002476593081000511</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.003290227578162127</v>
+        <v>0.003290227578162121</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.003149544606781565</v>
+        <v>0.00314954460678156</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.0002829044346950708</v>
+        <v>0.0002829044346950704</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.05359375051953085</v>
+        <v>0.05359375051953075</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.000552082732991472</v>
+        <v>0.0005520827329914709</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.263384866404726e-05</v>
+        <v>6.263384866404715e-05</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.04886657998433273</v>
+        <v>0.04886657998433264</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.006804386168348163</v>
+        <v>0.00680438616834815</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.02214202986634854</v>
+        <v>0.02214202986634849</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.000383400056248179</v>
+        <v>0.0003834000562481783</v>
       </c>
       <c r="BF17" t="n">
-        <v>0.0005743023755022545</v>
+        <v>0.0005743023755022535</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.0009177328602469742</v>
+        <v>0.0009177328602469725</v>
       </c>
       <c r="BH17" t="n">
-        <v>0.01449400485070745</v>
+        <v>0.01449400485070742</v>
       </c>
       <c r="BI17" t="n">
-        <v>0.0004207870170637173</v>
+        <v>0.0004207870170637165</v>
       </c>
       <c r="BJ17" t="n">
-        <v>7.955291607649624e-05</v>
+        <v>7.955291607649609e-05</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.008065754923530401</v>
+        <v>0.008065754923530385</v>
       </c>
       <c r="BL17" t="n">
-        <v>7.891635247581617e-05</v>
+        <v>7.891635247581602e-05</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.02453602203652264</v>
+        <v>0.0245360220365226</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.001375439512742643</v>
+        <v>0.00137543951274264</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.790217554829133e-05</v>
+        <v>3.790217554829125e-05</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.0002080555588645426</v>
+        <v>0.0002080555588645423</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.0004929698411740952</v>
+        <v>0.0004929698411740945</v>
       </c>
       <c r="BR17" t="n">
-        <v>6.288620684439775e-05</v>
+        <v>6.288620684439763e-05</v>
       </c>
       <c r="BS17" t="n">
-        <v>0.01681993792424363</v>
+        <v>0.01681993792424359</v>
       </c>
       <c r="BT17" t="n">
-        <v>0.005939143501909487</v>
+        <v>0.005939143501909476</v>
       </c>
       <c r="BU17" t="n">
-        <v>0.002702769091263287</v>
+        <v>0.002702769091263282</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.003032612141934242</v>
+        <v>0.003032612141934238</v>
       </c>
       <c r="BW17" t="n">
-        <v>5.050147252675561e-06</v>
+        <v>5.050147252675552e-06</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.002042727213716987</v>
+        <v>0.002042727213716983</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.000104682592842036</v>
+        <v>0.0001046825928420358</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.003408499243218245</v>
+        <v>0.003408499243218239</v>
       </c>
       <c r="CA17" t="n">
-        <v>8.635270826925168e-05</v>
+        <v>8.635270826925152e-05</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.0003294409049942673</v>
+        <v>0.0003294409049942667</v>
       </c>
       <c r="CC17" t="n">
-        <v>8.472291645198798e-05</v>
+        <v>8.472291645198782e-05</v>
       </c>
       <c r="CD17" t="n">
-        <v>0.0001626668326362286</v>
+        <v>0.0001626668326362282</v>
       </c>
       <c r="CE17" t="n">
-        <v>0.00690861896524938</v>
+        <v>0.006908618965249367</v>
       </c>
       <c r="CF17" t="n">
-        <v>0.001249841231396709</v>
+        <v>0.001249841231396706</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.001971092077951116</v>
+        <v>0.001971092077951112</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.0003664682219733398</v>
+        <v>0.0003664682219733391</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.0001395614032200665</v>
+        <v>0.0001395614032200662</v>
       </c>
       <c r="CJ17" t="n">
-        <v>0.003846169694937042</v>
+        <v>0.003846169694937035</v>
       </c>
       <c r="CK17" t="n">
-        <v>8.381395480228596e-06</v>
+        <v>8.381395480228581e-06</v>
       </c>
       <c r="CL17" t="n">
-        <v>0.0003453961352067602</v>
+        <v>0.0003453961352067592</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.16030551501902e-05</v>
+        <v>2.160305515019016e-05</v>
       </c>
       <c r="CN17" t="n">
-        <v>0.0002209741481720769</v>
+        <v>0.0002209741481720764</v>
       </c>
       <c r="CO17" t="n">
-        <v>0.0009520600251581208</v>
+        <v>0.000952060025158119</v>
       </c>
       <c r="CP17" t="n">
-        <v>0.0005674705423025673</v>
+        <v>0.0005674705423025662</v>
       </c>
       <c r="CQ17" t="n">
-        <v>0.000570432586830578</v>
+        <v>0.0005704325868305774</v>
       </c>
       <c r="CR17" t="n">
-        <v>0.0005544443176426115</v>
+        <v>0.0005544443176426109</v>
       </c>
       <c r="CS17" t="n">
-        <v>8.866520999326356e-05</v>
+        <v>8.86652099932634e-05</v>
       </c>
       <c r="CT17" t="n">
-        <v>0.0001845267536657608</v>
+        <v>0.0001845267536657605</v>
       </c>
       <c r="CU17" t="n">
-        <v>9.918040746000986e-05</v>
+        <v>9.918040746000967e-05</v>
       </c>
       <c r="CV17" t="n">
-        <v>0.0002778546763867709</v>
+        <v>0.0002778546763867703</v>
       </c>
       <c r="CW17" t="n">
-        <v>0.0003617716391315846</v>
+        <v>0.0003617716391315839</v>
       </c>
       <c r="CX17" t="n">
-        <v>0.003598297443736773</v>
+        <v>0.003598297443736767</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.0001069680607088709</v>
+        <v>0.0001069680607088707</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.0001740761298674071</v>
+        <v>0.0001740761298674067</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.0002208838313862022</v>
+        <v>0.0002208838313862018</v>
       </c>
       <c r="DB17" t="n">
-        <v>0.0003195702578134587</v>
+        <v>0.0003195702578134581</v>
       </c>
       <c r="DC17" t="n">
-        <v>0.0001006477127996057</v>
+        <v>0.0001006477127996056</v>
       </c>
       <c r="DD17" t="n">
-        <v>0.001069807747485388</v>
+        <v>0.001069807747485386</v>
       </c>
       <c r="DE17" t="n">
-        <v>6.873481766846088e-06</v>
+        <v>6.873481766846075e-06</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.0003679999278624259</v>
+        <v>0.0003679999278624252</v>
       </c>
       <c r="DG17" t="n">
-        <v>0.004166121585816861</v>
+        <v>0.004166121585816853</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.0003515711973770507</v>
+        <v>0.00035157119737705</v>
       </c>
       <c r="DI17" t="n">
-        <v>8.019102470218472e-05</v>
+        <v>8.019102470218457e-05</v>
       </c>
       <c r="DJ17" t="n">
-        <v>5.451735285236109e-05</v>
+        <v>5.451735285236098e-05</v>
       </c>
       <c r="DK17" t="n">
-        <v>0.001051630613939794</v>
+        <v>0.001051630613939792</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.0001837893616012302</v>
+        <v>0.0001837893616012298</v>
       </c>
       <c r="DM17" t="n">
-        <v>0.0002037306526251759</v>
+        <v>0.0002037306526251755</v>
       </c>
       <c r="DN17" t="n">
-        <v>3.470563225396629e-05</v>
+        <v>3.470563225396622e-05</v>
       </c>
       <c r="DO17" t="n">
-        <v>0.0008019016660113242</v>
+        <v>0.0008019016660113226</v>
       </c>
       <c r="DP17" t="n">
-        <v>0.1541281423823047</v>
+        <v>0.1541281423823044</v>
       </c>
       <c r="DQ17" t="n">
-        <v>3.945080086390415e-06</v>
+        <v>3.945080086390407e-06</v>
       </c>
       <c r="DR17" t="n">
-        <v>4.55070380458344e-05</v>
+        <v>4.550703804583431e-05</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.003030780187189291</v>
+        <v>0.003030780187189285</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.001080910931690243</v>
+        <v>0.001080910931690241</v>
       </c>
       <c r="DU17" t="n">
-        <v>0.002402038218682367</v>
+        <v>0.002402038218682363</v>
       </c>
       <c r="DV17" t="n">
-        <v>6.292396638284643e-05</v>
+        <v>6.292396638284633e-05</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.0003833170806812588</v>
+        <v>0.0003833170806812581</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.0004864330383639901</v>
+        <v>0.0004864330383639892</v>
       </c>
       <c r="DY17" t="n">
-        <v>0.0002451784477108443</v>
+        <v>0.0002451784477108439</v>
       </c>
       <c r="DZ17" t="n">
-        <v>0.0001753688878877511</v>
+        <v>0.0001753688878877508</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.0003620587947878517</v>
+        <v>0.000362058794787851</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.0002096576720597361</v>
+        <v>0.0002096576720597357</v>
       </c>
       <c r="EC17" t="n">
-        <v>0.008117523773644686</v>
+        <v>0.008117523773644671</v>
       </c>
       <c r="ED17" t="n">
-        <v>5.17398005304692e-06</v>
+        <v>5.173980053046911e-06</v>
       </c>
       <c r="EE17" t="n">
-        <v>8.232246393721071e-05</v>
+        <v>8.232246393721055e-05</v>
       </c>
       <c r="EF17" t="n">
-        <v>2.001559751650579e-06</v>
+        <v>2.001559751650575e-06</v>
       </c>
       <c r="EG17" t="n">
-        <v>5.035386018980238e-05</v>
+        <v>5.035386018980229e-05</v>
       </c>
       <c r="EH17" t="n">
-        <v>1.937457294514608e-05</v>
+        <v>1.937457294514604e-05</v>
       </c>
       <c r="EI17" t="n">
-        <v>1.482176197963941e-05</v>
+        <v>1.482176197963938e-05</v>
       </c>
       <c r="EJ17" t="n">
-        <v>2.420780622873918e-05</v>
+        <v>2.420780622873913e-05</v>
       </c>
       <c r="EK17" t="n">
-        <v>3.532585436974768</v>
+        <v>3.532585436974775</v>
       </c>
       <c r="EL17" t="inlineStr">
         <is>
@@ -9398,424 +9398,424 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.3650342009336014</v>
+        <v>0.3650342009336008</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0005696592021732335</v>
+        <v>0.0005696592021732325</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0007697300571981612</v>
+        <v>0.0007697300571981599</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01020828125458456</v>
+        <v>0.01020828125458455</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2217892661567528</v>
+        <v>0.2217892661567524</v>
       </c>
       <c r="G18" t="n">
-        <v>0.610541746826741</v>
+        <v>0.61054174682674</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2585679992503969</v>
+        <v>0.2585679992503965</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0810766574926836</v>
+        <v>0.08107665749268346</v>
       </c>
       <c r="J18" t="n">
-        <v>0.01909350336988797</v>
+        <v>0.01909350336988794</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1179860134543248</v>
+        <v>0.1179860134543246</v>
       </c>
       <c r="L18" t="n">
-        <v>0.02687370328787018</v>
+        <v>0.02687370328787014</v>
       </c>
       <c r="M18" t="n">
-        <v>0.002940163620158978</v>
+        <v>0.002940163620158971</v>
       </c>
       <c r="N18" t="n">
-        <v>0.01285480496807716</v>
+        <v>0.01285480496807713</v>
       </c>
       <c r="O18" t="n">
-        <v>0.003008128090973159</v>
+        <v>0.003008128090973154</v>
       </c>
       <c r="P18" t="n">
-        <v>0.004274422958892725</v>
+        <v>0.004274422958892717</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.004481745631244775</v>
+        <v>0.002825395123118925</v>
       </c>
       <c r="R18" t="n">
-        <v>0.006512777118788149</v>
+        <v>0.006512777118788138</v>
       </c>
       <c r="S18" t="n">
-        <v>0.004019155835911675</v>
+        <v>0.004019155835911671</v>
       </c>
       <c r="T18" t="n">
-        <v>0.01323227985844572</v>
+        <v>0.0132322798584457</v>
       </c>
       <c r="U18" t="n">
-        <v>2.868418450260135e-05</v>
+        <v>2.86841845026013e-05</v>
       </c>
       <c r="V18" t="n">
-        <v>0.001366137459076177</v>
+        <v>0.001366137459076174</v>
       </c>
       <c r="W18" t="n">
-        <v>0.05871949883175197</v>
+        <v>0.05871949883175187</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0003400470523882176</v>
+        <v>0.0003400470523882171</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.003074300827190869</v>
+        <v>0.003074300827190863</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.002720831020997819</v>
+        <v>0.002720831020997814</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.03909994863228689</v>
+        <v>0.03909994863228683</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.0006198666288863056</v>
+        <v>0.0006198666288863045</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.02275738719670907</v>
+        <v>0.02275738719670903</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.7527559007701e-05</v>
+        <v>2.752755900770095e-05</v>
       </c>
       <c r="AE18" t="n">
-        <v>8.004120238920518e-06</v>
+        <v>8.004120238920505e-06</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.06692209692445332</v>
+        <v>0.06692209692445321</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.02280353246081934</v>
+        <v>0.0228035324608193</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.001856459899621281</v>
+        <v>0.001856459899621278</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.001174407523124253</v>
+        <v>0.001174407523124251</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.002491523520162363</v>
+        <v>0.002491523520162357</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.01164600652073184</v>
+        <v>0.01164600652073182</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.0006893096633073772</v>
+        <v>0.000689309663307376</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.0002643910998764151</v>
+        <v>0.0002643910998764146</v>
       </c>
       <c r="AN18" t="n">
-        <v>0.0002536073150782196</v>
+        <v>0.0002536073150782192</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.000442374258158029</v>
+        <v>0.0004423742581580282</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.0003273634475817142</v>
+        <v>0.0003273634475817137</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.00130025567812156</v>
+        <v>0.001300255678121557</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.006760586455906063</v>
+        <v>0.006760586455906051</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.0001540966347736209</v>
+        <v>0.0001540966347736206</v>
       </c>
       <c r="AT18" t="n">
-        <v>4.363284252150871e-05</v>
+        <v>4.363284252150864e-05</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.0002657731735858921</v>
+        <v>0.0002657731735858917</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.003935888420612569</v>
+        <v>0.003935888420612562</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.002846759792482003</v>
+        <v>0.002846759792481998</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.0002920348459138466</v>
+        <v>0.0002920348459138461</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.05521119683031222</v>
+        <v>0.0552111968303121</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.0005271878128941193</v>
+        <v>0.0005271878128941185</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.214241074019171e-05</v>
+        <v>6.21424107401916e-05</v>
       </c>
       <c r="BB18" t="n">
-        <v>0.05022123900681674</v>
+        <v>0.05022123900681662</v>
       </c>
       <c r="BC18" t="n">
-        <v>0.006784337228342118</v>
+        <v>0.006784337228342107</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.02323241079605995</v>
+        <v>0.0232324107960599</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.0004180363681211612</v>
+        <v>0.0004180363681211604</v>
       </c>
       <c r="BF18" t="n">
-        <v>0.0006208978186005704</v>
+        <v>0.0006208978186005694</v>
       </c>
       <c r="BG18" t="n">
-        <v>0.0007142882419329288</v>
+        <v>0.000714288241932928</v>
       </c>
       <c r="BH18" t="n">
-        <v>0.01410614445461148</v>
+        <v>0.01410614445461146</v>
       </c>
       <c r="BI18" t="n">
-        <v>0.0004348511587189965</v>
+        <v>0.0004348511587189958</v>
       </c>
       <c r="BJ18" t="n">
-        <v>2.231561562412052e-06</v>
+        <v>2.231561562412049e-06</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.007716306227240419</v>
+        <v>0.007716306227240404</v>
       </c>
       <c r="BL18" t="n">
-        <v>8.853941025930571e-05</v>
+        <v>8.853941025930556e-05</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.02174138617389625</v>
+        <v>0.02174138617389622</v>
       </c>
       <c r="BN18" t="n">
-        <v>0.001283396058235565</v>
+        <v>0.001283396058235563</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.470872336588107e-05</v>
+        <v>3.470872336588101e-05</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.0001968986371931381</v>
+        <v>0.0001968986371931378</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0.0005243358330226524</v>
+        <v>0.0005243358330226515</v>
       </c>
       <c r="BR18" t="n">
-        <v>7.471591000537427e-05</v>
+        <v>7.471591000537415e-05</v>
       </c>
       <c r="BS18" t="n">
-        <v>0.01668610559968934</v>
+        <v>0.01668610559968932</v>
       </c>
       <c r="BT18" t="n">
-        <v>0.004829788899865072</v>
+        <v>0.004829788899865062</v>
       </c>
       <c r="BU18" t="n">
-        <v>0.002561413536539372</v>
+        <v>0.002561413536539368</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.002735029861005963</v>
+        <v>0.002735029861005958</v>
       </c>
       <c r="BW18" t="n">
-        <v>6.254616795389829e-06</v>
+        <v>6.254616795389818e-06</v>
       </c>
       <c r="BX18" t="n">
-        <v>0.002114680794657318</v>
+        <v>0.002114680794657314</v>
       </c>
       <c r="BY18" t="n">
-        <v>0.000114409869077879</v>
+        <v>0.0001144098690778788</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0.002334293038453719</v>
+        <v>0.002334293038453715</v>
       </c>
       <c r="CA18" t="n">
-        <v>8.155429384044714e-05</v>
+        <v>8.155429384044702e-05</v>
       </c>
       <c r="CB18" t="n">
-        <v>0.0003354746820972779</v>
+        <v>0.0003354746820972773</v>
       </c>
       <c r="CC18" t="n">
-        <v>7.806456318332048e-05</v>
+        <v>7.806456318332038e-05</v>
       </c>
       <c r="CD18" t="n">
-        <v>0.0001504825622307543</v>
+        <v>0.0001504825622307541</v>
       </c>
       <c r="CE18" t="n">
-        <v>0.006925343552870738</v>
+        <v>0.006925343552870726</v>
       </c>
       <c r="CF18" t="n">
-        <v>0.001437601731754501</v>
+        <v>0.001437601731754499</v>
       </c>
       <c r="CG18" t="n">
-        <v>0.001803294231078732</v>
+        <v>0.001803294231078728</v>
       </c>
       <c r="CH18" t="n">
-        <v>0.0003590820624621665</v>
+        <v>0.0003590820624621659</v>
       </c>
       <c r="CI18" t="n">
-        <v>0.0001812095791103055</v>
+        <v>0.0001812095791103052</v>
       </c>
       <c r="CJ18" t="n">
-        <v>0.003377954070705414</v>
+        <v>0.003377954070705409</v>
       </c>
       <c r="CK18" t="n">
-        <v>6.65836054812207e-06</v>
+        <v>6.658360548122059e-06</v>
       </c>
       <c r="CL18" t="n">
-        <v>0.0003933428859074347</v>
+        <v>0.0003933428859074341</v>
       </c>
       <c r="CM18" t="n">
-        <v>1.851754231460183e-05</v>
+        <v>1.851754231460179e-05</v>
       </c>
       <c r="CN18" t="n">
-        <v>0.0001863843521935318</v>
+        <v>0.0001863843521935316</v>
       </c>
       <c r="CO18" t="n">
-        <v>0.001522778292561195</v>
+        <v>0.001522778292561192</v>
       </c>
       <c r="CP18" t="n">
-        <v>0.0004628653331790823</v>
+        <v>0.0004628653331790815</v>
       </c>
       <c r="CQ18" t="n">
-        <v>0.0004592543823378734</v>
+        <v>0.0004592543823378725</v>
       </c>
       <c r="CR18" t="n">
-        <v>0.0005328674164743373</v>
+        <v>0.0005328674164743364</v>
       </c>
       <c r="CS18" t="n">
-        <v>8.735176577761552e-05</v>
+        <v>8.735176577761538e-05</v>
       </c>
       <c r="CT18" t="n">
-        <v>0.0001663489749297677</v>
+        <v>0.0001663489749297674</v>
       </c>
       <c r="CU18" t="n">
-        <v>8.839561430257429e-05</v>
+        <v>8.839561430257414e-05</v>
       </c>
       <c r="CV18" t="n">
-        <v>0.0002651170005486518</v>
+        <v>0.0002651170005486514</v>
       </c>
       <c r="CW18" t="n">
-        <v>0.0003579408467786327</v>
+        <v>0.0003579408467786321</v>
       </c>
       <c r="CX18" t="n">
-        <v>0.003315717343277404</v>
+        <v>0.003315717343277399</v>
       </c>
       <c r="CY18" t="n">
-        <v>9.419444876683963e-05</v>
+        <v>9.419444876683947e-05</v>
       </c>
       <c r="CZ18" t="n">
-        <v>0.0001668110893564444</v>
+        <v>0.0001668110893564442</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.000201398747610146</v>
+        <v>0.0002013987476101456</v>
       </c>
       <c r="DB18" t="n">
-        <v>0.0003163998726809679</v>
+        <v>0.0003163998726809673</v>
       </c>
       <c r="DC18" t="n">
-        <v>0.0001087398369159846</v>
+        <v>0.0001087398369159844</v>
       </c>
       <c r="DD18" t="n">
-        <v>0.000922051006908766</v>
+        <v>0.0009220510069087644</v>
       </c>
       <c r="DE18" t="n">
-        <v>7.154360387530015e-06</v>
+        <v>7.154360387530002e-06</v>
       </c>
       <c r="DF18" t="n">
-        <v>0.00045197793748535</v>
+        <v>0.0004519779374853493</v>
       </c>
       <c r="DG18" t="n">
-        <v>0.004317910988237223</v>
+        <v>0.004317910988237216</v>
       </c>
       <c r="DH18" t="n">
-        <v>0.0003997466693822759</v>
+        <v>0.0003997466693822752</v>
       </c>
       <c r="DI18" t="n">
-        <v>8.616361687360169e-05</v>
+        <v>8.616361687360154e-05</v>
       </c>
       <c r="DJ18" t="n">
-        <v>4.505278407876487e-05</v>
+        <v>4.505278407876479e-05</v>
       </c>
       <c r="DK18" t="n">
-        <v>0.001024469082008705</v>
+        <v>0.001024469082008703</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.000178331775078999</v>
+        <v>0.0001783317750789987</v>
       </c>
       <c r="DM18" t="n">
-        <v>0.0002383312255011111</v>
+        <v>0.0002383312255011107</v>
       </c>
       <c r="DN18" t="n">
-        <v>3.284799181115411e-05</v>
+        <v>3.284799181115405e-05</v>
       </c>
       <c r="DO18" t="n">
-        <v>0.0007640623654627928</v>
+        <v>0.0007640623654627915</v>
       </c>
       <c r="DP18" t="n">
-        <v>0.1557417063136397</v>
+        <v>0.1557417063136394</v>
       </c>
       <c r="DQ18" t="n">
-        <v>3.409173972834998e-06</v>
+        <v>3.409173972834992e-06</v>
       </c>
       <c r="DR18" t="n">
-        <v>3.872210700375885e-05</v>
+        <v>3.872210700375879e-05</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.00342434920339789</v>
+        <v>0.003424349203397885</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.001010648938888221</v>
+        <v>0.001010648938888219</v>
       </c>
       <c r="DU18" t="n">
-        <v>0.002446528560063091</v>
+        <v>0.002446528560063087</v>
       </c>
       <c r="DV18" t="n">
-        <v>8.065467230034421e-05</v>
+        <v>8.065467230034408e-05</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.0003873568304367136</v>
+        <v>0.0003873568304367129</v>
       </c>
       <c r="DX18" t="n">
-        <v>0.0005041738044867757</v>
+        <v>0.0005041738044867748</v>
       </c>
       <c r="DY18" t="n">
-        <v>0.0002369804197105963</v>
+        <v>0.0002369804197105959</v>
       </c>
       <c r="DZ18" t="n">
-        <v>0.0001603662093148674</v>
+        <v>0.0001603662093148671</v>
       </c>
       <c r="EA18" t="n">
-        <v>0.0003343321291464497</v>
+        <v>0.0003343321291464491</v>
       </c>
       <c r="EB18" t="n">
-        <v>0.0002133862324026611</v>
+        <v>0.0002133862324026607</v>
       </c>
       <c r="EC18" t="n">
-        <v>0.007835672198355171</v>
+        <v>0.007835672198355159</v>
       </c>
       <c r="ED18" t="n">
-        <v>4.175063976824209e-06</v>
+        <v>4.175063976824202e-06</v>
       </c>
       <c r="EE18" t="n">
-        <v>7.756022564998829e-05</v>
+        <v>7.756022564998812e-05</v>
       </c>
       <c r="EF18" t="n">
-        <v>1.745565880593482e-06</v>
+        <v>1.74556588059348e-06</v>
       </c>
       <c r="EG18" t="n">
-        <v>4.504922890370271e-05</v>
+        <v>4.504922890370264e-05</v>
       </c>
       <c r="EH18" t="n">
-        <v>2.720933235499135e-05</v>
+        <v>2.72093323549913e-05</v>
       </c>
       <c r="EI18" t="n">
-        <v>2.106185854888474e-05</v>
+        <v>2.10618585488847e-05</v>
       </c>
       <c r="EJ18" t="n">
-        <v>2.384867104244218e-05</v>
+        <v>2.384867104244214e-05</v>
       </c>
       <c r="EK18" t="n">
-        <v>3.697943256417583</v>
+        <v>3.697943256417589</v>
       </c>
       <c r="EL18" t="inlineStr">
         <is>
@@ -9906,10 +9906,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.3624167039161414</v>
+        <v>0.3624167039161412</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0005330875227220692</v>
+        <v>0.0005330875227220693</v>
       </c>
       <c r="D19" t="n">
         <v>0.0007313697411423027</v>
@@ -9921,13 +9921,13 @@
         <v>0.2099842098305722</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6027095015948658</v>
+        <v>0.6027095015948648</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2402872979684581</v>
+        <v>0.2402872979684583</v>
       </c>
       <c r="I19" t="n">
-        <v>0.07232194509890615</v>
+        <v>0.07232194509890616</v>
       </c>
       <c r="J19" t="n">
         <v>0.02108740906197547</v>
@@ -9936,28 +9936,28 @@
         <v>0.1001814109343353</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0279510647360637</v>
+        <v>0.02795106473606373</v>
       </c>
       <c r="M19" t="n">
         <v>0.00331706862130119</v>
       </c>
       <c r="N19" t="n">
-        <v>0.01323743816668417</v>
+        <v>0.01323743816668418</v>
       </c>
       <c r="O19" t="n">
         <v>0.003148384273029454</v>
       </c>
       <c r="P19" t="n">
-        <v>0.004622816887055406</v>
+        <v>0.004622816887055409</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.004965720391699337</v>
+        <v>0.002831514166186885</v>
       </c>
       <c r="R19" t="n">
-        <v>0.006738566044440671</v>
+        <v>0.006738566044440675</v>
       </c>
       <c r="S19" t="n">
-        <v>0.00408233937892325</v>
+        <v>0.004082339378923248</v>
       </c>
       <c r="T19" t="n">
         <v>0.01519179964967387</v>
@@ -9966,46 +9966,46 @@
         <v>2.51556802161331e-05</v>
       </c>
       <c r="V19" t="n">
-        <v>0.001459079695664011</v>
+        <v>0.001459079695664012</v>
       </c>
       <c r="W19" t="n">
-        <v>0.04942402226719853</v>
+        <v>0.04942402226719854</v>
       </c>
       <c r="X19" t="n">
-        <v>0.0003404464354664331</v>
+        <v>0.0003404464354664332</v>
       </c>
       <c r="Y19" t="n">
         <v>0.003425739322815754</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.003052012057466644</v>
+        <v>0.003052012057466645</v>
       </c>
       <c r="AA19" t="n">
         <v>0.03816464914869597</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.0006626274530067974</v>
+        <v>0.0006626274530067978</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.02520750419250734</v>
+        <v>0.02520750419250733</v>
       </c>
       <c r="AD19" t="n">
         <v>2.818519636219284e-05</v>
       </c>
       <c r="AE19" t="n">
-        <v>9.968723616546827e-06</v>
+        <v>9.968723616546828e-06</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.06379879681704456</v>
+        <v>0.06379879681704458</v>
       </c>
       <c r="AG19" t="n">
         <v>0.0235642964383977</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.001820519767030028</v>
+        <v>0.001820519767030029</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.001225896456566013</v>
+        <v>0.001225896456566014</v>
       </c>
       <c r="AJ19" t="n">
         <v>0.002579585357292189</v>
@@ -10014,7 +10014,7 @@
         <v>0.01348574368262262</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.0007091833770896643</v>
+        <v>0.0007091833770896645</v>
       </c>
       <c r="AM19" t="n">
         <v>0.0003003048909164891</v>
@@ -10026,16 +10026,16 @@
         <v>0.0004523273795171233</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.0003297080148996597</v>
+        <v>0.0003297080148996598</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.0013756186604948</v>
+        <v>0.001375618660494801</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.007062580459950529</v>
+        <v>0.00706258045995053</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.0001507887776776519</v>
+        <v>0.000150788777677652</v>
       </c>
       <c r="AT19" t="n">
         <v>5.619932723971792e-05</v>
@@ -10053,52 +10053,52 @@
         <v>0.000292331066019831</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.05291802878248285</v>
+        <v>0.05291802878248289</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.0006030585495855968</v>
+        <v>0.0006030585495855969</v>
       </c>
       <c r="BA19" t="n">
         <v>6.677596784342456e-05</v>
       </c>
       <c r="BB19" t="n">
-        <v>0.05010367791298082</v>
+        <v>0.0501036779129808</v>
       </c>
       <c r="BC19" t="n">
-        <v>0.006800807162446394</v>
+        <v>0.006800807162446397</v>
       </c>
       <c r="BD19" t="n">
-        <v>0.02551816773606724</v>
+        <v>0.02551816773606725</v>
       </c>
       <c r="BE19" t="n">
         <v>0.0004386830287683619</v>
       </c>
       <c r="BF19" t="n">
-        <v>0.0006174331599326156</v>
+        <v>0.000617433159932616</v>
       </c>
       <c r="BG19" t="n">
-        <v>0.0008232866915907143</v>
+        <v>0.0008232866915907141</v>
       </c>
       <c r="BH19" t="n">
-        <v>0.01477229576818848</v>
+        <v>0.01477229576818847</v>
       </c>
       <c r="BI19" t="n">
-        <v>0.0004027621489522623</v>
+        <v>0.0004027621489522624</v>
       </c>
       <c r="BJ19" t="n">
         <v>0.0001138877796868427</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.007041476123928042</v>
+        <v>0.007041476123928045</v>
       </c>
       <c r="BL19" t="n">
-        <v>8.572481697708277e-05</v>
+        <v>8.572481697708281e-05</v>
       </c>
       <c r="BM19" t="n">
         <v>0.02376213370278344</v>
       </c>
       <c r="BN19" t="n">
-        <v>0.001256181450895546</v>
+        <v>0.001256181450895547</v>
       </c>
       <c r="BO19" t="n">
         <v>3.556478857712248e-05</v>
@@ -10110,7 +10110,7 @@
         <v>0.0004580201155338647</v>
       </c>
       <c r="BR19" t="n">
-        <v>8.398083290595051e-05</v>
+        <v>8.398083290595053e-05</v>
       </c>
       <c r="BS19" t="n">
         <v>0.01721048914019958</v>
@@ -10125,13 +10125,13 @@
         <v>0.003060980414508927</v>
       </c>
       <c r="BW19" t="n">
-        <v>6.972303247226163e-06</v>
+        <v>6.972303247226167e-06</v>
       </c>
       <c r="BX19" t="n">
         <v>0.00219701899137024</v>
       </c>
       <c r="BY19" t="n">
-        <v>9.885583139272867e-05</v>
+        <v>9.885583139272868e-05</v>
       </c>
       <c r="BZ19" t="n">
         <v>0.003198281833577727</v>
@@ -10143,10 +10143,10 @@
         <v>0.0003154503970550022</v>
       </c>
       <c r="CC19" t="n">
-        <v>8.489083579569048e-05</v>
+        <v>8.489083579569049e-05</v>
       </c>
       <c r="CD19" t="n">
-        <v>0.0001736089479613229</v>
+        <v>0.000173608947961323</v>
       </c>
       <c r="CE19" t="n">
         <v>0.007016298094291305</v>
@@ -10158,58 +10158,58 @@
         <v>0.002273411225045024</v>
       </c>
       <c r="CH19" t="n">
-        <v>0.0003589404449617216</v>
+        <v>0.0003589404449617217</v>
       </c>
       <c r="CI19" t="n">
         <v>0.0001903305808920679</v>
       </c>
       <c r="CJ19" t="n">
-        <v>0.004304968646325614</v>
+        <v>0.004304968646325615</v>
       </c>
       <c r="CK19" t="n">
-        <v>6.713929963719564e-06</v>
+        <v>6.713929963719565e-06</v>
       </c>
       <c r="CL19" t="n">
         <v>0.000412936834190458</v>
       </c>
       <c r="CM19" t="n">
-        <v>1.713454058579513e-05</v>
+        <v>1.713454058579514e-05</v>
       </c>
       <c r="CN19" t="n">
         <v>0.0002109871514537551</v>
       </c>
       <c r="CO19" t="n">
-        <v>0.001146210042227357</v>
+        <v>0.001146210042227358</v>
       </c>
       <c r="CP19" t="n">
-        <v>0.0005098464786596699</v>
+        <v>0.0005098464786596701</v>
       </c>
       <c r="CQ19" t="n">
-        <v>0.0004949431238588603</v>
+        <v>0.0004949431238588604</v>
       </c>
       <c r="CR19" t="n">
-        <v>0.0005202029619048229</v>
+        <v>0.000520202961904823</v>
       </c>
       <c r="CS19" t="n">
-        <v>9.080536273001795e-05</v>
+        <v>9.080536273001796e-05</v>
       </c>
       <c r="CT19" t="n">
         <v>0.0001808557801543137</v>
       </c>
       <c r="CU19" t="n">
-        <v>9.071251955530113e-05</v>
+        <v>9.071251955530112e-05</v>
       </c>
       <c r="CV19" t="n">
         <v>0.0002993265871351347</v>
       </c>
       <c r="CW19" t="n">
-        <v>0.000389150124026188</v>
+        <v>0.0003891501240261883</v>
       </c>
       <c r="CX19" t="n">
-        <v>0.003452283542171334</v>
+        <v>0.003452283542171335</v>
       </c>
       <c r="CY19" t="n">
-        <v>9.002282199120107e-05</v>
+        <v>9.002282199120108e-05</v>
       </c>
       <c r="CZ19" t="n">
         <v>0.0001926772358799488</v>
@@ -10230,16 +10230,16 @@
         <v>6.746550838901393e-06</v>
       </c>
       <c r="DF19" t="n">
-        <v>0.0003638613326867834</v>
+        <v>0.0003638613326867835</v>
       </c>
       <c r="DG19" t="n">
-        <v>0.004320271682123755</v>
+        <v>0.004320271682123752</v>
       </c>
       <c r="DH19" t="n">
-        <v>0.0004185501942448721</v>
+        <v>0.0004185501942448722</v>
       </c>
       <c r="DI19" t="n">
-        <v>7.666997731471822e-05</v>
+        <v>7.666997731471823e-05</v>
       </c>
       <c r="DJ19" t="n">
         <v>4.225846497850852e-05</v>
@@ -10254,10 +10254,10 @@
         <v>0.0002558688760493804</v>
       </c>
       <c r="DN19" t="n">
-        <v>3.241507591503502e-05</v>
+        <v>3.241507591503503e-05</v>
       </c>
       <c r="DO19" t="n">
-        <v>0.0007871505645623626</v>
+        <v>0.0007871505645623627</v>
       </c>
       <c r="DP19" t="n">
         <v>0.1531311298536746</v>
@@ -10275,13 +10275,13 @@
         <v>0.0009980772197744055</v>
       </c>
       <c r="DU19" t="n">
-        <v>0.002943344327926664</v>
+        <v>0.002943344327926665</v>
       </c>
       <c r="DV19" t="n">
-        <v>8.69225642515611e-05</v>
+        <v>8.692256425156112e-05</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.0003909976173068613</v>
+        <v>0.0003909976173068616</v>
       </c>
       <c r="DX19" t="n">
         <v>0.0004518049084657726</v>
@@ -10293,7 +10293,7 @@
         <v>0.0001676685773172143</v>
       </c>
       <c r="EA19" t="n">
-        <v>0.0003631324545822652</v>
+        <v>0.0003631324545822653</v>
       </c>
       <c r="EB19" t="n">
         <v>0.0002103582806580788</v>
@@ -10314,7 +10314,7 @@
         <v>4.694600520485056e-05</v>
       </c>
       <c r="EH19" t="n">
-        <v>2.482170657137479e-05</v>
+        <v>2.48217065713748e-05</v>
       </c>
       <c r="EI19" t="n">
         <v>2.123608630254798e-05</v>
